--- a/tools/precos/planilhas/precos-oficiais-Beauty-of-Joseon.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-Beauty-of-Joseon.xlsx
@@ -41,12 +41,17 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F4E8"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -72,7 +77,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -81,6 +86,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -564,12 +570,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MB003678</t>
+          <t>MB003649</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Relief Sun Aqua-Fresh FPS 50+ PA++++: protetor solar de arroz + B5 50 ml</t>
+          <t>Hanbang Serum Discovery Kit: 4 séruns mini de 10 ml</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -578,27 +584,25 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>137.9</v>
+        <v>156.9</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Relief Sun Aqua-Fresh : Rice + B5  (SPF50+ PA++++)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1-Pack</t>
-        </is>
-      </c>
+          <t>Hanbang Serum Discovery Kit</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="I2" s="4" t="n"/>
+        <v>21.6</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>27</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>Esgotado</t>
@@ -606,7 +610,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-aqua-fresh-rice-b5-spf50-pa-uk?variant=52419629646196</t>
+          <t>https://beautyofjoseon.com/products/hanbang-serum-discovery-kit</t>
         </is>
       </c>
       <c r="L2" s="2">
@@ -621,12 +625,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MB003700</t>
+          <t>MB002809</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Tinted Mineral Dayscreen FPS 30: protetor solar mineral com cor 40 ml</t>
+          <t>JELLOSKIN Massage Cream for Face and Body</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -635,35 +639,37 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>145.9</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tinted Mineral Dayscreen SPF 30</t>
+          <t>JELLOSKIN Massage Cream For Face and Body</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>15C</t>
+          <t>1-Pack</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I3" s="4" t="n"/>
+        <v>12.5</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/tinted-mineral-dayscreen-spf-30-global?variant=54870451323252</t>
+          <t>https://beautyofjoseon.com/products/jelloskin-massage-cream-for-face-and-body</t>
         </is>
       </c>
       <c r="L3" s="2">
@@ -678,41 +684,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MB002883</t>
+          <t>MB002813</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bojagi: tecido tradicional coreano para embrulhar presentes · Calm Blue</t>
+          <t>Hanbang Serum Discovery Kit</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>80.90000000000001</v>
+        <v>999.99</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bojagi</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Olive</t>
-        </is>
-      </c>
+          <t>Hanbang Serum Discovery Kit</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="I4" s="4" t="n"/>
+        <v>21.6</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>27</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>Esgotado</t>
@@ -720,7 +724,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/bojagi?variant=40739062481061</t>
+          <t>https://beautyofjoseon.com/products/hanbang-serum-discovery-kit</t>
         </is>
       </c>
       <c r="L4" s="2">
@@ -735,12 +739,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MB002882</t>
+          <t>MB003676</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bojagi: tecido tradicional coreano para embrulhar presentes · Maehwa</t>
+          <t>Beauty of Joseon Matte Sun Stick FPS 50+ PA++++: protetor solar em bastão artemísia + camélia 18 g</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -749,27 +753,29 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+        <v>163.9</v>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bojagi</t>
+          <t>Matte Sun Stick : Mugwort+Camelia (SPF 50+ PA++++)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Olive</t>
+          <t>2-Pack</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="I5" s="4" t="n"/>
+        <v>22.5</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>30</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Esgotado</t>
@@ -777,7 +783,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/bojagi?variant=40739062481061</t>
+          <t>https://beautyofjoseon.com/products/matte-sun-stick-mugwort-camelia-duo</t>
         </is>
       </c>
       <c r="L5" s="2">
@@ -792,12 +798,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MB002881</t>
+          <t>MB003678</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bojagi: tecido tradicional coreano para embrulhar presentes · Olive</t>
+          <t>Beauty of Joseon Relief Sun Aqua-Fresh FPS 50+ PA++++: protetor solar de arroz + B5 50 ml</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,25 +812,25 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+        <v>137.9</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bojagi</t>
+          <t>Relief Sun Aqua-Fresh : Rice + B5  (SPF50+ PA++++)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Olive</t>
+          <t>1-Pack</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I6" s="4" t="n"/>
       <c r="J6" t="inlineStr">
@@ -834,7 +840,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/bojagi?variant=40739062481061</t>
+          <t>https://beautyofjoseon.com/products/relief-sun-aqua-fresh-rice-b5-spf50-pa-uk?variant=52419629646196</t>
         </is>
       </c>
       <c r="L6" s="2">
@@ -849,12 +855,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MB003659</t>
+          <t>MB003700</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Calming Barrier Mask: máscara calmante de centella, 10 unidades</t>
+          <t>Beauty of Joseon Tinted Mineral Dayscreen FPS 30: protetor solar mineral com cor 40 ml</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -863,25 +869,25 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>182.9</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
+        <v>145.9</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Calming Barrier Mask</t>
+          <t>Tinted Mineral Dayscreen SPF 30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>18 mL / 0.60 FL. OZ. (10 Sheets)</t>
+          <t>15C</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I7" s="4" t="n"/>
       <c r="J7" t="inlineStr">
@@ -891,7 +897,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/calming-barrier-sheet-mask-global</t>
+          <t>https://beautyofjoseon.com/products/tinted-mineral-dayscreen-spf-30-global?variant=54870451323252</t>
         </is>
       </c>
       <c r="L7" s="2">
@@ -906,12 +912,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MB003681</t>
+          <t>MB002883</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Duo Revive: sérum para olhos + hidratante firmador com retinol</t>
+          <t>Bojagi: tecido tradicional coreano para embrulhar presentes · Calm Blue</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -920,25 +926,27 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>298.9</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revive Ritual Eye Duo</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Bojagi</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Olive</t>
+        </is>
+      </c>
       <c r="H8" s="4" t="n">
-        <v>27.75</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>37</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="I8" s="4" t="n"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Esgotado</t>
@@ -946,7 +954,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-ritual-eye-duo-eu</t>
+          <t>https://beautyofjoseon.com/products/bojagi?variant=40739062481061</t>
         </is>
       </c>
       <c r="L8" s="2">
@@ -961,12 +969,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MB002838</t>
+          <t>MB002882</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dynasty Cream: creme hidratante de arroz e ginseng · 3.38 fl.oz.(100ml) 2-Pack</t>
+          <t>Bojagi: tecido tradicional coreano para embrulhar presentes · Maehwa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -975,37 +983,35 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>525.9</v>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dynasty Cream</t>
+          <t>Bojagi</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3.38 fl.oz.(100ml)</t>
+          <t>Olive</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>40</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="I9" s="4" t="n"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/dynasty-cream?variant=43222120792229</t>
+          <t>https://beautyofjoseon.com/products/bojagi?variant=40739062481061</t>
         </is>
       </c>
       <c r="L9" s="2">
@@ -1020,12 +1026,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MB003661</t>
+          <t>MB002881</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ginseng Essence Water: essência de ginseng 150 ml</t>
+          <t>Bojagi: tecido tradicional coreano para embrulhar presentes · Olive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1034,35 +1040,35 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>116.9</v>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ginseng Essence Water</t>
+          <t>Bojagi</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>150 ml (5.07 FL. OZ.)</t>
+          <t>Olive</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I10" s="4" t="n"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/ginseng-essence-water</t>
+          <t>https://beautyofjoseon.com/products/bojagi?variant=40739062481061</t>
         </is>
       </c>
       <c r="L10" s="2">
@@ -1077,12 +1083,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MB003668</t>
+          <t>MB003659</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Glow Deep Serum: arroz + alfa-arbutina 30 ml</t>
+          <t>Calming Barrier Mask: máscara calmante de centella, 10 unidades</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1091,25 +1097,25 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>110.9</v>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
+        <v>182.9</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Glow Deep Serum : Rice + Alpha-Arbutin</t>
+          <t>Calming Barrier Mask</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.01 fl. oz.(30ml)</t>
+          <t>18 mL / 0.60 FL. OZ. (10 Sheets)</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I11" s="4" t="n"/>
       <c r="J11" t="inlineStr">
@@ -1119,7 +1125,7 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/glow-deep-serum-rice-alpha-arbutin?variant=51833689211252</t>
+          <t>https://beautyofjoseon.com/products/calming-barrier-sheet-mask-global</t>
         </is>
       </c>
       <c r="L11" s="2">
@@ -1134,12 +1140,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MB003657</t>
+          <t>MB003681</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Glow Replenishing Rice Milk: tônico de arroz 150 ml</t>
+          <t>Duo Revive: sérum para olhos + hidratante firmador com retinol</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1148,37 +1154,33 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>116.9</v>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
+        <v>298.9</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Glow Replenishing Rice Milk</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>150 ml (5.07 FL. OZ.)</t>
-        </is>
-      </c>
+          <t>Revive Ritual Eye Duo</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" s="4" t="n">
-        <v>15.3</v>
+        <v>27.75</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/glow-replenishing-rice-milk</t>
+          <t>https://beautyofjoseon.com/products/revive-ritual-eye-duo-eu</t>
         </is>
       </c>
       <c r="L12" s="2">
@@ -1193,12 +1195,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MB003670</t>
+          <t>MB002838</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Glow Serum: própolis + niacinamida 30 ml</t>
+          <t>Dynasty Cream: creme hidratante de arroz e ginseng · 3.38 fl.oz.(100ml) 2-Pack</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1207,37 +1209,37 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
+        <v>525.9</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Glow Serum : Propolis + Niacinamide</t>
+          <t>Dynasty Cream</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.01 fl. oz.(30ml)</t>
+          <t>3.38 fl.oz.(100ml) 2-Pack</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>15.3</v>
+        <v>72</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/glow-serum-propolis-niacinamide?variant=51833681772916</t>
+          <t>https://beautyofjoseon.com/products/dynasty-cream?variant=55014470091124</t>
         </is>
       </c>
       <c r="L13" s="2">
@@ -1252,12 +1254,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MB003649</t>
+          <t>MB003661</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hanbang Serum Discovery Kit: 4 séruns mini de 10 ml</t>
+          <t>Ginseng Essence Water: essência de ginseng 150 ml</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1266,33 +1268,35 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>156.9</v>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
+        <v>116.9</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hanbang Serum Discovery Kit</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Ginseng Essence Water</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>150 ml (5.07 FL. OZ.)</t>
+        </is>
+      </c>
       <c r="H14" s="4" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>27</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I14" s="4" t="n"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/hanbang-serum-discovery-kit</t>
+          <t>https://beautyofjoseon.com/products/ginseng-essence-water</t>
         </is>
       </c>
       <c r="L14" s="2">
@@ -1307,12 +1311,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MB002809</t>
+          <t>MB003668</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JELLOSKIN Massage Cream for Face and Body</t>
+          <t>Glow Deep Serum: arroz + alfa-arbutina 30 ml</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1321,37 +1325,35 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
+        <v>110.9</v>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JELLOSKIN Massage Cream For Face and Body</t>
+          <t>Glow Deep Serum : Rice + Alpha-Arbutin</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1-Pack</t>
+          <t>1.01 fl. oz.(30ml)</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>25</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I15" s="4" t="n"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/jelloskin-massage-cream-for-face-and-body</t>
+          <t>https://beautyofjoseon.com/products/glow-deep-serum-rice-alpha-arbutin?variant=51833689211252</t>
         </is>
       </c>
       <c r="L15" s="2">
@@ -1366,12 +1368,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MB003680</t>
+          <t>MB003657</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kit Revive Essentials: sérum para olhos, adesivos e hidratante firmador</t>
+          <t>Glow Replenishing Rice Milk: tônico de arroz 150 ml</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1380,24 +1382,28 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>332.9</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
+        <v>116.9</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revive Essentials Set</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Glow Replenishing Rice Milk</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>150 ml (5.07 FL. OZ.)</t>
+        </is>
+      </c>
       <c r="H16" s="4" t="n">
-        <v>45.75</v>
+        <v>15.3</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1406,7 +1412,7 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-essentials-set-global</t>
+          <t>https://beautyofjoseon.com/products/glow-replenishing-rice-milk</t>
         </is>
       </c>
       <c r="L16" s="2">
@@ -1421,12 +1427,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MB003667</t>
+          <t>MB003670</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Light On Serum: centella + vitamina C 30 ml</t>
+          <t>Glow Serum: própolis + niacinamida 30 ml</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1435,27 +1441,29 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Light On Serum : Centella + Vita C</t>
+          <t>Glow Serum : Propolis + Niacinamide</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>30 ml (1.01 FL. OZ.)</t>
+          <t>1.01 fl. oz.(30ml)</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="I17" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="I17" s="4" t="n"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1463,7 +1471,7 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/light-on-serum-centella-vita-c</t>
+          <t>https://beautyofjoseon.com/products/glow-serum-propolis-niacinamide?variant=51833681772916</t>
         </is>
       </c>
       <c r="L17" s="2">
@@ -1478,12 +1486,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MB003666</t>
+          <t>MB003680</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Red Bean Water Gel: hidratante em gel de feijão vermelho 100 ml</t>
+          <t>Kit Revive Essentials: sérum para olhos, adesivos e hidratante firmador</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1492,28 +1500,24 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>104.9</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
+        <v>332.9</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Red Bean Water Gel</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>100 ml (3.38 FL. OZ.)</t>
-        </is>
-      </c>
+          <t>Revive Essentials Set</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" s="4" t="n">
-        <v>14.4</v>
+        <v>45.75</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1522,7 +1526,7 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/red-bean-water-gel</t>
+          <t>https://beautyofjoseon.com/products/revive-essentials-set-global</t>
         </is>
       </c>
       <c r="L18" s="2">
@@ -1537,12 +1541,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MB003669</t>
+          <t>MB003667</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Revive Serum: ginseng + mucina de caracol 30 ml</t>
+          <t>Light On Serum: centella + vitamina C 30 ml</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1551,29 +1555,27 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>110.9</v>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revive Eye Serum : Ginseng + Retinal</t>
+          <t>Light On Serum : Centella + Vita C</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>30ML X 2-PACK</t>
+          <t>30 ml (1.01 FL. OZ.)</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>34</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I19" s="4" t="n"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1581,7 +1583,7 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
+          <t>https://beautyofjoseon.com/products/light-on-serum-centella-vita-c</t>
         </is>
       </c>
       <c r="L19" s="2">
@@ -1596,12 +1598,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MB003682</t>
+          <t>MB003666</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Revive Under Eye Patch: adesivos para olhos de ginseng + retinal, 60 unidades</t>
+          <t>Red Bean Water Gel: hidratante em gel de feijão vermelho 100 ml</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1610,27 +1612,29 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
+        <v>104.9</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revive Under Eye Patch: Ginseng + Retinal</t>
+          <t>Red Bean Water Gel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>100 g / 3.52 OZ. (60 Patches)</t>
+          <t>100 ml (3.38 FL. OZ.)</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I20" s="4" t="n"/>
+        <v>14.4</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>18</v>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1638,7 +1642,7 @@
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-under-eye-patch-global</t>
+          <t>https://beautyofjoseon.com/products/red-bean-water-gel</t>
         </is>
       </c>
       <c r="L20" s="2">
@@ -1653,12 +1657,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MB003693</t>
+          <t>MB003669</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Trio Red Bean para Poros: sérum, máscara e gel hidratante</t>
+          <t>Revive Serum: ginseng + mucina de caracol 30 ml</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1667,31 +1671,37 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>400.9</v>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
+        <v>110.9</v>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Red Bean Pore Care Trio</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>Revive Eye Serum : Ginseng + Retinal</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>30ML X 2-PACK</t>
+        </is>
+      </c>
       <c r="H21" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="I21" s="4" t="n"/>
+        <v>25.5</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>34</v>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/red-bean-pore-care-trio-eu</t>
+          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
         </is>
       </c>
       <c r="L21" s="2">
@@ -1706,49 +1716,49 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MB003696</t>
+          <t>MB003682</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Hydra Shield FPS 50+: protetor solar para o corpo 150 ml</t>
+          <t>Revive Under Eye Patch: adesivos para olhos de ginseng + retinal, 60 unidades</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>181.9</v>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
+        <v>144.9</v>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hydra Shield Body Sun Lotion SPF 50+</t>
+          <t>Revive Under Eye Patch: Ginseng + Retinal</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>150 ml (5.07 FL. OZ.)</t>
+          <t>100 g / 3.52 OZ. (60 Patches)</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I22" s="4" t="n"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/hydra-shield-body-sun-lotion-spf-50-eu</t>
+          <t>https://beautyofjoseon.com/products/revive-under-eye-patch-global</t>
         </is>
       </c>
       <c r="L22" s="2">
@@ -1763,39 +1773,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MB004038</t>
+          <t>MB003693</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Relief Sun Aqua-Fresh FPS 50+ PA++++: protetor solar de arroz + B5, kit com 2 de 50 ml</t>
+          <t>Trio Red Bean para Poros: sérum, máscara e gel hidratante</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>213.9</v>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
+        <v>400.9</v>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Relief Sun Aqua-Fresh : Rice + B5  (SPF50+ PA++++)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>1-Pack</t>
-        </is>
-      </c>
+          <t>Red Bean Pore Care Trio</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" s="4" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="I23" s="4" t="n"/>
       <c r="J23" t="inlineStr">
@@ -1805,7 +1811,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-aqua-fresh-rice-b5-spf50-pa-uk?variant=52419629646196</t>
+          <t>https://beautyofjoseon.com/products/red-bean-pore-care-trio-eu</t>
         </is>
       </c>
       <c r="L23" s="2">
@@ -1820,12 +1826,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MB003646</t>
+          <t>MB003696</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Relief Sun: Rice + Probiotics (SPF 50+ PA++++)</t>
+          <t>Beauty of Joseon Hydra Shield FPS 50+: protetor solar para o corpo 150 ml</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1834,25 +1840,25 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
+        <v>181.9</v>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
+          <t>Hydra Shield Body Sun Lotion SPF 50+</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1-Pack</t>
+          <t>150 ml (5.07 FL. OZ.)</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I24" s="4" t="n"/>
       <c r="J24" t="inlineStr">
@@ -1862,7 +1868,7 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
+          <t>https://beautyofjoseon.com/products/hydra-shield-body-sun-lotion-spf-50-eu</t>
         </is>
       </c>
       <c r="L24" s="2">
@@ -1877,12 +1883,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MB002813</t>
+          <t>MB004038</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hanbang Serum Discovery Kit</t>
+          <t>Beauty of Joseon Relief Sun Aqua-Fresh FPS 50+ PA++++: protetor solar de arroz + B5, kit com 2 de 50 ml</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1891,25 +1897,27 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>999.99</v>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
+        <v>213.9</v>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hanbang Serum Discovery Kit</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>Relief Sun Aqua-Fresh : Rice + B5  (SPF50+ PA++++)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1-Pack</t>
+        </is>
+      </c>
       <c r="H25" s="4" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>27</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="I25" s="4" t="n"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>Esgotado</t>
@@ -1917,7 +1925,7 @@
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/hanbang-serum-discovery-kit</t>
+          <t>https://beautyofjoseon.com/products/relief-sun-aqua-fresh-rice-b5-spf50-pa-uk?variant=52419629646196</t>
         </is>
       </c>
       <c r="L25" s="2">
@@ -1932,12 +1940,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MB003658</t>
+          <t>MB003646</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JELLOSKIN: creme de massagem para rosto e corpo</t>
+          <t>Beauty of Joseon Relief Sun: Rice + Probiotics (SPF 50+ PA++++)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1946,16 +1954,16 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
+        <v>137.9</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JELLOSKIN Massage Cream For Face and Body</t>
+          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1964,11 +1972,9 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>25</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I26" s="4" t="n"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>Esgotado</t>
@@ -1976,7 +1982,7 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/jelloskin-massage-cream-for-face-and-body</t>
+          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
         </is>
       </c>
       <c r="L26" s="2">
@@ -1991,12 +1997,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MB003643</t>
+          <t>MB003658</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Relief Sun Aqua-Fresh Sunscreen: Rice + B5 (SPF 50+ PA++++)</t>
+          <t>JELLOSKIN: creme de massagem para rosto e corpo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2005,24 +2011,28 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Relief Sun Duo : Original + Aqua-Fresh</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>JELLOSKIN Massage Cream For Face and Body</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1-Pack</t>
+        </is>
+      </c>
       <c r="H27" s="4" t="n">
-        <v>29.25</v>
+        <v>12.5</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2031,7 +2041,7 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-duo-original-aqua-fresh-uk</t>
+          <t>https://beautyofjoseon.com/products/jelloskin-massage-cream-for-face-and-body</t>
         </is>
       </c>
       <c r="L27" s="2">
@@ -2046,12 +2056,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MB002785</t>
+          <t>MB003643</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Relief Sun: Arroz + Probióticos (FPS 50+ PA++++) · 1-Pack</t>
+          <t>Relief Sun Aqua-Fresh Sunscreen: Rice + B5 (SPF 50+ PA++++)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2060,27 +2070,25 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>999.99</v>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
+        <v>137.9</v>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>1-Pack</t>
-        </is>
-      </c>
+          <t>Relief Sun Duo : Original + Aqua-Fresh</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="I28" s="4" t="n"/>
+        <v>29.25</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>39</v>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>Esgotado</t>
@@ -2088,7 +2096,7 @@
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
+          <t>https://beautyofjoseon.com/products/relief-sun-duo-original-aqua-fresh-uk</t>
         </is>
       </c>
       <c r="L28" s="2">
@@ -2103,12 +2111,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MB002808</t>
+          <t>MB002785</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sérum Light On: Centella + Vitamina C</t>
+          <t>Relief Sun: Arroz + Probióticos (FPS 50+ PA++++) · 1-Pack</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2117,35 +2125,35 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
+        <v>999.99</v>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Light On Serum : Centella + Vita C</t>
+          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>30 ml (1.01 FL. OZ.)</t>
+          <t>1-Pack</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I29" s="4" t="n"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/light-on-serum-centella-vita-c</t>
+          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
         </is>
       </c>
       <c r="L29" s="2">
@@ -2160,51 +2168,49 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MB003676</t>
+          <t>MB002808</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Matte Sun Stick FPS 50+ PA++++: protetor solar em bastão artemísia + camélia 18 g</t>
+          <t>Sérum Light On: Centella + Vitamina C</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>163.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Matte Sun Stick : Mugwort+Camelia (SPF 50+ PA++++)</t>
+          <t>Light On Serum : Centella + Vita C</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2-Pack</t>
+          <t>30 ml (1.01 FL. OZ.)</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>30</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I30" s="4" t="n"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/matte-sun-stick-mugwort-camelia-duo</t>
+          <t>https://beautyofjoseon.com/products/light-on-serum-centella-vita-c</t>
         </is>
       </c>
       <c r="L30" s="2">
@@ -2235,7 +2241,7 @@
       <c r="D31" s="2" t="n">
         <v>212.9</v>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
@@ -2290,7 +2296,7 @@
       <c r="D32" s="2" t="n">
         <v>144.9</v>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
@@ -2347,7 +2353,7 @@
       <c r="D33" s="2" t="n">
         <v>170.9</v>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
@@ -2402,7 +2408,7 @@
       <c r="D34" s="2" t="n">
         <v>193.9</v>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
@@ -2457,7 +2463,7 @@
       <c r="D35" s="2" t="n">
         <v>201.9</v>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
@@ -2512,7 +2518,7 @@
       <c r="D36" s="2" t="n">
         <v>104.9</v>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
@@ -2569,7 +2575,7 @@
       <c r="D37" s="2" t="n">
         <v>137.9</v>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
@@ -2626,7 +2632,7 @@
       <c r="D38" s="2" t="n">
         <v>213.9</v>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
@@ -2683,7 +2689,7 @@
       <c r="D39" s="2" t="n">
         <v>82.90000000000001</v>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
@@ -2740,7 +2746,7 @@
       <c r="D40" s="2" t="n">
         <v>174.9</v>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
@@ -2797,31 +2803,29 @@
       <c r="D41" s="2" t="n">
         <v>194.9</v>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lightweight Sun Duo</t>
+          <t>Pick + Mix Serum Duo</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" s="4" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>38</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="I41" s="4" t="n"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/lightweight-sun-duo-skincare-set</t>
+          <t>https://beautyofjoseon.com/products/pick-and-mix-serum-duo-skincare-set-eu-uk</t>
         </is>
       </c>
       <c r="L41" s="2">
@@ -2852,7 +2856,7 @@
       <c r="D42" s="2" t="n">
         <v>495.9</v>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
@@ -2907,7 +2911,7 @@
       <c r="D43" s="2" t="n">
         <v>160.9</v>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
@@ -2966,7 +2970,7 @@
       <c r="D44" s="2" t="n">
         <v>160.9</v>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
@@ -3025,7 +3029,7 @@
       <c r="D45" s="2" t="n">
         <v>144.9</v>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E45" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
@@ -5488,7 +5492,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>01BP052</t>
@@ -5683,7 +5691,11 @@
           <t>Esgotado</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>99BP037</t>
@@ -5717,7 +5729,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>01BP089</t>
@@ -5954,7 +5970,11 @@
           <t>Esgotado</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>99BP017</t>
@@ -7428,7 +7448,11 @@
           <t>Esgotado</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
           <t>82BP027</t>
@@ -7462,7 +7486,11 @@
           <t>Esgotado</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
           <t>99BP020</t>
@@ -7496,7 +7524,11 @@
           <t>Esgotado</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr">
         <is>
           <t>82BP027</t>
@@ -11319,7 +11351,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site oficial: https://beautyofjoseon.com · loja "Beauty of Joseon" · moeda USD · lido em 30/10/2026 06:02 UTC</t>
+          <t>Site oficial: https://beautyofjoseon.com · loja "Beauty of Joseon" · moeda USD · lido em 30/10/2026 06:04 UTC</t>
         </is>
       </c>
     </row>

--- a/tools/precos/planilhas/precos-oficiais-Beauty-of-Joseon.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-Beauty-of-Joseon.xlsx
@@ -165,8 +165,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Comparacao" displayName="Comparacao" ref="A1:N96" headerRowCount="1">
-  <autoFilter ref="A1:N96"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Comparacao" displayName="Comparacao" ref="A1:N198" headerRowCount="1">
+  <autoFilter ref="A1:N198"/>
   <tableColumns count="14">
     <tableColumn id="1" name="SKU"/>
     <tableColumn id="2" name="Nosso produto"/>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N96"/>
+  <dimension ref="A1:N198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -570,12 +570,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MB003649</t>
+          <t>MB002826</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hanbang Serum Discovery Kit: 4 séruns mini de 10 ml</t>
+          <t>Duo Glass Skin · Large</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>156.9</v>
+        <v>387.9</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -593,24 +593,28 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hanbang Serum Discovery Kit</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Glass Skin Duo</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
       <c r="H2" s="4" t="n">
-        <v>21.6</v>
+        <v>74</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/hanbang-serum-discovery-kit</t>
+          <t>https://beautyofjoseon.com/products/glass-skin-duo-us?variant=55226029998452</t>
         </is>
       </c>
       <c r="L2" s="2">
@@ -625,12 +629,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MB002809</t>
+          <t>MB002825</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JELLOSKIN Massage Cream for Face and Body</t>
+          <t>Duo Glass Skin · Original</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -639,7 +643,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>193.9</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -648,28 +652,28 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JELLOSKIN Massage Cream For Face and Body</t>
+          <t>Glass Skin Duo</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1-Pack</t>
+          <t>Original</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>12.5</v>
+        <v>26.65</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/jelloskin-massage-cream-for-face-and-body</t>
+          <t>https://beautyofjoseon.com/products/glass-skin-duo-us?variant=55226029965684</t>
         </is>
       </c>
       <c r="L3" s="2">
@@ -684,21 +688,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MB002813</t>
+          <t>MB003649</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hanbang Serum Discovery Kit</t>
+          <t>Hanbang Serum Discovery Kit: 4 séruns mini de 10 ml</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>999.99</v>
+        <v>156.9</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -739,12 +743,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MB003676</t>
+          <t>MB002809</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Matte Sun Stick FPS 50+ PA++++: protetor solar em bastão artemísia + camélia 18 g</t>
+          <t>JELLOSKIN Massage Cream for Face and Body</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -753,28 +757,28 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>163.9</v>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>90.90000000000001</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Matte Sun Stick : Mugwort+Camelia (SPF 50+ PA++++)</t>
+          <t>JELLOSKIN Massage Cream For Face and Body</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2-Pack</t>
+          <t>1-Pack</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>22.5</v>
+        <v>12.5</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -783,7 +787,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/matte-sun-stick-mugwort-camelia-duo</t>
+          <t>https://beautyofjoseon.com/products/jelloskin-massage-cream-for-face-and-body</t>
         </is>
       </c>
       <c r="L5" s="2">
@@ -798,41 +802,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MB003678</t>
+          <t>MB002846</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Relief Sun Aqua-Fresh FPS 50+ PA++++: protetor solar de arroz + B5 50 ml</t>
+          <t>Day and Night Skincare Duo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>999.99</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Relief Sun Aqua-Fresh : Rice + B5  (SPF50+ PA++++)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1-Pack</t>
-        </is>
-      </c>
+          <t>Day and Night Care Duo</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="I6" s="4" t="n"/>
+        <v>31.5</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>42</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>Esgotado</t>
@@ -840,7 +842,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-aqua-fresh-rice-b5-spf50-pa-uk?variant=52419629646196</t>
+          <t>https://beautyofjoseon.com/products/day-night-duo-skincare-set-uk</t>
         </is>
       </c>
       <c r="L6" s="2">
@@ -855,49 +857,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MB003700</t>
+          <t>MB002813</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Tinted Mineral Dayscreen FPS 30: protetor solar mineral com cor 40 ml</t>
+          <t>Hanbang Serum Discovery Kit</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>145.9</v>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>999.99</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tinted Mineral Dayscreen SPF 30</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>15C</t>
-        </is>
-      </c>
+          <t>Hanbang Serum Discovery Kit</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I7" s="4" t="n"/>
+        <v>21.6</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>27</v>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/tinted-mineral-dayscreen-spf-30-global?variant=54870451323252</t>
+          <t>https://beautyofjoseon.com/products/hanbang-serum-discovery-kit</t>
         </is>
       </c>
       <c r="L7" s="2">
@@ -912,12 +912,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MB002883</t>
+          <t>MB003676</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bojagi: tecido tradicional coreano para embrulhar presentes · Calm Blue</t>
+          <t>Beauty of Joseon Matte Sun Stick FPS 50+ PA++++: protetor solar em bastão artemísia + camélia 18 g</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>80.90000000000001</v>
+        <v>163.9</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
@@ -935,18 +935,20 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bojagi</t>
+          <t>Matte Sun Stick : Mugwort+Camelia (SPF 50+ PA++++)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Olive</t>
+          <t>2-Pack</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="I8" s="4" t="n"/>
+        <v>22.5</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>30</v>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Esgotado</t>
@@ -954,7 +956,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/bojagi?variant=40739062481061</t>
+          <t>https://beautyofjoseon.com/products/matte-sun-stick-mugwort-camelia-duo</t>
         </is>
       </c>
       <c r="L8" s="2">
@@ -969,12 +971,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MB002882</t>
+          <t>MB003678</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bojagi: tecido tradicional coreano para embrulhar presentes · Maehwa</t>
+          <t>Beauty of Joseon Relief Sun Aqua-Fresh FPS 50+ PA++++: protetor solar de arroz + B5 50 ml</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -983,7 +985,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>80.90000000000001</v>
+        <v>137.9</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -992,16 +994,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bojagi</t>
+          <t>Relief Sun Aqua-Fresh : Rice + B5  (SPF50+ PA++++)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Olive</t>
+          <t>1-Pack</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I9" s="4" t="n"/>
       <c r="J9" t="inlineStr">
@@ -1011,7 +1013,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/bojagi?variant=40739062481061</t>
+          <t>https://beautyofjoseon.com/products/relief-sun-aqua-fresh-rice-b5-spf50-pa-uk?variant=52419629646196</t>
         </is>
       </c>
       <c r="L9" s="2">
@@ -1026,12 +1028,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MB002881</t>
+          <t>MB003700</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bojagi: tecido tradicional coreano para embrulhar presentes · Olive</t>
+          <t>Beauty of Joseon Tinted Mineral Dayscreen FPS 30: protetor solar mineral com cor 40 ml</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1042,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>80.90000000000001</v>
+        <v>145.9</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -1049,26 +1051,26 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bojagi</t>
+          <t>Tinted Mineral Dayscreen SPF 30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Olive</t>
+          <t>15C</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I10" s="4" t="n"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/bojagi?variant=40739062481061</t>
+          <t>https://beautyofjoseon.com/products/tinted-mineral-dayscreen-spf-30-global?variant=54870451323252</t>
         </is>
       </c>
       <c r="L10" s="2">
@@ -1083,12 +1085,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MB003659</t>
+          <t>MB002883</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Calming Barrier Mask: máscara calmante de centella, 10 unidades</t>
+          <t>Bojagi: tecido tradicional coreano para embrulhar presentes · Calm Blue</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1097,7 +1099,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>182.9</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -1106,26 +1108,26 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Calming Barrier Mask</t>
+          <t>Bojagi</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>18 mL / 0.60 FL. OZ. (10 Sheets)</t>
+          <t>Olive</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I11" s="4" t="n"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/calming-barrier-sheet-mask-global</t>
+          <t>https://beautyofjoseon.com/products/bojagi?variant=40739062481061</t>
         </is>
       </c>
       <c r="L11" s="2">
@@ -1140,12 +1142,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MB003681</t>
+          <t>MB002882</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Duo Revive: sérum para olhos + hidratante firmador com retinol</t>
+          <t>Bojagi: tecido tradicional coreano para embrulhar presentes · Maehwa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1154,7 +1156,7 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>298.9</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -1163,16 +1165,18 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revive Ritual Eye Duo</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>Bojagi</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Olive</t>
+        </is>
+      </c>
       <c r="H12" s="4" t="n">
-        <v>27.75</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>37</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="I12" s="4" t="n"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>Esgotado</t>
@@ -1180,7 +1184,7 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-ritual-eye-duo-eu</t>
+          <t>https://beautyofjoseon.com/products/bojagi?variant=40739062481061</t>
         </is>
       </c>
       <c r="L12" s="2">
@@ -1195,12 +1199,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MB002838</t>
+          <t>MB002881</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dynasty Cream: creme hidratante de arroz e ginseng · 3.38 fl.oz.(100ml) 2-Pack</t>
+          <t>Bojagi: tecido tradicional coreano para embrulhar presentes · Olive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1209,7 +1213,7 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>525.9</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -1218,20 +1222,18 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dynasty Cream</t>
+          <t>Bojagi</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3.38 fl.oz.(100ml) 2-Pack</t>
+          <t>Olive</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>96</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="I13" s="4" t="n"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Esgotado</t>
@@ -1239,7 +1241,7 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/dynasty-cream?variant=55014470091124</t>
+          <t>https://beautyofjoseon.com/products/bojagi?variant=40739062481061</t>
         </is>
       </c>
       <c r="L13" s="2">
@@ -1254,12 +1256,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MB003661</t>
+          <t>MB003659</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ginseng Essence Water: essência de ginseng 150 ml</t>
+          <t>Calming Barrier Mask: máscara calmante de centella, 10 unidades</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1268,7 +1270,7 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>116.9</v>
+        <v>182.9</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -1277,16 +1279,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ginseng Essence Water</t>
+          <t>Calming Barrier Mask</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>150 ml (5.07 FL. OZ.)</t>
+          <t>18 mL / 0.60 FL. OZ. (10 Sheets)</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I14" s="4" t="n"/>
       <c r="J14" t="inlineStr">
@@ -1296,7 +1298,7 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/ginseng-essence-water</t>
+          <t>https://beautyofjoseon.com/products/calming-barrier-sheet-mask-global</t>
         </is>
       </c>
       <c r="L14" s="2">
@@ -1311,12 +1313,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MB003668</t>
+          <t>MB003681</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Glow Deep Serum: arroz + alfa-arbutina 30 ml</t>
+          <t>Duo Revive: sérum para olhos + hidratante firmador com retinol</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1325,7 +1327,7 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>110.9</v>
+        <v>298.9</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -1334,26 +1336,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Glow Deep Serum : Rice + Alpha-Arbutin</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>1.01 fl. oz.(30ml)</t>
-        </is>
-      </c>
+          <t>Revive Ritual Eye Duo</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="I15" s="4" t="n"/>
+        <v>27.75</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>37</v>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/glow-deep-serum-rice-alpha-arbutin?variant=51833689211252</t>
+          <t>https://beautyofjoseon.com/products/revive-ritual-eye-duo-eu</t>
         </is>
       </c>
       <c r="L15" s="2">
@@ -1368,12 +1368,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MB003657</t>
+          <t>MB002835</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Glow Replenishing Rice Milk: tônico de arroz 150 ml</t>
+          <t>Dynasty Cream: creme hidratante de arroz e ginseng · 1 fl.oz. (30ml)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>116.9</v>
+        <v>108.9</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -1391,20 +1391,18 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Glow Replenishing Rice Milk</t>
+          <t>Dynasty Cream</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>150 ml (5.07 FL. OZ.)</t>
+          <t>1 fl.oz. (30ml)</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>18</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I16" s="4" t="n"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1412,7 +1410,7 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/glow-replenishing-rice-milk</t>
+          <t>https://beautyofjoseon.com/products/dynasty-cream?variant=54217328460148</t>
         </is>
       </c>
       <c r="L16" s="2">
@@ -1427,12 +1425,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MB003670</t>
+          <t>MB002836</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Glow Serum: própolis + niacinamida 30 ml</t>
+          <t>Dynasty Cream: creme hidratante de arroz e ginseng · 1.69 fl.oz.(50ml)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1441,7 +1439,7 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>127.9</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -1450,20 +1448,18 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Glow Serum : Propolis + Niacinamide</t>
+          <t>Dynasty Cream</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.01 fl. oz.(30ml)</t>
+          <t>1.69 fl.oz.(50ml)</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>17</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="I17" s="4" t="n"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1471,7 +1467,7 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/glow-serum-propolis-niacinamide?variant=51833681772916</t>
+          <t>https://beautyofjoseon.com/products/dynasty-cream?variant=43222120759461</t>
         </is>
       </c>
       <c r="L17" s="2">
@@ -1486,12 +1482,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MB003680</t>
+          <t>MB002837</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kit Revive Essentials: sérum para olhos, adesivos e hidratante firmador</t>
+          <t>Dynasty Cream: creme hidratante de arroz e ginseng · 3.38 fl.oz.(100ml)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1500,7 +1496,7 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>332.9</v>
+        <v>291.9</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
@@ -1509,15 +1505,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revive Essentials Set</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Dynasty Cream</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>3.38 fl.oz.(100ml)</t>
+        </is>
+      </c>
       <c r="H18" s="4" t="n">
-        <v>45.75</v>
+        <v>32</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-essentials-set-global</t>
+          <t>https://beautyofjoseon.com/products/dynasty-cream?variant=43222120792229</t>
         </is>
       </c>
       <c r="L18" s="2">
@@ -1541,12 +1541,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MB003667</t>
+          <t>MB002838</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Light On Serum: centella + vitamina C 30 ml</t>
+          <t>Dynasty Cream: creme hidratante de arroz e ginseng · 3.38 fl.oz.(100ml) 2-Pack</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>92.90000000000001</v>
+        <v>525.9</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -1564,26 +1564,28 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Light On Serum : Centella + Vita C</t>
+          <t>Dynasty Cream</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>30 ml (1.01 FL. OZ.)</t>
+          <t>3.38 fl.oz.(100ml) 2-Pack</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="I19" s="4" t="n"/>
+        <v>72</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>96</v>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/light-on-serum-centella-vita-c</t>
+          <t>https://beautyofjoseon.com/products/dynasty-cream?variant=55014470091124</t>
         </is>
       </c>
       <c r="L19" s="2">
@@ -1598,12 +1600,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MB003666</t>
+          <t>MB002830</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Red Bean Water Gel: hidratante em gel de feijão vermelho 100 ml</t>
+          <t>Ginseng Cleansing Oil</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1612,7 +1614,7 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>104.9</v>
+        <v>144.9</v>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
@@ -1621,20 +1623,18 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Red Bean Water Gel</t>
+          <t>Ginseng Cleansing Oil</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>100 ml (3.38 FL. OZ.)</t>
+          <t>210 ml (7.10 FL. OZ.)</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>18</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I20" s="4" t="n"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/red-bean-water-gel</t>
+          <t>https://beautyofjoseon.com/products/ginseng-cleansing-oil</t>
         </is>
       </c>
       <c r="L20" s="2">
@@ -1657,12 +1657,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MB003669</t>
+          <t>MB003661</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Revive Serum: ginseng + mucina de caracol 30 ml</t>
+          <t>Ginseng Essence Water: essência de ginseng 150 ml</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>110.9</v>
+        <v>116.9</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
@@ -1680,20 +1680,18 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revive Eye Serum : Ginseng + Retinal</t>
+          <t>Ginseng Essence Water</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>30ML X 2-PACK</t>
+          <t>150 ml (5.07 FL. OZ.)</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>34</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I21" s="4" t="n"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1701,7 +1699,7 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
+          <t>https://beautyofjoseon.com/products/ginseng-essence-water</t>
         </is>
       </c>
       <c r="L21" s="2">
@@ -1716,12 +1714,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MB003682</t>
+          <t>MB003668</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Revive Under Eye Patch: adesivos para olhos de ginseng + retinal, 60 unidades</t>
+          <t>Glow Deep Serum: arroz + alfa-arbutina 30 ml</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1730,7 +1728,7 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>144.9</v>
+        <v>110.9</v>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
@@ -1739,16 +1737,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revive Under Eye Patch: Ginseng + Retinal</t>
+          <t>Glow Deep Serum : Rice + Alpha-Arbutin</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>100 g / 3.52 OZ. (60 Patches)</t>
+          <t>1.01 fl. oz.(30ml)</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I22" s="4" t="n"/>
       <c r="J22" t="inlineStr">
@@ -1758,7 +1756,7 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-under-eye-patch-global</t>
+          <t>https://beautyofjoseon.com/products/glow-deep-serum-rice-alpha-arbutin?variant=51833689211252</t>
         </is>
       </c>
       <c r="L22" s="2">
@@ -1773,12 +1771,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MB003693</t>
+          <t>MB003657</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Trio Red Bean para Poros: sérum, máscara e gel hidratante</t>
+          <t>Glow Replenishing Rice Milk: tônico de arroz 150 ml</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1787,7 +1785,7 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>400.9</v>
+        <v>116.9</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -1796,22 +1794,28 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Red Bean Pore Care Trio</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>Glow Replenishing Rice Milk</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>150 ml (5.07 FL. OZ.)</t>
+        </is>
+      </c>
       <c r="H23" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="I23" s="4" t="n"/>
+        <v>15.3</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>18</v>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/red-bean-pore-care-trio-eu</t>
+          <t>https://beautyofjoseon.com/products/glow-replenishing-rice-milk</t>
         </is>
       </c>
       <c r="L23" s="2">
@@ -1826,21 +1830,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MB003696</t>
+          <t>MB003670</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Hydra Shield FPS 50+: protetor solar para o corpo 150 ml</t>
+          <t>Glow Serum: própolis + niacinamida 30 ml</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>181.9</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -1849,26 +1853,28 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hydra Shield Body Sun Lotion SPF 50+</t>
+          <t>Glow Serum : Propolis + Niacinamide</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>150 ml (5.07 FL. OZ.)</t>
+          <t>1.01 fl. oz.(30ml)</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I24" s="4" t="n"/>
+        <v>15.3</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>17</v>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/hydra-shield-body-sun-lotion-spf-50-eu</t>
+          <t>https://beautyofjoseon.com/products/glow-serum-propolis-niacinamide?variant=51833681772916</t>
         </is>
       </c>
       <c r="L24" s="2">
@@ -1883,21 +1889,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MB004038</t>
+          <t>MB002812</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Relief Sun Aqua-Fresh FPS 50+ PA++++: protetor solar de arroz + B5, kit com 2 de 50 ml</t>
+          <t>Hanbok Scrunchie: elástico de cabelo de tecido em dois tons · Honey Green</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>213.9</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -1906,26 +1912,26 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Relief Sun Aqua-Fresh : Rice + B5  (SPF50+ PA++++)</t>
+          <t>Hanbok Scrunchie</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1-Pack</t>
+          <t>Orchid pink</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I25" s="4" t="n"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-aqua-fresh-rice-b5-spf50-pa-uk?variant=52419629646196</t>
+          <t>https://beautyofjoseon.com/products/hanbok-scrunchie?variant=43160500895909</t>
         </is>
       </c>
       <c r="L25" s="2">
@@ -1940,21 +1946,21 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MB003646</t>
+          <t>MB002811</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Relief Sun: Rice + Probiotics (SPF 50+ PA++++)</t>
+          <t>Hanbok Scrunchie: elástico de cabelo de tecido em dois tons · Orchid pink</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>137.9</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
@@ -1963,26 +1969,26 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
+          <t>Hanbok Scrunchie</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1-Pack</t>
+          <t>Orchid pink</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I26" s="4" t="n"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
+          <t>https://beautyofjoseon.com/products/hanbok-scrunchie?variant=43160500895909</t>
         </is>
       </c>
       <c r="L26" s="2">
@@ -1997,21 +2003,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MB003658</t>
+          <t>MB002801</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JELLOSKIN: creme de massagem para rosto e corpo</t>
+          <t>Kit Night-Reset: gel de limpeza de ameixa verde + Dynasty Cream 50 ml</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>305.9</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
@@ -2020,20 +2026,14 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JELLOSKIN Massage Cream For Face and Body</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>1-Pack</t>
-        </is>
-      </c>
+          <t>Night-Reset Dewy Finish Kit</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" s="4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>25</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="I27" s="4" t="n"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Esgotado</t>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/jelloskin-massage-cream-for-face-and-body</t>
+          <t>https://beautyofjoseon.com/products/night-restore-dewy-finish-night-skincare-set</t>
         </is>
       </c>
       <c r="L27" s="2">
@@ -2056,21 +2056,21 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MB003643</t>
+          <t>MB003680</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Relief Sun Aqua-Fresh Sunscreen: Rice + B5 (SPF 50+ PA++++)</t>
+          <t>Kit Revive Essentials: sérum para olhos, adesivos e hidratante firmador</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>137.9</v>
+        <v>332.9</v>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
@@ -2079,24 +2079,24 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Relief Sun Duo : Original + Aqua-Fresh</t>
+          <t>Revive Essentials Set</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" s="4" t="n">
-        <v>29.25</v>
+        <v>45.75</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-duo-original-aqua-fresh-uk</t>
+          <t>https://beautyofjoseon.com/products/revive-essentials-set-global</t>
         </is>
       </c>
       <c r="L28" s="2">
@@ -2111,21 +2111,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MB002785</t>
+          <t>MB002831</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Relief Sun: Arroz + Probióticos (FPS 50+ PA++++) · 1-Pack</t>
+          <t>Kit Ritual Glow: rotina completa de 6 passos, do sabonete ao protetor</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>999.99</v>
+        <v>968.9</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
@@ -2134,26 +2134,22 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>1-Pack</t>
-        </is>
-      </c>
+          <t>Rice Glow Ritual Set</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" s="4" t="n">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="I29" s="4" t="n"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
+          <t>https://beautyofjoseon.com/products/rice-glow-ritual-radiant-skincare-set-global</t>
         </is>
       </c>
       <c r="L29" s="2">
@@ -2168,21 +2164,21 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MB002808</t>
+          <t>MB002767</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sérum Light On: Centella + Vitamina C</t>
+          <t>Kit Sun-Cleanse: Relief Sun FPS 50+ + gel de limpeza de ameixa verde</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>92.90000000000001</v>
+        <v>254.9</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
@@ -2191,26 +2187,22 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Light On Serum : Centella + Vita C</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>30 ml (1.01 FL. OZ.)</t>
-        </is>
-      </c>
+          <t>Sun-Cleanse Daily Defense Set</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" s="4" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="I30" s="4" t="n"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/light-on-serum-centella-vita-c</t>
+          <t>https://beautyofjoseon.com/products/sun-cleanse-daily-shield-cleanser-sunscreen-set</t>
         </is>
       </c>
       <c r="L30" s="2">
@@ -2225,12 +2217,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MB003677</t>
+          <t>MB003667</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Duo Relief Sun Original + Aqua-Fresh FPS 50+ PA++++: dupla de protetores solares 2 x 50 ml</t>
+          <t>Light On Serum: centella + vitamina C 30 ml</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2239,33 +2231,35 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>212.9</v>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>92.90000000000001</v>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Relief Sun Duo : Original + Aqua-Fresh</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Light On Serum : Centella + Vita C</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>30 ml (1.01 FL. OZ.)</t>
+        </is>
+      </c>
       <c r="H31" s="4" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>39</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I31" s="4" t="n"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-duo-original-aqua-fresh-uk</t>
+          <t>https://beautyofjoseon.com/products/light-on-serum-centella-vita-c</t>
         </is>
       </c>
       <c r="L31" s="2">
@@ -2280,12 +2274,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MB003699</t>
+          <t>MB002804</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Glow Sun Stick FPS 50: protetor solar em bastão 14 g</t>
+          <t>Lucky Pouch: nécessaire de seda inspirada no hanbok 15,5 x 21 cm · Maehwa Pink</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2294,35 +2288,35 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>65.90000000000001</v>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Glow Sun Stick</t>
+          <t>Lucky Pouch</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>14 g (0.49 OZ.)</t>
+          <t>Olive</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I32" s="4" t="n"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/glow-sun-stick-sunscreen-stick</t>
+          <t>https://beautyofjoseon.com/products/lucky-pouch?variant=40739135783077</t>
         </is>
       </c>
       <c r="L32" s="2">
@@ -2337,12 +2331,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MB003653</t>
+          <t>MB002805</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Duo Glow de Arroz: Rice Milk + máscara de arroz com mel</t>
+          <t>Lucky Pouch: nécessaire de seda inspirada no hanbok 15,5 x 21 cm · Olive</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2351,33 +2345,35 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>170.9</v>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>65.90000000000001</v>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Guard Your Glow Duo</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>Lucky Pouch</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Olive</t>
+        </is>
+      </c>
       <c r="H33" s="4" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>54</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="I33" s="4" t="n"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/protect-your-glow-duo-global</t>
+          <t>https://beautyofjoseon.com/products/lucky-pouch?variant=40739135783077</t>
         </is>
       </c>
       <c r="L33" s="2">
@@ -2392,12 +2388,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MB002772</t>
+          <t>MB003666</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Duo Revive Autocuidado</t>
+          <t>Red Bean Water Gel: hidratante em gel de feijão vermelho 100 ml</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2406,33 +2402,37 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>193.9</v>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>104.9</v>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revive Ritual Eye Duo</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>Red Bean Water Gel</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>100 ml (3.38 FL. OZ.)</t>
+        </is>
+      </c>
       <c r="H34" s="4" t="n">
-        <v>27.75</v>
+        <v>14.4</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-ritual-eye-duo-eu</t>
+          <t>https://beautyofjoseon.com/products/red-bean-water-gel</t>
         </is>
       </c>
       <c r="L34" s="2">
@@ -2447,12 +2447,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MB003645</t>
+          <t>MB003669</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Duo Ritual Revive para os Olhos: sérum + adesivos</t>
+          <t>Revive Serum: ginseng + mucina de caracol 30 ml</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2461,33 +2461,37 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>201.9</v>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>110.9</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revive Ritual Eye Duo</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>Revive Eye Serum : Ginseng + Retinal</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>30ML X 2-PACK</t>
+        </is>
+      </c>
       <c r="H35" s="4" t="n">
-        <v>27.75</v>
+        <v>25.5</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-ritual-eye-duo-eu</t>
+          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
         </is>
       </c>
       <c r="L35" s="2">
@@ -2502,35 +2506,35 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MB003692</t>
+          <t>MB003682</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Dayscreen FPS 30: hidratante com protetor solar 60 ml</t>
+          <t>Revive Under Eye Patch: adesivos para olhos de ginseng + retinal, 60 unidades</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>104.9</v>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>144.9</v>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dayscreen Moisturizer SPF 30</t>
+          <t>Revive Under Eye Patch: Ginseng + Retinal</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1-Pack</t>
+          <t>100 g / 3.52 OZ. (60 Patches)</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
@@ -2539,12 +2543,12 @@
       <c r="I36" s="4" t="n"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/dayscreen-moisturizer-sunscreen-global?variant=54406380159348</t>
+          <t>https://beautyofjoseon.com/products/revive-under-eye-patch-global</t>
         </is>
       </c>
       <c r="L36" s="2">
@@ -2559,39 +2563,35 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MB003679</t>
+          <t>MB003693</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Relief Sun FPS 50+ PA++++: protetor solar de arroz + probióticos 50 ml</t>
+          <t>Trio Red Bean para Poros: sérum, máscara e gel hidratante</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>400.9</v>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>1-Pack</t>
-        </is>
-      </c>
+          <t>Red Bean Pore Care Trio</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" s="4" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="I37" s="4" t="n"/>
       <c r="J37" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
+          <t>https://beautyofjoseon.com/products/red-bean-pore-care-trio-eu</t>
         </is>
       </c>
       <c r="L37" s="2">
@@ -2616,12 +2616,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MB004030</t>
+          <t>MB003696</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Relief Sun FPS 50+ PA++++: protetor solar de arroz, kit com 2 de 50 ml</t>
+          <t>Beauty of Joseon Hydra Shield FPS 50+: protetor solar para o corpo 150 ml</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2630,25 +2630,25 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>213.9</v>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>181.9</v>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
+          <t>Hydra Shield Body Sun Lotion SPF 50+</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1-Pack</t>
+          <t>150 ml (5.07 FL. OZ.)</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I38" s="4" t="n"/>
       <c r="J38" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
+          <t>https://beautyofjoseon.com/products/hydra-shield-body-sun-lotion-spf-50-eu</t>
         </is>
       </c>
       <c r="L38" s="2">
@@ -2673,12 +2673,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MB003663</t>
+          <t>MB004038</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bálsamo de Limpeza Radiance 100 ml</t>
+          <t>Beauty of Joseon Relief Sun Aqua-Fresh FPS 50+ PA++++: protetor solar de arroz + B5, kit com 2 de 50 ml</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2687,21 +2687,21 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>213.9</v>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Radiance Cleansing Balm</t>
+          <t>Relief Sun Aqua-Fresh : Rice + B5  (SPF50+ PA++++)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>100 ml (3.38 FL. OZ.)</t>
+          <t>1-Pack</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
@@ -2710,12 +2710,12 @@
       <c r="I39" s="4" t="n"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/radiance-cleansing-balm</t>
+          <t>https://beautyofjoseon.com/products/relief-sun-aqua-fresh-rice-b5-spf50-pa-uk?variant=52419629646196</t>
         </is>
       </c>
       <c r="L39" s="2">
@@ -2730,12 +2730,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MB003685</t>
+          <t>MB003646</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Creme Dynasty</t>
+          <t>Beauty of Joseon Relief Sun: Rice + Probiotics (SPF 50+ PA++++)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2744,35 +2744,35 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>174.9</v>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>137.9</v>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dynasty Cream</t>
+          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1 fl.oz. (30ml)</t>
+          <t>1-Pack</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I40" s="4" t="n"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/dynasty-cream?variant=54217328460148</t>
+          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
         </is>
       </c>
       <c r="L40" s="2">
@@ -2787,12 +2787,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MB003651</t>
+          <t>MB002781</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Duo Pele de Vidro: Glow Serum + Dynasty Cream</t>
+          <t>Duo Relief Sun: Original + Aqua-Fresh</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2801,23 +2801,25 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>194.9</v>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>212.9</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pick + Mix Serum Duo</t>
+          <t>Relief Sun Duo : Original + Aqua-Fresh</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="I41" s="4" t="n"/>
+        <v>29.25</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>39</v>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>Esgotado</t>
@@ -2825,7 +2827,7 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/pick-and-mix-serum-duo-skincare-set-eu-uk</t>
+          <t>https://beautyofjoseon.com/products/relief-sun-duo-original-aqua-fresh-uk</t>
         </is>
       </c>
       <c r="L41" s="2">
@@ -2840,12 +2842,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MB003687</t>
+          <t>MB002822</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Paleta Hanbang: kit com os 4 séruns da marca</t>
+          <t>Glow Deep Serum: Arroz + Alfa-Arbutin · 1.01 fl. oz.(30ml)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2854,33 +2856,35 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>495.9</v>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>999.99</v>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hanbang Serum Discovery Kit</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>Glow Deep Serum : Rice + Alpha-Arbutin</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1.01 fl. oz.(30ml)</t>
+        </is>
+      </c>
       <c r="H42" s="4" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>27</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I42" s="4" t="n"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/hanbang-serum-discovery-kit</t>
+          <t>https://beautyofjoseon.com/products/glow-deep-serum-rice-alpha-arbutin?variant=51833689211252</t>
         </is>
       </c>
       <c r="L42" s="2">
@@ -2895,12 +2899,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MB003647</t>
+          <t>MB002823</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sérum para Olhos Revive: Ginseng + Retina</t>
+          <t>Glow Deep Serum: Arroz + Alfa-Arbutin · 2.03 fl. oz.(60ml)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2908,26 +2912,24 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n">
-        <v>160.9</v>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revive Eye Serum : Ginseng + Retinal</t>
+          <t>Glow Deep Serum : Rice + Alpha-Arbutin</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>30ML X 2-PACK</t>
+          <t>2.03 fl. oz.(60ml)</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>25.5</v>
+        <v>27.2</v>
       </c>
       <c r="I43" s="4" t="n">
         <v>34</v>
@@ -2939,7 +2941,7 @@
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
+          <t>https://beautyofjoseon.com/products/glow-deep-serum-rice-alpha-arbutin?variant=51833689244020</t>
         </is>
       </c>
       <c r="L43" s="2">
@@ -2954,12 +2956,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MB003683</t>
+          <t>MB003658</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sérum para Olhos Revive: ginseng + retinal 30 ml</t>
+          <t>JELLOSKIN: creme de massagem para rosto e corpo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2968,37 +2970,37 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>160.9</v>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>90.90000000000001</v>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revive Eye Serum : Ginseng + Retinal</t>
+          <t>JELLOSKIN Massage Cream For Face and Body</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>30ML X 2-PACK</t>
+          <t>1-Pack</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>25.5</v>
+        <v>12.5</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
+          <t>https://beautyofjoseon.com/products/jelloskin-massage-cream-for-face-and-body</t>
         </is>
       </c>
       <c r="L44" s="2">
@@ -3013,12 +3015,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MB003662</t>
+          <t>MB003643</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Óleo de Limpeza de Ginseng 210 ml</t>
+          <t>Relief Sun Aqua-Fresh Sunscreen: Rice + B5 (SPF 50+ PA++++)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3027,35 +3029,33 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>137.9</v>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ginseng Cleansing Oil</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>210 ml (7.10 FL. OZ.)</t>
-        </is>
-      </c>
+          <t>Relief Sun Duo : Original + Aqua-Fresh</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I45" s="4" t="n"/>
+        <v>29.25</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>39</v>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/ginseng-cleansing-oil</t>
+          <t>https://beautyofjoseon.com/products/relief-sun-duo-original-aqua-fresh-uk</t>
         </is>
       </c>
       <c r="L45" s="2">
@@ -3070,41 +3070,67 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MB003695</t>
+          <t>MB002782</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Duo Radiant + Dewy FPS 50 e FPS 50+: Glow Sun Stick 14 g + Hydra Shield protetor corporal 150 ml</t>
+          <t>Relief Sun Aqua-Fresh: Arroz + B5 (FPS 50+ PA++++) · 1-Pack</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>319.9</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="n"/>
-      <c r="L46" s="2" t="n"/>
-      <c r="M46" s="6" t="n"/>
+        <v>999.99</v>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Relief Sun Duo : Original + Aqua-Fresh</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" s="4" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/relief-sun-duo-original-aqua-fresh-uk</t>
+        </is>
+      </c>
+      <c r="L46" s="2">
+        <f>ROUND(H46*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M46" s="6">
+        <f>IF(OR(D46="",L46=""),"",D46/L46-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MB003648</t>
+          <t>MB002783</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bastão Protetor Solar Matte: Artemísia + Camélia (FPS 50+ PA++++)</t>
+          <t>Relief Sun Aqua-Fresh: Arroz + B5 (FPS 50+ PA++++) · 2-Pack</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3112,28 +3138,52 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="D47" s="2" t="n">
-        <v>163.9</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="n"/>
-      <c r="I47" s="4" t="n"/>
-      <c r="L47" s="2" t="n"/>
-      <c r="M47" s="6" t="n"/>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Relief Sun Duo : Original + Aqua-Fresh</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" s="4" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/relief-sun-duo-original-aqua-fresh-uk</t>
+        </is>
+      </c>
+      <c r="L47" s="2">
+        <f>ROUND(H47*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M47" s="6">
+        <f>IF(OR(D47="",L47=""),"",D47/L47-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MB003674</t>
+          <t>MB002785</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Beauty of Joseon All Day Sun Duo FPS 50+ PA++++: Relief Sun 50 ml + Matte Sun Stick 18 g</t>
+          <t>Relief Sun: Arroz + Probióticos (FPS 50+ PA++++) · 1-Pack</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3142,27 +3192,55 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>196.9</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="n"/>
+        <v>999.99</v>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1-Pack</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>18</v>
+      </c>
       <c r="I48" s="4" t="n"/>
-      <c r="L48" s="2" t="n"/>
-      <c r="M48" s="6" t="n"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
+        </is>
+      </c>
+      <c r="L48" s="2">
+        <f>ROUND(H48*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M48" s="6">
+        <f>IF(OR(D48="",L48=""),"",D48/L48-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MB003697</t>
+          <t>MB002786</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Comfort Protection FPS 40: protetor solar mineral para o corpo 150 ml</t>
+          <t>Relief Sun: Arroz + Probióticos (FPS 50+ PA++++) · 2-Pack</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3170,28 +3248,54 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n">
-        <v>181.9</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="n"/>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1-Pack</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>18</v>
+      </c>
       <c r="I49" s="4" t="n"/>
-      <c r="L49" s="2" t="n"/>
-      <c r="M49" s="6" t="n"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
+        </is>
+      </c>
+      <c r="L49" s="2">
+        <f>ROUND(H49*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M49" s="6">
+        <f>IF(OR(D49="",L49=""),"",D49/L49-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MB003671</t>
+          <t>MB002808</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Daily Tinted Fluid FPS 30: protetor solar mineral com cor</t>
+          <t>Sérum Light On: Centella + Vitamina C</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3200,27 +3304,55 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="n"/>
+        <v>92.90000000000001</v>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Light On Serum : Centella + Vita C</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>30 ml (1.01 FL. OZ.)</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>17</v>
+      </c>
       <c r="I50" s="4" t="n"/>
-      <c r="L50" s="2" t="n"/>
-      <c r="M50" s="6" t="n"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/light-on-serum-centella-vita-c</t>
+        </is>
+      </c>
+      <c r="L50" s="2">
+        <f>ROUND(H50*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M50" s="6">
+        <f>IF(OR(D50="",L50=""),"",D50/L50-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MB002843</t>
+          <t>MB002770</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Day Dew Mini FPS 50: protetor solar 10 ml</t>
+          <t>Sérum Revive: Ginseng + Muco de Caracol · 1.01 fl. oz.(30ml)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3229,27 +3361,57 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>104.9</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="n"/>
-      <c r="I51" s="4" t="n"/>
-      <c r="L51" s="2" t="n"/>
-      <c r="M51" s="6" t="n"/>
+        <v>92.90000000000001</v>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Revive Eye Serum : Ginseng + Retinal</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>30ML X 2-PACK</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
+        </is>
+      </c>
+      <c r="L51" s="2">
+        <f>ROUND(H51*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M51" s="6">
+        <f>IF(OR(D51="",L51=""),"",D51/L51-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MB003694</t>
+          <t>MB002771</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Duo Relax + Relief FPS 50+ PA++++ e FPS 40: Relief Sun 50 ml + protetor corporal mineral 150 ml</t>
+          <t>Sérum Revive: Ginseng + Muco de Caracol · 2.03 fl. oz.(60ml)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3258,85 +3420,167 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>319.9</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="n"/>
-      <c r="I52" s="4" t="n"/>
-      <c r="L52" s="2" t="n"/>
-      <c r="M52" s="6" t="n"/>
+        <v>160.9</v>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Revive Serum : Ginseng + Snail Mucin</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2.03 fl. oz.(60ml)</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/revive-serum-ginseng-snail-mucin?variant=51833686065524</t>
+        </is>
+      </c>
+      <c r="L52" s="2">
+        <f>ROUND(H52*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M52" s="6">
+        <f>IF(OR(D52="",L52=""),"",D52/L52-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MB003675</t>
+          <t>MB002834</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Ginseng Moist Sun Serum FPS 50+ PA++++: sérum solar hidratante</t>
+          <t>Dynasty Cream Mini: creme hidratante de arroz e ginseng 10 ml</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>112.9</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="n"/>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Dynasty Cream</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1 fl.oz. (30ml)</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="I53" s="4" t="n"/>
-      <c r="L53" s="2" t="n"/>
-      <c r="M53" s="6" t="n"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/dynasty-cream?variant=54217328460148</t>
+        </is>
+      </c>
+      <c r="L53" s="2">
+        <f>ROUND(H53*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M53" s="6">
+        <f>IF(OR(D53="",L53=""),"",D53/L53-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MB002873</t>
+          <t>MB002833</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Protetor Solar Daily Relief FPS 40 · 1-Pack</t>
+          <t>Kit Dynasty Triple Barrier Lock: gel de limpeza, Dynasty Cream e Relief Sun</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>195.9</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="n"/>
+        <v>452.9</v>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Dynasty Triple Barrier Lock</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" s="4" t="n">
+        <v>62</v>
+      </c>
       <c r="I54" s="4" t="n"/>
-      <c r="L54" s="2" t="n"/>
-      <c r="M54" s="6" t="n"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/dynasty-triple-barrier-lock-skincare-routine-set</t>
+        </is>
+      </c>
+      <c r="L54" s="2">
+        <f>ROUND(H54*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M54" s="6">
+        <f>IF(OR(D54="",L54=""),"",D54/L54-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MB002874</t>
+          <t>MB002807</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Protetor Solar Daily Relief FPS 40 · 2-Pack</t>
+          <t>Light On Serum Mini: centella + vitamina C 10 ml</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3345,27 +3589,55 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>195.9</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="n"/>
+        <v>999.99</v>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Light On Serum : Centella + Vita C</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>30 ml (1.01 FL. OZ.)</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>17</v>
+      </c>
       <c r="I55" s="4" t="n"/>
-      <c r="L55" s="2" t="n"/>
-      <c r="M55" s="6" t="n"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/light-on-serum-centella-vita-c</t>
+        </is>
+      </c>
+      <c r="L55" s="2">
+        <f>ROUND(H55*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M55" s="6">
+        <f>IF(OR(D55="",L55=""),"",D55/L55-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MB003644</t>
+          <t>MB002775</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Beauty of Joseon: Filtro Solar com Arroz + Probióticos (FPS 50+ PA++++)</t>
+          <t>Sérum para Olhos Revive Mini: ginseng + retinal 10 ml</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3374,317 +3646,609 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="n"/>
-      <c r="I56" s="4" t="n"/>
-      <c r="L56" s="2" t="n"/>
-      <c r="M56" s="6" t="n"/>
+        <v>26.9</v>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Revive Eye Serum : Ginseng + Retinal</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>30ML X 2-PACK</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
+        </is>
+      </c>
+      <c r="L56" s="2">
+        <f>ROUND(H56*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M56" s="6">
+        <f>IF(OR(D56="",L56=""),"",D56/L56-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MB002849</t>
+          <t>MB002824</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · LN110 / 50ml</t>
+          <t>Arroz Carregador Duo Glow</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="n"/>
-      <c r="I57" s="4" t="n"/>
-      <c r="L57" s="2" t="n"/>
-      <c r="M57" s="6" t="n"/>
+        <v>169.9</v>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Guard Your Glow Duo</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" s="4" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/protect-your-glow-duo-global</t>
+        </is>
+      </c>
+      <c r="L57" s="2">
+        <f>ROUND(H57*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M57" s="6">
+        <f>IF(OR(D57="",L57=""),"",D57/L57-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MB002850</t>
+          <t>MB003677</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · LN110 / 7ml</t>
+          <t>Beauty of Joseon Duo Relief Sun Original + Aqua-Fresh FPS 50+ PA++++: dupla de protetores solares 2 x 50 ml</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="n"/>
-      <c r="I58" s="4" t="n"/>
-      <c r="L58" s="2" t="n"/>
-      <c r="M58" s="6" t="n"/>
+        <v>212.9</v>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Relief Sun Duo : Original + Aqua-Fresh</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" s="4" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/relief-sun-duo-original-aqua-fresh-uk</t>
+        </is>
+      </c>
+      <c r="L58" s="2">
+        <f>ROUND(H58*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M58" s="6">
+        <f>IF(OR(D58="",L58=""),"",D58/L58-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MB002847</t>
+          <t>MB003699</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · LP100 / 50ml</t>
+          <t>Beauty of Joseon Glow Sun Stick FPS 50: protetor solar em bastão 14 g</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="n"/>
+        <v>144.9</v>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Glow Sun Stick</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>14 g (0.49 OZ.)</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="I59" s="4" t="n"/>
-      <c r="L59" s="2" t="n"/>
-      <c r="M59" s="6" t="n"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/glow-sun-stick-sunscreen-stick</t>
+        </is>
+      </c>
+      <c r="L59" s="2">
+        <f>ROUND(H59*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M59" s="6">
+        <f>IF(OR(D59="",L59=""),"",D59/L59-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MB002848</t>
+          <t>MB002784</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · LP100 / 7ml</t>
+          <t>Beauty of Joseon Relief Sun Aqua-Fresh Mini FPS 50+ PA++++: protetor solar de arroz + B5 10 ml</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="n"/>
+        <v>26.9</v>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Relief Sun Aqua-Fresh : Rice + B5  (SPF50+ PA++++)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1-Pack</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>19</v>
+      </c>
       <c r="I60" s="4" t="n"/>
-      <c r="L60" s="2" t="n"/>
-      <c r="M60" s="6" t="n"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/relief-sun-aqua-fresh-rice-b5-spf50-pa-uk?variant=52419629646196</t>
+        </is>
+      </c>
+      <c r="L60" s="2">
+        <f>ROUND(H60*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M60" s="6">
+        <f>IF(OR(D60="",L60=""),"",D60/L60-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MB002851</t>
+          <t>MB003653</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · LP110 / 50ml</t>
+          <t>Duo Glow de Arroz: Rice Milk + máscara de arroz com mel</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="n"/>
-      <c r="I61" s="4" t="n"/>
-      <c r="L61" s="2" t="n"/>
-      <c r="M61" s="6" t="n"/>
+        <v>170.9</v>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Guard Your Glow Duo</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" s="4" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/protect-your-glow-duo-global</t>
+        </is>
+      </c>
+      <c r="L61" s="2">
+        <f>ROUND(H61*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M61" s="6">
+        <f>IF(OR(D61="",L61=""),"",D61/L61-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MB002852</t>
+          <t>MB002772</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · LP110 / 7ml</t>
+          <t>Duo Revive Autocuidado</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="n"/>
-      <c r="I62" s="4" t="n"/>
-      <c r="L62" s="2" t="n"/>
-      <c r="M62" s="6" t="n"/>
+        <v>193.9</v>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Revive Ritual Eye Duo</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" s="4" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/revive-ritual-eye-duo-eu</t>
+        </is>
+      </c>
+      <c r="L62" s="2">
+        <f>ROUND(H62*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M62" s="6">
+        <f>IF(OR(D62="",L62=""),"",D62/L62-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MB002860</t>
+          <t>MB003645</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · MN230 / 7ml</t>
+          <t>Duo Ritual Revive para os Olhos: sérum + adesivos</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="n"/>
-      <c r="I63" s="4" t="n"/>
-      <c r="L63" s="2" t="n"/>
-      <c r="M63" s="6" t="n"/>
+        <v>201.9</v>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Revive Ritual Eye Duo</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" s="4" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/revive-ritual-eye-duo-eu</t>
+        </is>
+      </c>
+      <c r="L63" s="2">
+        <f>ROUND(H63*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M63" s="6">
+        <f>IF(OR(D63="",L63=""),"",D63/L63-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MB002853</t>
+          <t>MB002797</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · MP200 / 50ml</t>
+          <t>Gua Sha de Porcelana: ferramenta de massagem para rosto e corpo</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="n"/>
+        <v>123.9</v>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Porcelain Gwalsa (Gua Sha)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" s="4" t="n">
+        <v>17</v>
+      </c>
       <c r="I64" s="4" t="n"/>
-      <c r="L64" s="2" t="n"/>
-      <c r="M64" s="6" t="n"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/porcelain-gwalsa-guasha</t>
+        </is>
+      </c>
+      <c r="L64" s="2">
+        <f>ROUND(H64*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M64" s="6">
+        <f>IF(OR(D64="",L64=""),"",D64/L64-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MB002854</t>
+          <t>MB002827</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · MP200 / 7ml</t>
+          <t>Kit Presente Ginseng Ritual: essência, sérum e adesivos para olhos + espelho</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="n"/>
-      <c r="I65" s="4" t="n"/>
-      <c r="L65" s="2" t="n"/>
-      <c r="M65" s="6" t="n"/>
+        <v>327.9</v>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Ginseng Firming Ritual Set</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/ginseng-firming-ritual-ginseng-retinol-skincare-set</t>
+        </is>
+      </c>
+      <c r="L65" s="2">
+        <f>ROUND(H65*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M65" s="6">
+        <f>IF(OR(D65="",L65=""),"",D65/L65-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MB002857</t>
+          <t>MB002779</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · MY220 / 50ml</t>
+          <t>Kit Revive Essencial</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="n"/>
-      <c r="I66" s="4" t="n"/>
-      <c r="L66" s="2" t="n"/>
-      <c r="M66" s="6" t="n"/>
+        <v>332.9</v>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Revive Essentials Set</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" s="4" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/revive-essentials-set-global</t>
+        </is>
+      </c>
+      <c r="L66" s="2">
+        <f>ROUND(H66*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M66" s="6">
+        <f>IF(OR(D66="",L66=""),"",D66/L66-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MB003673</t>
+          <t>MB002844</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Duo Dia e Noite: Relief Sun FPS 50+ PA++++ + Dynasty Cream</t>
+          <t>Beauty of Joseon Day Dew FPS 50: protetor solar com ácido hialurônico e niacinamida 50 ml · 1-Pack</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3693,27 +4257,57 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>305.9</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="n"/>
-      <c r="I67" s="4" t="n"/>
-      <c r="L67" s="2" t="n"/>
-      <c r="M67" s="6" t="n"/>
+        <v>105.9</v>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Day Dew Sunscreen</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1-Pack</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I67" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/day-dew-sunscreen?variant=53692453814644</t>
+        </is>
+      </c>
+      <c r="L67" s="2">
+        <f>ROUND(H67*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M67" s="6">
+        <f>IF(OR(D67="",L67=""),"",D67/L67-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MB003652</t>
+          <t>MB002845</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Duo Dupla Limpeza: óleo de ginseng + gel de ameixa verde</t>
+          <t>Beauty of Joseon Day Dew FPS 50: protetor solar com ácido hialurônico e niacinamida 50 ml · 2-Pack</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3722,27 +4316,57 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>155.9</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="n"/>
-      <c r="I68" s="4" t="n"/>
-      <c r="L68" s="2" t="n"/>
-      <c r="M68" s="6" t="n"/>
+        <v>170.9</v>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Day Dew Sunscreen</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2-Pack</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/day-dew-sunscreen?variant=53692453847412</t>
+        </is>
+      </c>
+      <c r="L68" s="2">
+        <f>ROUND(H68*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M68" s="6">
+        <f>IF(OR(D68="",L68=""),"",D68/L68-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MB002872</t>
+          <t>MB003692</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Duo Escudo Diário e Hidratação Profunda</t>
+          <t>Beauty of Joseon Dayscreen FPS 30: hidratante com protetor solar 60 ml</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3751,27 +4375,55 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>999.99</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="n"/>
+        <v>104.9</v>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Dayscreen Moisturizer SPF 30</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1-Pack</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="I69" s="4" t="n"/>
-      <c r="L69" s="2" t="n"/>
-      <c r="M69" s="6" t="n"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/dayscreen-moisturizer-sunscreen-global?variant=54406380159348</t>
+        </is>
+      </c>
+      <c r="L69" s="2">
+        <f>ROUND(H69*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M69" s="6">
+        <f>IF(OR(D69="",L69=""),"",D69/L69-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MB002880</t>
+          <t>MB003679</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Duo Iluminador e Firmador</t>
+          <t>Beauty of Joseon Relief Sun FPS 50+ PA++++: protetor solar de arroz + probióticos 50 ml</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3780,27 +4432,55 @@
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>999.99</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="n"/>
+        <v>137.9</v>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1-Pack</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>18</v>
+      </c>
       <c r="I70" s="4" t="n"/>
-      <c r="L70" s="2" t="n"/>
-      <c r="M70" s="6" t="n"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
+        </is>
+      </c>
+      <c r="L70" s="2">
+        <f>ROUND(H70*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M70" s="6">
+        <f>IF(OR(D70="",L70=""),"",D70/L70-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MB003650</t>
+          <t>MB004030</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Duo Iluminador e Firmador: Light On Serum + Revive Eye Serum</t>
+          <t>Beauty of Joseon Relief Sun FPS 50+ PA++++: protetor solar de arroz, kit com 2 de 50 ml</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3809,27 +4489,55 @@
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>148.9</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="n"/>
+        <v>213.9</v>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1-Pack</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="n">
+        <v>18</v>
+      </c>
       <c r="I71" s="4" t="n"/>
-      <c r="L71" s="2" t="n"/>
-      <c r="M71" s="6" t="n"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
+        </is>
+      </c>
+      <c r="L71" s="2">
+        <f>ROUND(H71*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M71" s="6">
+        <f>IF(OR(D71="",L71=""),"",D71/L71-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MB003689</t>
+          <t>MB002780</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Duo Proteja o Seu Brilho: Glow Serum + Dayscreen FPS 30</t>
+          <t>Beauty of Joseon Relief Sun Mini FPS 50+ PA++++: protetor solar de arroz 10 ml</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3838,27 +4546,55 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>315.9</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="n"/>
+        <v>26.9</v>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Matte Sun Stick : Mugwort+Camelia (SPF 50+ PA++++)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1-Pack</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>19</v>
+      </c>
       <c r="I72" s="4" t="n"/>
-      <c r="L72" s="2" t="n"/>
-      <c r="M72" s="6" t="n"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/matte-sun-stick-mugwort-camelia-spf-50-pa-uk?variant=52419626303860</t>
+        </is>
+      </c>
+      <c r="L72" s="2">
+        <f>ROUND(H72*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M72" s="6">
+        <f>IF(OR(D72="",L72=""),"",D72/L72-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MB003688</t>
+          <t>MB003663</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Duo Proteção Diária e Hidratação Profunda: Dynasty Cream + Dayscreen FPS 30</t>
+          <t>Bálsamo de Limpeza Radiance 100 ml</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3867,27 +4603,55 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>256.9</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="n"/>
+        <v>82.90000000000001</v>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Radiance Cleansing Balm</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>100 ml (3.38 FL. OZ.)</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>19</v>
+      </c>
       <c r="I73" s="4" t="n"/>
-      <c r="L73" s="2" t="n"/>
-      <c r="M73" s="6" t="n"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/radiance-cleansing-balm</t>
+        </is>
+      </c>
+      <c r="L73" s="2">
+        <f>ROUND(H73*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M73" s="6">
+        <f>IF(OR(D73="",L73=""),"",D73/L73-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MB003654</t>
+          <t>MB003685</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Duo Refinador de Poros: máscaras de feijão vermelho e de arroz com mel</t>
+          <t>Creme Dynasty</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3896,27 +4660,55 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>180.9</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="n"/>
+        <v>174.9</v>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Dynasty Cream</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1 fl.oz. (30ml)</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="I74" s="4" t="n"/>
-      <c r="L74" s="2" t="n"/>
-      <c r="M74" s="6" t="n"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/dynasty-cream?variant=54217328460148</t>
+        </is>
+      </c>
+      <c r="L74" s="2">
+        <f>ROUND(H74*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M74" s="6">
+        <f>IF(OR(D74="",L74=""),"",D74/L74-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MB003642</t>
+          <t>MB002841</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Duo Revitalizante para os Olhos</t>
+          <t>Dayscreen Hidratante FPS 30 · 1-Pack</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3925,27 +4717,55 @@
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>201.9</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="n"/>
+        <v>999.99</v>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Dayscreen Moisturizer SPF 30</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1-Pack</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="I75" s="4" t="n"/>
-      <c r="L75" s="2" t="n"/>
-      <c r="M75" s="6" t="n"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/dayscreen-moisturizer-sunscreen-global?variant=54406380159348</t>
+        </is>
+      </c>
+      <c r="L75" s="2">
+        <f>ROUND(H75*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M75" s="6">
+        <f>IF(OR(D75="",L75=""),"",D75/L75-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MB002885</t>
+          <t>MB002842</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Duo de Protetor Solar para o Dia Todo</t>
+          <t>Dayscreen Hidratante FPS 30 · 2-Pack</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3956,25 +4776,53 @@
       <c r="D76" s="2" t="n">
         <v>999.99</v>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="n"/>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Dayscreen Moisturizer SPF 30</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2-Pack</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>40</v>
+      </c>
       <c r="I76" s="4" t="n"/>
-      <c r="L76" s="2" t="n"/>
-      <c r="M76" s="6" t="n"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/dayscreen-moisturizer-sunscreen-global?variant=54406380192116</t>
+        </is>
+      </c>
+      <c r="L76" s="2">
+        <f>ROUND(H76*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M76" s="6">
+        <f>IF(OR(D76="",L76=""),"",D76/L76-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MB002884</t>
+          <t>MB003651</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Gel Esfoliante Flor de Damasco</t>
+          <t>Duo Pele de Vidro: Glow Serum + Dynasty Cream</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3983,27 +4831,51 @@
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>999.99</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="n"/>
+        <v>194.9</v>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Pick + Mix Serum Duo</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" s="4" t="n">
+        <v>34</v>
+      </c>
       <c r="I77" s="4" t="n"/>
-      <c r="L77" s="2" t="n"/>
-      <c r="M77" s="6" t="n"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/pick-and-mix-serum-duo-skincare-set-eu-uk</t>
+        </is>
+      </c>
+      <c r="L77" s="2">
+        <f>ROUND(H77*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M77" s="6">
+        <f>IF(OR(D77="",L77=""),"",D77/L77-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MB003660</t>
+          <t>MB002773</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Gel Esfoliante Flor de Damasco 100 ml</t>
+          <t>Duo Ritual Revive para a Área dos Olhos</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4012,27 +4884,53 @@
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="n"/>
-      <c r="I78" s="4" t="n"/>
-      <c r="L78" s="2" t="n"/>
-      <c r="M78" s="6" t="n"/>
+        <v>201.9</v>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Revive Ritual Eye Duo</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" s="4" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/revive-ritual-eye-duo-eu</t>
+        </is>
+      </c>
+      <c r="L78" s="2">
+        <f>ROUND(H78*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M78" s="6">
+        <f>IF(OR(D78="",L78=""),"",D78/L78-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MB003664</t>
+          <t>MB002787</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Gel de Limpeza Refrescante de Ameixa Verde</t>
+          <t>Duo Solar Relax + Alívio</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4041,27 +4939,51 @@
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="n"/>
+        <v>319.9</v>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Relax + Relief SPF Duo</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" s="4" t="n">
+        <v>44</v>
+      </c>
       <c r="I79" s="4" t="n"/>
-      <c r="L79" s="2" t="n"/>
-      <c r="M79" s="6" t="n"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/relax-relief-spf-duo-eu</t>
+        </is>
+      </c>
+      <c r="L79" s="2">
+        <f>ROUND(H79*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M79" s="6">
+        <f>IF(OR(D79="",L79=""),"",D79/L79-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MB003684</t>
+          <t>MB002829</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Hidratante Firmador Revive: ginseng + retinol 60 ml</t>
+          <t>Essência Ginseng</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4070,27 +4992,55 @@
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>139.9</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="n"/>
+        <v>116.9</v>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Ginseng Essence Water</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>150 ml (5.07 FL. OZ.)</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>18</v>
+      </c>
       <c r="I80" s="4" t="n"/>
-      <c r="L80" s="2" t="n"/>
-      <c r="M80" s="6" t="n"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/ginseng-essence-water</t>
+        </is>
+      </c>
+      <c r="L80" s="2">
+        <f>ROUND(H80*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M80" s="6">
+        <f>IF(OR(D80="",L80=""),"",D80/L80-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MB003686</t>
+          <t>MB003687</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Kit Essencial: 5 minis em nécessaire de viagem</t>
+          <t>Paleta Hanbang: kit com os 4 séruns da marca</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4099,27 +5049,53 @@
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>255.9</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="n"/>
-      <c r="I81" s="4" t="n"/>
-      <c r="L81" s="2" t="n"/>
-      <c r="M81" s="6" t="n"/>
+        <v>495.9</v>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Hanbang Serum Discovery Kit</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" s="4" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="I81" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/hanbang-serum-discovery-kit</t>
+        </is>
+      </c>
+      <c r="L81" s="2">
+        <f>ROUND(H81*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M81" s="6">
+        <f>IF(OR(D81="",L81=""),"",D81/L81-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MB002871</t>
+          <t>MB002819</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Kit Protetores + Dupla Limpeza: 4 protetores, óleo e gel de limpeza</t>
+          <t>Sérum Iluminador: Própolis + Niacinamida · 1.01 fl. oz.(30ml)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4128,27 +5104,57 @@
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>291.9</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="n"/>
-      <c r="I82" s="4" t="n"/>
-      <c r="L82" s="2" t="n"/>
-      <c r="M82" s="6" t="n"/>
+        <v>98.90000000000001</v>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Revive Eye Serum : Ginseng + Retinal</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>30ML X 2-PACK</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="I82" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
+        </is>
+      </c>
+      <c r="L82" s="2">
+        <f>ROUND(H82*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M82" s="6">
+        <f>IF(OR(D82="",L82=""),"",D82/L82-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MB003690</t>
+          <t>MB002820</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Kit Rotina Verde Refrescante: tônico de ameixa verde + Dayscreen FPS 30</t>
+          <t>Sérum Iluminador: Própolis + Niacinamida · 2.03 fl. oz.(60ml)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4157,27 +5163,57 @@
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>319.9</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="n"/>
-      <c r="I83" s="4" t="n"/>
-      <c r="L83" s="2" t="n"/>
-      <c r="M83" s="6" t="n"/>
+        <v>160.9</v>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Glow Serum : Propolis + Niacinamide</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2.03 fl. oz.(60ml)</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="I83" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/glow-serum-propolis-niacinamide?variant=51833681805684</t>
+        </is>
+      </c>
+      <c r="L83" s="2">
+        <f>ROUND(H83*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M83" s="6">
+        <f>IF(OR(D83="",L83=""),"",D83/L83-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MB002876</t>
+          <t>MB003647</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Loção Solar Corporal Mineral Comfort Protection FPS 30</t>
+          <t>Sérum para Olhos Revive: Ginseng + Retina</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4186,27 +5222,57 @@
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>999.99</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="n"/>
-      <c r="I84" s="4" t="n"/>
-      <c r="L84" s="2" t="n"/>
-      <c r="M84" s="6" t="n"/>
+        <v>160.9</v>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Revive Eye Serum : Ginseng + Retinal</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>30ML X 2-PACK</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="I84" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
+        </is>
+      </c>
+      <c r="L84" s="2">
+        <f>ROUND(H84*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M84" s="6">
+        <f>IF(OR(D84="",L84=""),"",D84/L84-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MB002875</t>
+          <t>MB002776</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Loção Solar Corporal Mineral Comfort Protection FPS 40</t>
+          <t>Sérum para Olhos Revive: Ginseng + Retinal · 30ml</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4215,27 +5281,57 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>999.99</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H85" s="4" t="n"/>
-      <c r="I85" s="4" t="n"/>
-      <c r="L85" s="2" t="n"/>
-      <c r="M85" s="6" t="n"/>
+        <v>160.9</v>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Revive Eye Serum : Ginseng + Retinal</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>30ML X 2-PACK</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="I85" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
+        </is>
+      </c>
+      <c r="L85" s="2">
+        <f>ROUND(H85*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M85" s="6">
+        <f>IF(OR(D85="",L85=""),"",D85/L85-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MB002879</t>
+          <t>MB002777</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Máscara Calmante de Barreira</t>
+          <t>Sérum para Olhos Revive: Ginseng + Retinal · 30ml x 2-Pack</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4243,28 +5339,56 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n">
-        <v>181.9</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="n"/>
-      <c r="I86" s="4" t="n"/>
-      <c r="L86" s="2" t="n"/>
-      <c r="M86" s="6" t="n"/>
+      <c r="D86" s="2" t="n"/>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Revive Eye Serum : Ginseng + Retinal</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>30ML X 2-PACK</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="I86" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
+        </is>
+      </c>
+      <c r="L86" s="2">
+        <f>ROUND(H86*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M86" s="6">
+        <f>IF(OR(D86="",L86=""),"",D86/L86-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MB002877</t>
+          <t>MB002778</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Máscara Calmante de Centella Asiática (10 unidades)</t>
+          <t>Sérum para Olhos Revive: Ginseng + Retinal · 50ml x 2-Pack</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4272,28 +5396,56 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="D87" s="2" t="n">
-        <v>999.99</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H87" s="4" t="n"/>
-      <c r="I87" s="4" t="n"/>
-      <c r="L87" s="2" t="n"/>
-      <c r="M87" s="6" t="n"/>
+      <c r="D87" s="2" t="n"/>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Revive Eye Serum : Ginseng + Retinal</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>50ml x 2-Pack</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="I87" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal?variant=54416123003252</t>
+        </is>
+      </c>
+      <c r="L87" s="2">
+        <f>ROUND(H87*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M87" s="6">
+        <f>IF(OR(D87="",L87=""),"",D87/L87-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MB003655</t>
+          <t>MB003683</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Máscara Refrescante de Poros de Feijão Vermelho 140 ml</t>
+          <t>Sérum para Olhos Revive: ginseng + retinal 30 ml</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4302,27 +5454,57 @@
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>116.9</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="n"/>
-      <c r="I88" s="4" t="n"/>
-      <c r="L88" s="2" t="n"/>
-      <c r="M88" s="6" t="n"/>
+        <v>160.9</v>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Revive Eye Serum : Ginseng + Retinal</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>30ML X 2-PACK</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="I88" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
+        </is>
+      </c>
+      <c r="L88" s="2">
+        <f>ROUND(H88*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M88" s="6">
+        <f>IF(OR(D88="",L88=""),"",D88/L88-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MB003656</t>
+          <t>MB003662</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Máscara de Arroz Moído e Mel 150 ml</t>
+          <t>Óleo de Limpeza de Ginseng 210 ml</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4331,36 +5513,64 @@
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H89" s="4" t="n"/>
+        <v>144.9</v>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Ginseng Cleansing Oil</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>210 ml (7.10 FL. OZ.)</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="I89" s="4" t="n"/>
-      <c r="L89" s="2" t="n"/>
-      <c r="M89" s="6" t="n"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/ginseng-cleansing-oil</t>
+        </is>
+      </c>
+      <c r="L89" s="2">
+        <f>ROUND(H89*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M89" s="6">
+        <f>IF(OR(D89="",L89=""),"",D89/L89-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MB003691</t>
+          <t>MB003695</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sérum Calmante Barreira: Green Tea-HA + pantenol 30 ml</t>
+          <t>Beauty of Joseon Duo Radiant + Dewy FPS 50 e FPS 50+: Glow Sun Stick 14 g + Hydra Shield protetor corporal 150 ml</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>99.90000000000001</v>
+        <v>319.9</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -4375,12 +5585,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MB002878</t>
+          <t>MB002769</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sérum Calmante para a Barreira da Pele</t>
+          <t>Adesivo para Olhos Revive: Ginseng + Retinal</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4389,7 +5599,7 @@
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>999.99</v>
+        <v>144.9</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -4404,12 +5614,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MB003698</t>
+          <t>MB002818</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sérum Firmador de Poros: PDRN de feijão vermelho + peptídeo 30 ml</t>
+          <t>Bastão Protetor Solar Glow</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4418,7 +5628,7 @@
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>144.9</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -4433,12 +5643,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MB003672</t>
+          <t>MB003648</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Trio Solar Perfeito Hanbang: Relief Sun + Matte Sun Stick + Ginseng Moist Sun Serum</t>
+          <t>Bastão Protetor Solar Matte: Artemísia + Camélia (FPS 50+ PA++++)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4447,7 +5657,7 @@
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>306.9</v>
+        <v>163.9</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -4462,12 +5672,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MB003665</t>
+          <t>MB002802</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tônico Refrescante de Ameixa Verde: AHA + BHA 150 ml</t>
+          <t>Bastão Solar Matte: Artemísia + Camélia (FPS 50+ PA++++) · 1-Pack</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4476,7 +5686,7 @@
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>104.9</v>
+        <v>999.99</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -4491,12 +5701,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MB002887</t>
+          <t>MB002803</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>[BOJ x Ian Charms] Kit All Day (edição limitada)</t>
+          <t>Bastão Solar Matte: Artemísia + Camélia (FPS 50+ PA++++) · 2-Pack</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4504,9 +5714,7 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="D95" s="2" t="n">
-        <v>999.99</v>
-      </c>
+      <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>Sem par</t>
@@ -4520,12 +5728,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MB002886</t>
+          <t>MB003674</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>[BOJ x Ian Charms] Kit Só os Ícones (edição limitada)</t>
+          <t>Beauty of Joseon All Day Sun Duo FPS 50+ PA++++: Relief Sun 50 ml + Matte Sun Stick 18 g</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4534,7 +5742,7 @@
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>999.99</v>
+        <v>196.9</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -4545,6 +5753,2962 @@
       <c r="I96" s="4" t="n"/>
       <c r="L96" s="2" t="n"/>
       <c r="M96" s="6" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>MB003697</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Comfort Protection FPS 40: protetor solar mineral para o corpo 150 ml</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="n"/>
+      <c r="I97" s="4" t="n"/>
+      <c r="L97" s="2" t="n"/>
+      <c r="M97" s="6" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>MB003671</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Daily Tinted Fluid FPS 30: protetor solar mineral com cor</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="n"/>
+      <c r="I98" s="4" t="n"/>
+      <c r="L98" s="2" t="n"/>
+      <c r="M98" s="6" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>MB002843</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Day Dew Mini FPS 50: protetor solar 10 ml</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="n"/>
+      <c r="I99" s="4" t="n"/>
+      <c r="L99" s="2" t="n"/>
+      <c r="M99" s="6" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>MB003694</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Duo Relax + Relief FPS 50+ PA++++ e FPS 40: Relief Sun 50 ml + protetor corporal mineral 150 ml</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>319.9</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="n"/>
+      <c r="I100" s="4" t="n"/>
+      <c r="L100" s="2" t="n"/>
+      <c r="M100" s="6" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MB002806</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Duo de Protetores Leves Day Dew FPS 50 + Dayscreen FPS 30: protetores solares 50 ml + 60 ml</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>166.9</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="n"/>
+      <c r="I101" s="4" t="n"/>
+      <c r="L101" s="2" t="n"/>
+      <c r="M101" s="6" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>MB003675</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Ginseng Moist Sun Serum FPS 50+ PA++++: sérum solar hidratante</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="n"/>
+      <c r="I102" s="4" t="n"/>
+      <c r="L102" s="2" t="n"/>
+      <c r="M102" s="6" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>MB002873</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Protetor Solar Daily Relief FPS 40 · 1-Pack</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>195.9</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="n"/>
+      <c r="I103" s="4" t="n"/>
+      <c r="L103" s="2" t="n"/>
+      <c r="M103" s="6" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>MB002874</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Protetor Solar Daily Relief FPS 40 · 2-Pack</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>195.9</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="n"/>
+      <c r="I104" s="4" t="n"/>
+      <c r="L104" s="2" t="n"/>
+      <c r="M104" s="6" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>MB002752</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 15C</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="n"/>
+      <c r="I105" s="4" t="n"/>
+      <c r="L105" s="2" t="n"/>
+      <c r="M105" s="6" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>MB002753</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 17N</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="n"/>
+      <c r="I106" s="4" t="n"/>
+      <c r="L106" s="2" t="n"/>
+      <c r="M106" s="6" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>MB002754</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 21W</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="n"/>
+      <c r="I107" s="4" t="n"/>
+      <c r="L107" s="2" t="n"/>
+      <c r="M107" s="6" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>MB002755</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 23N</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="n"/>
+      <c r="I108" s="4" t="n"/>
+      <c r="L108" s="2" t="n"/>
+      <c r="M108" s="6" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>MB002756</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 25W</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="n"/>
+      <c r="I109" s="4" t="n"/>
+      <c r="L109" s="2" t="n"/>
+      <c r="M109" s="6" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>MB002757</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 29N</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="n"/>
+      <c r="I110" s="4" t="n"/>
+      <c r="L110" s="2" t="n"/>
+      <c r="M110" s="6" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>MB002758</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 33N</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="n"/>
+      <c r="I111" s="4" t="n"/>
+      <c r="L111" s="2" t="n"/>
+      <c r="M111" s="6" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>MB002759</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 35N</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="n"/>
+      <c r="I112" s="4" t="n"/>
+      <c r="L112" s="2" t="n"/>
+      <c r="M112" s="6" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>MB002760</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 39W</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="n"/>
+      <c r="I113" s="4" t="n"/>
+      <c r="L113" s="2" t="n"/>
+      <c r="M113" s="6" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>MB002761</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 43W</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="n"/>
+      <c r="I114" s="4" t="n"/>
+      <c r="L114" s="2" t="n"/>
+      <c r="M114" s="6" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>MB002762</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 45N</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="n"/>
+      <c r="I115" s="4" t="n"/>
+      <c r="L115" s="2" t="n"/>
+      <c r="M115" s="6" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>MB002763</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 47N</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="n"/>
+      <c r="I116" s="4" t="n"/>
+      <c r="L116" s="2" t="n"/>
+      <c r="M116" s="6" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>MB002764</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 51N</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="n"/>
+      <c r="I117" s="4" t="n"/>
+      <c r="L117" s="2" t="n"/>
+      <c r="M117" s="6" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>MB002765</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 54N</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="n"/>
+      <c r="I118" s="4" t="n"/>
+      <c r="L118" s="2" t="n"/>
+      <c r="M118" s="6" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>MB002766</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 59N</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="n"/>
+      <c r="I119" s="4" t="n"/>
+      <c r="L119" s="2" t="n"/>
+      <c r="M119" s="6" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>MB003644</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Beauty of Joseon: Filtro Solar com Arroz + Probióticos (FPS 50+ PA++++)</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>137.9</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="n"/>
+      <c r="I120" s="4" t="n"/>
+      <c r="L120" s="2" t="n"/>
+      <c r="M120" s="6" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>MB002794</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Bálsamo de Limpeza Radiance</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="n"/>
+      <c r="I121" s="4" t="n"/>
+      <c r="L121" s="2" t="n"/>
+      <c r="M121" s="6" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>MB002863</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · DN310 / 50ml</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="n"/>
+      <c r="I122" s="4" t="n"/>
+      <c r="L122" s="2" t="n"/>
+      <c r="M122" s="6" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>MB002864</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · DN310 / 7ml</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="n"/>
+      <c r="I123" s="4" t="n"/>
+      <c r="L123" s="2" t="n"/>
+      <c r="M123" s="6" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>MB002869</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · DN350 / 50ml</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="n"/>
+      <c r="I124" s="4" t="n"/>
+      <c r="L124" s="2" t="n"/>
+      <c r="M124" s="6" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>MB002870</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · DN350 / 7ml</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="n"/>
+      <c r="I125" s="4" t="n"/>
+      <c r="L125" s="2" t="n"/>
+      <c r="M125" s="6" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>MB002865</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · DP320 / 50ml</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="n"/>
+      <c r="I126" s="4" t="n"/>
+      <c r="L126" s="2" t="n"/>
+      <c r="M126" s="6" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>MB002866</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · DP320 / 7ml</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="n"/>
+      <c r="I127" s="4" t="n"/>
+      <c r="L127" s="2" t="n"/>
+      <c r="M127" s="6" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>MB002861</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · DY300 / 50ml</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="n"/>
+      <c r="I128" s="4" t="n"/>
+      <c r="L128" s="2" t="n"/>
+      <c r="M128" s="6" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>MB002862</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · DY300 / 7ml</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H129" s="4" t="n"/>
+      <c r="I129" s="4" t="n"/>
+      <c r="L129" s="2" t="n"/>
+      <c r="M129" s="6" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>MB002867</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · DY330 / 50ml</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="n"/>
+      <c r="I130" s="4" t="n"/>
+      <c r="L130" s="2" t="n"/>
+      <c r="M130" s="6" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>MB002868</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · DY330 / 7ml</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="n"/>
+      <c r="I131" s="4" t="n"/>
+      <c r="L131" s="2" t="n"/>
+      <c r="M131" s="6" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>MB002849</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · LN110 / 50ml</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="n"/>
+      <c r="I132" s="4" t="n"/>
+      <c r="L132" s="2" t="n"/>
+      <c r="M132" s="6" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>MB002850</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · LN110 / 7ml</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H133" s="4" t="n"/>
+      <c r="I133" s="4" t="n"/>
+      <c r="L133" s="2" t="n"/>
+      <c r="M133" s="6" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>MB002847</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · LP100 / 50ml</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="n"/>
+      <c r="I134" s="4" t="n"/>
+      <c r="L134" s="2" t="n"/>
+      <c r="M134" s="6" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>MB002848</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · LP100 / 7ml</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H135" s="4" t="n"/>
+      <c r="I135" s="4" t="n"/>
+      <c r="L135" s="2" t="n"/>
+      <c r="M135" s="6" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>MB002851</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · LP110 / 50ml</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="n"/>
+      <c r="I136" s="4" t="n"/>
+      <c r="L136" s="2" t="n"/>
+      <c r="M136" s="6" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>MB002852</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · LP110 / 7ml</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H137" s="4" t="n"/>
+      <c r="I137" s="4" t="n"/>
+      <c r="L137" s="2" t="n"/>
+      <c r="M137" s="6" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>MB002859</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · MN230 / 50ml</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="n"/>
+      <c r="I138" s="4" t="n"/>
+      <c r="L138" s="2" t="n"/>
+      <c r="M138" s="6" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>MB002860</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · MN230 / 7ml</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H139" s="4" t="n"/>
+      <c r="I139" s="4" t="n"/>
+      <c r="L139" s="2" t="n"/>
+      <c r="M139" s="6" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>MB002853</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · MP200 / 50ml</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="n"/>
+      <c r="I140" s="4" t="n"/>
+      <c r="L140" s="2" t="n"/>
+      <c r="M140" s="6" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>MB002854</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · MP200 / 7ml</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H141" s="4" t="n"/>
+      <c r="I141" s="4" t="n"/>
+      <c r="L141" s="2" t="n"/>
+      <c r="M141" s="6" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>MB002855</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · MY210 / 50ml</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="n"/>
+      <c r="I142" s="4" t="n"/>
+      <c r="L142" s="2" t="n"/>
+      <c r="M142" s="6" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>MB002856</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · MY210 / 7ml</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="n"/>
+      <c r="I143" s="4" t="n"/>
+      <c r="L143" s="2" t="n"/>
+      <c r="M143" s="6" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>MB002857</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · MY220 / 50ml</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="n"/>
+      <c r="I144" s="4" t="n"/>
+      <c r="L144" s="2" t="n"/>
+      <c r="M144" s="6" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>MB002858</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · MY220 / 7ml</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H145" s="4" t="n"/>
+      <c r="I145" s="4" t="n"/>
+      <c r="L145" s="2" t="n"/>
+      <c r="M145" s="6" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>MB002768</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Duo Arroz Alívio</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="n"/>
+      <c r="I146" s="4" t="n"/>
+      <c r="L146" s="2" t="n"/>
+      <c r="M146" s="6" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>MB003673</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Duo Dia e Noite: Relief Sun FPS 50+ PA++++ + Dynasty Cream</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>305.9</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="n"/>
+      <c r="I147" s="4" t="n"/>
+      <c r="L147" s="2" t="n"/>
+      <c r="M147" s="6" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>MB003652</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Duo Dupla Limpeza: óleo de ginseng + gel de ameixa verde</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="n"/>
+      <c r="I148" s="4" t="n"/>
+      <c r="L148" s="2" t="n"/>
+      <c r="M148" s="6" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>MB002872</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Duo Escudo Diário e Hidratação Profunda</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="n"/>
+      <c r="I149" s="4" t="n"/>
+      <c r="L149" s="2" t="n"/>
+      <c r="M149" s="6" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>MB002880</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Duo Iluminador e Firmador</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="n"/>
+      <c r="I150" s="4" t="n"/>
+      <c r="L150" s="2" t="n"/>
+      <c r="M150" s="6" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>MB003650</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Duo Iluminador e Firmador: Light On Serum + Revive Eye Serum</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>148.9</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H151" s="4" t="n"/>
+      <c r="I151" s="4" t="n"/>
+      <c r="L151" s="2" t="n"/>
+      <c r="M151" s="6" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>MB002795</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Duo Protege o Seu Brilho</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>314.9</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="n"/>
+      <c r="I152" s="4" t="n"/>
+      <c r="L152" s="2" t="n"/>
+      <c r="M152" s="6" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>MB003689</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Duo Proteja o Seu Brilho: Glow Serum + Dayscreen FPS 30</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>315.9</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="n"/>
+      <c r="I153" s="4" t="n"/>
+      <c r="L153" s="2" t="n"/>
+      <c r="M153" s="6" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>MB003688</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Duo Proteção Diária e Hidratação Profunda: Dynasty Cream + Dayscreen FPS 30</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>256.9</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="n"/>
+      <c r="I154" s="4" t="n"/>
+      <c r="L154" s="2" t="n"/>
+      <c r="M154" s="6" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>MB002789</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Duo Refinador de Poros</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H155" s="4" t="n"/>
+      <c r="I155" s="4" t="n"/>
+      <c r="L155" s="2" t="n"/>
+      <c r="M155" s="6" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>MB003654</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Duo Refinador de Poros: máscaras de feijão vermelho e de arroz com mel</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>180.9</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="n"/>
+      <c r="I156" s="4" t="n"/>
+      <c r="L156" s="2" t="n"/>
+      <c r="M156" s="6" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>MB003642</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Duo Revitalizante para os Olhos</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>201.9</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H157" s="4" t="n"/>
+      <c r="I157" s="4" t="n"/>
+      <c r="L157" s="2" t="n"/>
+      <c r="M157" s="6" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>MB002793</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Duo Solar Radiante + Iluminado</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>319.9</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="n"/>
+      <c r="I158" s="4" t="n"/>
+      <c r="L158" s="2" t="n"/>
+      <c r="M158" s="6" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>MB002840</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Duo de Limpeza Dupla Profunda · Large</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>217.9</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H159" s="4" t="n"/>
+      <c r="I159" s="4" t="n"/>
+      <c r="L159" s="2" t="n"/>
+      <c r="M159" s="6" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>MB002839</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Duo de Limpeza Dupla Profunda · Original</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="n"/>
+      <c r="I160" s="4" t="n"/>
+      <c r="L160" s="2" t="n"/>
+      <c r="M160" s="6" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>MB002885</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Duo de Protetor Solar para o Dia Todo</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="n"/>
+      <c r="I161" s="4" t="n"/>
+      <c r="L161" s="2" t="n"/>
+      <c r="M161" s="6" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>MB002884</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Gel Esfoliante Flor de Damasco</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="n"/>
+      <c r="I162" s="4" t="n"/>
+      <c r="L162" s="2" t="n"/>
+      <c r="M162" s="6" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>MB003660</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Gel Esfoliante Flor de Damasco 100 ml</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="n"/>
+      <c r="I163" s="4" t="n"/>
+      <c r="L163" s="2" t="n"/>
+      <c r="M163" s="6" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>MB003664</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Gel de Limpeza Refrescante de Ameixa Verde</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="n"/>
+      <c r="I164" s="4" t="n"/>
+      <c r="L164" s="2" t="n"/>
+      <c r="M164" s="6" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>MB002790</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Gel de Água de Feijão Azuki</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H165" s="4" t="n"/>
+      <c r="I165" s="4" t="n"/>
+      <c r="L165" s="2" t="n"/>
+      <c r="M165" s="6" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>MB002774</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Hidratante Firmador Revive: Ginseng + Retinol</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>139.9</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="n"/>
+      <c r="I166" s="4" t="n"/>
+      <c r="L166" s="2" t="n"/>
+      <c r="M166" s="6" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>MB003684</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Hidratante Firmador Revive: ginseng + retinol 60 ml</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>139.9</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="n"/>
+      <c r="I167" s="4" t="n"/>
+      <c r="L167" s="2" t="n"/>
+      <c r="M167" s="6" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>MB002832</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Kit Essencial</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>254.9</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="n"/>
+      <c r="I168" s="4" t="n"/>
+      <c r="L168" s="2" t="n"/>
+      <c r="M168" s="6" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>MB003686</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Kit Essencial: 5 minis em nécessaire de viagem</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>255.9</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H169" s="4" t="n"/>
+      <c r="I169" s="4" t="n"/>
+      <c r="L169" s="2" t="n"/>
+      <c r="M169" s="6" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>MB002871</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Kit Protetores + Dupla Limpeza: 4 protetores, óleo e gel de limpeza</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>291.9</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="n"/>
+      <c r="I170" s="4" t="n"/>
+      <c r="L170" s="2" t="n"/>
+      <c r="M170" s="6" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>MB002788</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Kit Rotina Refrescante Verde</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>319.9</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H171" s="4" t="n"/>
+      <c r="I171" s="4" t="n"/>
+      <c r="L171" s="2" t="n"/>
+      <c r="M171" s="6" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>MB003690</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Kit Rotina Verde Refrescante: tônico de ameixa verde + Dayscreen FPS 30</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>319.9</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="n"/>
+      <c r="I172" s="4" t="n"/>
+      <c r="L172" s="2" t="n"/>
+      <c r="M172" s="6" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>MB002821</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Leite de Arroz Reabastecedor Glow</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H173" s="4" t="n"/>
+      <c r="I173" s="4" t="n"/>
+      <c r="L173" s="2" t="n"/>
+      <c r="M173" s="6" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>MB002810</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Loção Solar Corporal Hydra Shield FPS 50+</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H174" s="4" t="n"/>
+      <c r="I174" s="4" t="n"/>
+      <c r="L174" s="2" t="n"/>
+      <c r="M174" s="6" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>MB002876</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Loção Solar Corporal Mineral Comfort Protection FPS 30</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H175" s="4" t="n"/>
+      <c r="I175" s="4" t="n"/>
+      <c r="L175" s="2" t="n"/>
+      <c r="M175" s="6" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>MB002875</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Loção Solar Corporal Mineral Comfort Protection FPS 40</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H176" s="4" t="n"/>
+      <c r="I176" s="4" t="n"/>
+      <c r="L176" s="2" t="n"/>
+      <c r="M176" s="6" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>MB002879</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Máscara Calmante de Barreira</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H177" s="4" t="n"/>
+      <c r="I177" s="4" t="n"/>
+      <c r="L177" s="2" t="n"/>
+      <c r="M177" s="6" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>MB002877</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Máscara Calmante de Centella Asiática (10 unidades)</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="n"/>
+      <c r="I178" s="4" t="n"/>
+      <c r="L178" s="2" t="n"/>
+      <c r="M178" s="6" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>MB002814</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Máscara Facial Esfoliante Iluminadora de Arroz e Mel</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H179" s="4" t="n"/>
+      <c r="I179" s="4" t="n"/>
+      <c r="L179" s="2" t="n"/>
+      <c r="M179" s="6" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>MB003655</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Máscara Refrescante de Poros de Feijão Vermelho 140 ml</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="n"/>
+      <c r="I180" s="4" t="n"/>
+      <c r="L180" s="2" t="n"/>
+      <c r="M180" s="6" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>MB002791</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Máscara Refrescante para Poros com Feijão Azuki</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H181" s="4" t="n"/>
+      <c r="I181" s="4" t="n"/>
+      <c r="L181" s="2" t="n"/>
+      <c r="M181" s="6" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>MB003656</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Máscara de Arroz Moído e Mel 150 ml</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H182" s="4" t="n"/>
+      <c r="I182" s="4" t="n"/>
+      <c r="L182" s="2" t="n"/>
+      <c r="M182" s="6" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>MB002799</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Paleta Perfeita Hanbang</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H183" s="4" t="n"/>
+      <c r="I183" s="4" t="n"/>
+      <c r="L183" s="2" t="n"/>
+      <c r="M183" s="6" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>MB002816</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Sabonete Refrescante de Ameixa Verde · 100ml</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H184" s="4" t="n"/>
+      <c r="I184" s="4" t="n"/>
+      <c r="L184" s="2" t="n"/>
+      <c r="M184" s="6" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>MB002817</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Sabonete Refrescante de Ameixa Verde · 200ml</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="n"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H185" s="4" t="n"/>
+      <c r="I185" s="4" t="n"/>
+      <c r="L185" s="2" t="n"/>
+      <c r="M185" s="6" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>MB002800</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Saquinho Nobang para sabonete em barra, de organza</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H186" s="4" t="n"/>
+      <c r="I186" s="4" t="n"/>
+      <c r="L186" s="2" t="n"/>
+      <c r="M186" s="6" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>MB003691</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Sérum Calmante Barreira: Green Tea-HA + pantenol 30 ml</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H187" s="4" t="n"/>
+      <c r="I187" s="4" t="n"/>
+      <c r="L187" s="2" t="n"/>
+      <c r="M187" s="6" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>MB002878</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Sérum Calmante para a Barreira da Pele</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H188" s="4" t="n"/>
+      <c r="I188" s="4" t="n"/>
+      <c r="L188" s="2" t="n"/>
+      <c r="M188" s="6" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>MB002796</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Sérum Firmador de Poros</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H189" s="4" t="n"/>
+      <c r="I189" s="4" t="n"/>
+      <c r="L189" s="2" t="n"/>
+      <c r="M189" s="6" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>MB003698</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Sérum Firmador de Poros: PDRN de feijão vermelho + peptídeo 30 ml</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H190" s="4" t="n"/>
+      <c r="I190" s="4" t="n"/>
+      <c r="L190" s="2" t="n"/>
+      <c r="M190" s="6" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>MB002828</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Sérum Solar Ginseng Hidratante (FPS 50+ PA++++)</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H191" s="4" t="n"/>
+      <c r="I191" s="4" t="n"/>
+      <c r="L191" s="2" t="n"/>
+      <c r="M191" s="6" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>MB002798</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Trio Solar Perfeito Hanbang [Relief Sun + Bastão Solar Matte + Sérum Solar]</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H192" s="4" t="n"/>
+      <c r="I192" s="4" t="n"/>
+      <c r="L192" s="2" t="n"/>
+      <c r="M192" s="6" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>MB003672</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Trio Solar Perfeito Hanbang: Relief Sun + Matte Sun Stick + Ginseng Moist Sun Serum</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="n">
+        <v>306.9</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H193" s="4" t="n"/>
+      <c r="I193" s="4" t="n"/>
+      <c r="L193" s="2" t="n"/>
+      <c r="M193" s="6" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>MB002792</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Trio de Cuidados com os Poros de Feijão Azuki</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>400.9</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H194" s="4" t="n"/>
+      <c r="I194" s="4" t="n"/>
+      <c r="L194" s="2" t="n"/>
+      <c r="M194" s="6" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>MB002815</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Tônico Refrescante de Ameixa Verde: AHA + BHA</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H195" s="4" t="n"/>
+      <c r="I195" s="4" t="n"/>
+      <c r="L195" s="2" t="n"/>
+      <c r="M195" s="6" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>MB003665</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Tônico Refrescante de Ameixa Verde: AHA + BHA 150 ml</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H196" s="4" t="n"/>
+      <c r="I196" s="4" t="n"/>
+      <c r="L196" s="2" t="n"/>
+      <c r="M196" s="6" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>MB002887</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>[BOJ x Ian Charms] Kit All Day (edição limitada)</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H197" s="4" t="n"/>
+      <c r="I197" s="4" t="n"/>
+      <c r="L197" s="2" t="n"/>
+      <c r="M197" s="6" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>MB002886</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>[BOJ x Ian Charms] Kit Só os Ícones (edição limitada)</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>999.99</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H198" s="4" t="n"/>
+      <c r="I198" s="4" t="n"/>
+      <c r="L198" s="2" t="n"/>
+      <c r="M198" s="6" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4592,10 +8756,54 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId45"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId89"/>
   </tableParts>
 </worksheet>
 </file>

--- a/tools/precos/planilhas/precos-oficiais-Beauty-of-Joseon.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-Beauty-of-Joseon.xlsx
@@ -570,12 +570,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MB002826</t>
+          <t>MB003659</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Duo Glass Skin · Large</t>
+          <t>Calming Barrier Mask: máscara calmante de centella, 10 unidades</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>387.9</v>
+        <v>182.9</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -593,20 +593,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Glass Skin Duo</t>
+          <t>Calming Barrier Mask</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>18 mL / 0.60 FL. OZ. (10 Sheets)</t>
         </is>
       </c>
       <c r="H2" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>82</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="I2" s="4" t="n"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -614,7 +612,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/glass-skin-duo-us?variant=55226029998452</t>
+          <t>https://beautyofjoseon.com/products/calming-barrier-sheet-mask-global</t>
         </is>
       </c>
       <c r="L2" s="2">
@@ -629,12 +627,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MB002825</t>
+          <t>MB002835</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Duo Glass Skin · Original</t>
+          <t>Dynasty Cream: creme hidratante de arroz e ginseng · 1 fl.oz. (30ml)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -643,7 +641,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>193.9</v>
+        <v>108.9</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -652,20 +650,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Glass Skin Duo</t>
+          <t>Dynasty Cream</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>1 fl.oz. (30ml)</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>26.65</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>41</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I3" s="4" t="n"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -673,7 +669,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/glass-skin-duo-us?variant=55226029965684</t>
+          <t>https://beautyofjoseon.com/products/dynasty-cream?variant=54217328460148</t>
         </is>
       </c>
       <c r="L3" s="2">
@@ -688,12 +684,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MB003649</t>
+          <t>MB002836</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hanbang Serum Discovery Kit: 4 séruns mini de 10 ml</t>
+          <t>Dynasty Cream: creme hidratante de arroz e ginseng · 1.69 fl.oz.(50ml)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -702,7 +698,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>156.9</v>
+        <v>127.9</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -711,24 +707,26 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hanbang Serum Discovery Kit</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Dynasty Cream</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1.69 fl.oz.(50ml)</t>
+        </is>
+      </c>
       <c r="H4" s="4" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>27</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="I4" s="4" t="n"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/hanbang-serum-discovery-kit</t>
+          <t>https://beautyofjoseon.com/products/dynasty-cream?variant=43222120759461</t>
         </is>
       </c>
       <c r="L4" s="2">
@@ -743,12 +741,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MB002809</t>
+          <t>MB002837</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JELLOSKIN Massage Cream for Face and Body</t>
+          <t>Dynasty Cream: creme hidratante de arroz e ginseng · 3.38 fl.oz.(100ml)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -757,7 +755,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>291.9</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -766,28 +764,28 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JELLOSKIN Massage Cream For Face and Body</t>
+          <t>Dynasty Cream</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1-Pack</t>
+          <t>3.38 fl.oz.(100ml)</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>12.5</v>
+        <v>32</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/jelloskin-massage-cream-for-face-and-body</t>
+          <t>https://beautyofjoseon.com/products/dynasty-cream?variant=43222120792229</t>
         </is>
       </c>
       <c r="L5" s="2">
@@ -802,21 +800,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MB002846</t>
+          <t>MB002838</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Day and Night Skincare Duo</t>
+          <t>Dynasty Cream: creme hidratante de arroz e ginseng · 3.38 fl.oz.(100ml) 2-Pack</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>999.99</v>
+        <v>525.9</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -825,15 +823,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Day and Night Care Duo</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>Dynasty Cream</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3.38 fl.oz.(100ml) 2-Pack</t>
+        </is>
+      </c>
       <c r="H6" s="4" t="n">
-        <v>31.5</v>
+        <v>72</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -842,7 +844,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/day-night-duo-skincare-set-uk</t>
+          <t>https://beautyofjoseon.com/products/dynasty-cream?variant=55014470091124</t>
         </is>
       </c>
       <c r="L6" s="2">
@@ -857,21 +859,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MB002813</t>
+          <t>MB002830</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hanbang Serum Discovery Kit</t>
+          <t>Ginseng Cleansing Oil</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>999.99</v>
+        <v>144.9</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -880,24 +882,26 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hanbang Serum Discovery Kit</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Ginseng Cleansing Oil</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>210 ml (7.10 FL. OZ.)</t>
+        </is>
+      </c>
       <c r="H7" s="4" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>27</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I7" s="4" t="n"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/hanbang-serum-discovery-kit</t>
+          <t>https://beautyofjoseon.com/products/ginseng-cleansing-oil</t>
         </is>
       </c>
       <c r="L7" s="2">
@@ -912,12 +916,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MB003676</t>
+          <t>MB003661</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Matte Sun Stick FPS 50+ PA++++: protetor solar em bastão artemísia + camélia 18 g</t>
+          <t>Ginseng Essence Water: essência de ginseng 150 ml</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -926,37 +930,35 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>163.9</v>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>116.9</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Matte Sun Stick : Mugwort+Camelia (SPF 50+ PA++++)</t>
+          <t>Ginseng Essence Water</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2-Pack</t>
+          <t>150 ml (5.07 FL. OZ.)</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>30</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I8" s="4" t="n"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/matte-sun-stick-mugwort-camelia-duo</t>
+          <t>https://beautyofjoseon.com/products/ginseng-essence-water</t>
         </is>
       </c>
       <c r="L8" s="2">
@@ -971,12 +973,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MB003678</t>
+          <t>MB003657</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Relief Sun Aqua-Fresh FPS 50+ PA++++: protetor solar de arroz + B5 50 ml</t>
+          <t>Glow Replenishing Rice Milk: tônico de arroz 150 ml</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -985,35 +987,37 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>116.9</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Relief Sun Aqua-Fresh : Rice + B5  (SPF50+ PA++++)</t>
+          <t>Glow Replenishing Rice Milk</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1-Pack</t>
+          <t>150 ml (5.07 FL. OZ.)</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="I9" s="4" t="n"/>
+        <v>15.3</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>18</v>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-aqua-fresh-rice-b5-spf50-pa-uk?variant=52419629646196</t>
+          <t>https://beautyofjoseon.com/products/glow-replenishing-rice-milk</t>
         </is>
       </c>
       <c r="L9" s="2">
@@ -1028,12 +1032,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MB003700</t>
+          <t>MB002809</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Tinted Mineral Dayscreen FPS 30: protetor solar mineral com cor 40 ml</t>
+          <t>JELLOSKIN Massage Cream for Face and Body</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1042,35 +1046,37 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>145.9</v>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>90.90000000000001</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tinted Mineral Dayscreen SPF 30</t>
+          <t>JELLOSKIN Massage Cream For Face and Body</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>15C</t>
+          <t>1-Pack</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I10" s="4" t="n"/>
+        <v>12.5</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/tinted-mineral-dayscreen-spf-30-global?variant=54870451323252</t>
+          <t>https://beautyofjoseon.com/products/jelloskin-massage-cream-for-face-and-body</t>
         </is>
       </c>
       <c r="L10" s="2">
@@ -1085,12 +1091,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MB002883</t>
+          <t>MB003666</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bojagi: tecido tradicional coreano para embrulhar presentes · Calm Blue</t>
+          <t>Red Bean Water Gel: hidratante em gel de feijão vermelho 100 ml</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1099,35 +1105,37 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>104.9</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bojagi</t>
+          <t>Red Bean Water Gel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Olive</t>
+          <t>100 ml (3.38 FL. OZ.)</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="I11" s="4" t="n"/>
+        <v>14.4</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>18</v>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/bojagi?variant=40739062481061</t>
+          <t>https://beautyofjoseon.com/products/red-bean-water-gel</t>
         </is>
       </c>
       <c r="L11" s="2">
@@ -1142,49 +1150,49 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MB002882</t>
+          <t>MB002769</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bojagi: tecido tradicional coreano para embrulhar presentes · Maehwa</t>
+          <t>Adesivo para Olhos Revive: Ginseng + Retinal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>144.9</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bojagi</t>
+          <t>Revive Under Eye Patch: Ginseng + Retinal</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Olive</t>
+          <t>100 g / 3.52 OZ. (60 Patches)</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I12" s="4" t="n"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/bojagi?variant=40739062481061</t>
+          <t>https://beautyofjoseon.com/products/revive-under-eye-patch-global</t>
         </is>
       </c>
       <c r="L12" s="2">
@@ -1199,39 +1207,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MB002881</t>
+          <t>MB002818</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bojagi: tecido tradicional coreano para embrulhar presentes · Olive</t>
+          <t>Bastão Protetor Solar Glow</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>144.9</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bojagi</t>
+          <t>Glow Sun Stick</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Olive</t>
+          <t>14 g (0.49 OZ.)</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I13" s="4" t="n"/>
       <c r="J13" t="inlineStr">
@@ -1241,7 +1249,7 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/bojagi?variant=40739062481061</t>
+          <t>https://beautyofjoseon.com/products/glow-sun-stick-sunscreen-stick</t>
         </is>
       </c>
       <c r="L13" s="2">
@@ -1256,39 +1264,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MB003659</t>
+          <t>MB002794</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Calming Barrier Mask: máscara calmante de centella, 10 unidades</t>
+          <t>Bálsamo de Limpeza Radiance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>182.9</v>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>82.90000000000001</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Calming Barrier Mask</t>
+          <t>Radiance Cleansing Balm</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>18 mL / 0.60 FL. OZ. (10 Sheets)</t>
+          <t>100 ml (3.38 FL. OZ.)</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I14" s="4" t="n"/>
       <c r="J14" t="inlineStr">
@@ -1298,7 +1306,7 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/calming-barrier-sheet-mask-global</t>
+          <t>https://beautyofjoseon.com/products/radiance-cleansing-balm</t>
         </is>
       </c>
       <c r="L14" s="2">
@@ -1313,47 +1321,49 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MB003681</t>
+          <t>MB003663</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Duo Revive: sérum para olhos + hidratante firmador com retinol</t>
+          <t>Bálsamo de Limpeza Radiance 100 ml</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>298.9</v>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>82.90000000000001</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revive Ritual Eye Duo</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Radiance Cleansing Balm</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>100 ml (3.38 FL. OZ.)</t>
+        </is>
+      </c>
       <c r="H15" s="4" t="n">
-        <v>27.75</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>37</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="I15" s="4" t="n"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-ritual-eye-duo-eu</t>
+          <t>https://beautyofjoseon.com/products/radiance-cleansing-balm</t>
         </is>
       </c>
       <c r="L15" s="2">
@@ -1368,49 +1378,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MB002835</t>
+          <t>MB002846</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dynasty Cream: creme hidratante de arroz e ginseng · 1 fl.oz. (30ml)</t>
+          <t>Day and Night Skincare Duo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>108.9</v>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>999.99</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dynasty Cream</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>1 fl.oz. (30ml)</t>
-        </is>
-      </c>
+          <t>Day and Night Care Duo</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="I16" s="4" t="n"/>
+        <v>31.5</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>42</v>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/dynasty-cream?variant=54217328460148</t>
+          <t>https://beautyofjoseon.com/products/day-night-duo-skincare-set-uk</t>
         </is>
       </c>
       <c r="L16" s="2">
@@ -1425,49 +1433,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MB002836</t>
+          <t>MB002813</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dynasty Cream: creme hidratante de arroz e ginseng · 1.69 fl.oz.(50ml)</t>
+          <t>Hanbang Serum Discovery Kit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>127.9</v>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>999.99</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dynasty Cream</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>1.69 fl.oz.(50ml)</t>
-        </is>
-      </c>
+          <t>Hanbang Serum Discovery Kit</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I17" s="4" t="n"/>
+        <v>21.6</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>27</v>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/dynasty-cream?variant=43222120759461</t>
+          <t>https://beautyofjoseon.com/products/hanbang-serum-discovery-kit</t>
         </is>
       </c>
       <c r="L17" s="2">
@@ -1482,42 +1488,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MB002837</t>
+          <t>MB002776</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dynasty Cream: creme hidratante de arroz e ginseng · 3.38 fl.oz.(100ml)</t>
+          <t>Sérum para Olhos Revive: Ginseng + Retinal · 30ml</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>291.9</v>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>160.9</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dynasty Cream</t>
+          <t>Revive Eye Serum : Ginseng + Retinal</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3.38 fl.oz.(100ml)</t>
+          <t>30ML X 2-PACK</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>32</v>
+        <v>25.5</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1526,7 +1532,7 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/dynasty-cream?variant=43222120792229</t>
+          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
         </is>
       </c>
       <c r="L18" s="2">
@@ -1541,51 +1547,49 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MB002838</t>
+          <t>MB002777</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dynasty Cream: creme hidratante de arroz e ginseng · 3.38 fl.oz.(100ml) 2-Pack</t>
+          <t>Sérum para Olhos Revive: Ginseng + Retinal · 30ml x 2-Pack</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>525.9</v>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dynasty Cream</t>
+          <t>Revive Eye Serum : Ginseng + Retinal</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3.38 fl.oz.(100ml) 2-Pack</t>
+          <t>30ML X 2-PACK</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>72</v>
+        <v>25.5</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/dynasty-cream?variant=55014470091124</t>
+          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
         </is>
       </c>
       <c r="L19" s="2">
@@ -1600,41 +1604,41 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MB002830</t>
+          <t>MB002778</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ginseng Cleansing Oil</t>
+          <t>Sérum para Olhos Revive: Ginseng + Retinal · 50ml x 2-Pack</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ginseng Cleansing Oil</t>
+          <t>Revive Eye Serum : Ginseng + Retinal</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>210 ml (7.10 FL. OZ.)</t>
+          <t>50ml x 2-Pack</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I20" s="4" t="n"/>
+        <v>42</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>56</v>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1642,7 +1646,7 @@
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/ginseng-cleansing-oil</t>
+          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal?variant=54416123003252</t>
         </is>
       </c>
       <c r="L20" s="2">
@@ -1657,39 +1661,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MB003661</t>
+          <t>MB003662</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ginseng Essence Water: essência de ginseng 150 ml</t>
+          <t>Óleo de Limpeza de Ginseng 210 ml</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>116.9</v>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>144.9</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ginseng Essence Water</t>
+          <t>Ginseng Cleansing Oil</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>150 ml (5.07 FL. OZ.)</t>
+          <t>210 ml (7.10 FL. OZ.)</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I21" s="4" t="n"/>
       <c r="J21" t="inlineStr">
@@ -1699,7 +1703,7 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/ginseng-essence-water</t>
+          <t>https://beautyofjoseon.com/products/ginseng-cleansing-oil</t>
         </is>
       </c>
       <c r="L21" s="2">
@@ -1714,12 +1718,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MB003668</t>
+          <t>MB002824</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Glow Deep Serum: arroz + alfa-arbutina 30 ml</t>
+          <t>Arroz Carregador Duo Glow</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1728,7 +1732,7 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>110.9</v>
+        <v>169.9</v>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
@@ -1737,18 +1741,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Glow Deep Serum : Rice + Alpha-Arbutin</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>1.01 fl. oz.(30ml)</t>
-        </is>
-      </c>
+          <t>Glow Charging Rice Duo</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="I22" s="4" t="n"/>
+        <v>27</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>36</v>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1756,7 +1758,7 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/glow-deep-serum-rice-alpha-arbutin?variant=51833689211252</t>
+          <t>https://beautyofjoseon.com/products/glow-charging-rice-duo</t>
         </is>
       </c>
       <c r="L22" s="2">
@@ -1771,12 +1773,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MB003657</t>
+          <t>MB003676</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Glow Replenishing Rice Milk: tônico de arroz 150 ml</t>
+          <t>Beauty of Joseon Matte Sun Stick FPS 50+ PA++++: protetor solar em bastão artemísia + camélia 18 g</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,7 +1787,7 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>116.9</v>
+        <v>163.9</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -1794,28 +1796,28 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Glow Replenishing Rice Milk</t>
+          <t>Matte Sun Stick : Mugwort+Camelia (SPF 50+ PA++++)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>150 ml (5.07 FL. OZ.)</t>
+          <t>2-Pack</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>15.3</v>
+        <v>22.5</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/glow-replenishing-rice-milk</t>
+          <t>https://beautyofjoseon.com/products/matte-sun-stick-mugwort-camelia-duo</t>
         </is>
       </c>
       <c r="L23" s="2">
@@ -1830,12 +1832,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MB003670</t>
+          <t>MB003678</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Glow Serum: própolis + niacinamida 30 ml</t>
+          <t>Beauty of Joseon Relief Sun Aqua-Fresh FPS 50+ PA++++: protetor solar de arroz + B5 50 ml</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1844,7 +1846,7 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>137.9</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
@@ -1853,28 +1855,26 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Glow Serum : Propolis + Niacinamide</t>
+          <t>Relief Sun Aqua-Fresh : Rice + B5  (SPF50+ PA++++)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.01 fl. oz.(30ml)</t>
+          <t>1-Pack</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>17</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="I24" s="4" t="n"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/glow-serum-propolis-niacinamide?variant=51833681772916</t>
+          <t>https://beautyofjoseon.com/products/relief-sun-aqua-fresh-rice-b5-spf50-pa-uk?variant=52419629646196</t>
         </is>
       </c>
       <c r="L24" s="2">
@@ -1889,12 +1889,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MB002812</t>
+          <t>MB002883</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hanbok Scrunchie: elástico de cabelo de tecido em dois tons · Honey Green</t>
+          <t>Bojagi: tecido tradicional coreano para embrulhar presentes · Calm Blue</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>93.90000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -1912,26 +1912,26 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hanbok Scrunchie</t>
+          <t>Bojagi</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Orchid pink</t>
+          <t>Calm Blue</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I25" s="4" t="n"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/hanbok-scrunchie?variant=43160500895909</t>
+          <t>https://beautyofjoseon.com/products/bojagi?variant=40739062546597</t>
         </is>
       </c>
       <c r="L25" s="2">
@@ -1946,12 +1946,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MB002811</t>
+          <t>MB002882</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hanbok Scrunchie: elástico de cabelo de tecido em dois tons · Orchid pink</t>
+          <t>Bojagi: tecido tradicional coreano para embrulhar presentes · Maehwa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>93.90000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
@@ -1969,26 +1969,26 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hanbok Scrunchie</t>
+          <t>Bojagi</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Orchid pink</t>
+          <t>Maehwa</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I26" s="4" t="n"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/hanbok-scrunchie?variant=43160500895909</t>
+          <t>https://beautyofjoseon.com/products/bojagi?variant=40739062513829</t>
         </is>
       </c>
       <c r="L26" s="2">
@@ -2003,12 +2003,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MB002801</t>
+          <t>MB002881</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kit Night-Reset: gel de limpeza de ameixa verde + Dynasty Cream 50 ml</t>
+          <t>Bojagi: tecido tradicional coreano para embrulhar presentes · Olive</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>305.9</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
@@ -2026,12 +2026,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Night-Reset Dewy Finish Kit</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>Bojagi</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Olive</t>
+        </is>
+      </c>
       <c r="H27" s="4" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="I27" s="4" t="n"/>
       <c r="J27" t="inlineStr">
@@ -2041,7 +2045,7 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/night-restore-dewy-finish-night-skincare-set</t>
+          <t>https://beautyofjoseon.com/products/bojagi?variant=40739062481061</t>
         </is>
       </c>
       <c r="L27" s="2">
@@ -2056,12 +2060,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MB003680</t>
+          <t>MB002826</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kit Revive Essentials: sérum para olhos, adesivos e hidratante firmador</t>
+          <t>Duo Glass Skin · Large</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2070,7 +2074,7 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>332.9</v>
+        <v>387.9</v>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
@@ -2079,15 +2083,19 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revive Essentials Set</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>Glass Skin Duo</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
       <c r="H28" s="4" t="n">
-        <v>45.75</v>
+        <v>74</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2096,7 +2104,7 @@
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-essentials-set-global</t>
+          <t>https://beautyofjoseon.com/products/glass-skin-duo-us?variant=55226029998452</t>
         </is>
       </c>
       <c r="L28" s="2">
@@ -2111,12 +2119,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MB002831</t>
+          <t>MB002825</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kit Ritual Glow: rotina completa de 6 passos, do sabonete ao protetor</t>
+          <t>Duo Glass Skin · Original</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2125,7 +2133,7 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>968.9</v>
+        <v>193.9</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
@@ -2134,14 +2142,20 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rice Glow Ritual Set</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>Glass Skin Duo</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
       <c r="H29" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="I29" s="4" t="n"/>
+        <v>26.65</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>41</v>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2149,7 +2163,7 @@
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/rice-glow-ritual-radiant-skincare-set-global</t>
+          <t>https://beautyofjoseon.com/products/glass-skin-duo-us?variant=55226029965684</t>
         </is>
       </c>
       <c r="L29" s="2">
@@ -2164,12 +2178,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MB002767</t>
+          <t>MB003681</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kit Sun-Cleanse: Relief Sun FPS 50+ + gel de limpeza de ameixa verde</t>
+          <t>Duo Revive: sérum para olhos + hidratante firmador com retinol</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2178,7 +2192,7 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>254.9</v>
+        <v>298.9</v>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
@@ -2187,14 +2201,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sun-Cleanse Daily Defense Set</t>
+          <t>Revive Ritual Eye Duo</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="I30" s="4" t="n"/>
+        <v>27.75</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>37</v>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>Esgotado</t>
@@ -2202,7 +2218,7 @@
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/sun-cleanse-daily-shield-cleanser-sunscreen-set</t>
+          <t>https://beautyofjoseon.com/products/revive-ritual-eye-duo-eu</t>
         </is>
       </c>
       <c r="L30" s="2">
@@ -2217,12 +2233,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MB003667</t>
+          <t>MB003668</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Light On Serum: centella + vitamina C 30 ml</t>
+          <t>Glow Deep Serum: arroz + alfa-arbutina 30 ml</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2231,7 +2247,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>92.90000000000001</v>
+        <v>110.9</v>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
@@ -2240,12 +2256,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Light On Serum : Centella + Vita C</t>
+          <t>Glow Deep Serum : Rice + Alpha-Arbutin</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>30 ml (1.01 FL. OZ.)</t>
+          <t>1.01 fl. oz.(30ml)</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
@@ -2259,7 +2275,7 @@
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/light-on-serum-centella-vita-c</t>
+          <t>https://beautyofjoseon.com/products/glow-deep-serum-rice-alpha-arbutin?variant=51833689211252</t>
         </is>
       </c>
       <c r="L31" s="2">
@@ -2274,12 +2290,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MB002804</t>
+          <t>MB003670</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lucky Pouch: nécessaire de seda inspirada no hanbok 15,5 x 21 cm · Maehwa Pink</t>
+          <t>Glow Serum: própolis + niacinamida 30 ml</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2288,7 +2304,7 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>65.90000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
@@ -2297,18 +2313,20 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lucky Pouch</t>
+          <t>Glow Serum : Propolis + Niacinamide</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Olive</t>
+          <t>1.01 fl. oz.(30ml)</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="I32" s="4" t="n"/>
+        <v>15.3</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>17</v>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2316,7 +2334,7 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/lucky-pouch?variant=40739135783077</t>
+          <t>https://beautyofjoseon.com/products/glow-serum-propolis-niacinamide?variant=51833681772916</t>
         </is>
       </c>
       <c r="L32" s="2">
@@ -2331,12 +2349,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MB002805</t>
+          <t>MB002812</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lucky Pouch: nécessaire de seda inspirada no hanbok 15,5 x 21 cm · Olive</t>
+          <t>Hanbok Scrunchie: elástico de cabelo de tecido em dois tons · Honey Green</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2345,7 +2363,7 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>65.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
@@ -2354,16 +2372,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lucky Pouch</t>
+          <t>Hanbok Scrunchie</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Olive</t>
+          <t>Honey Green</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I33" s="4" t="n"/>
       <c r="J33" t="inlineStr">
@@ -2373,7 +2391,7 @@
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/lucky-pouch?variant=40739135783077</t>
+          <t>https://beautyofjoseon.com/products/hanbok-scrunchie?variant=43160500928677</t>
         </is>
       </c>
       <c r="L33" s="2">
@@ -2388,12 +2406,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MB003666</t>
+          <t>MB002811</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Red Bean Water Gel: hidratante em gel de feijão vermelho 100 ml</t>
+          <t>Hanbok Scrunchie: elástico de cabelo de tecido em dois tons · Orchid pink</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2402,7 +2420,7 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>104.9</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
@@ -2411,20 +2429,18 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Red Bean Water Gel</t>
+          <t>Hanbok Scrunchie</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>100 ml (3.38 FL. OZ.)</t>
+          <t>Orchid pink</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>18</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="I34" s="4" t="n"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2432,7 +2448,7 @@
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/red-bean-water-gel</t>
+          <t>https://beautyofjoseon.com/products/hanbok-scrunchie?variant=43160500895909</t>
         </is>
       </c>
       <c r="L34" s="2">
@@ -2447,12 +2463,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MB003669</t>
+          <t>MB002801</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Revive Serum: ginseng + mucina de caracol 30 ml</t>
+          <t>Kit Night-Reset: gel de limpeza de ameixa verde + Dynasty Cream 50 ml</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2461,7 +2477,7 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>110.9</v>
+        <v>305.9</v>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
@@ -2470,28 +2486,22 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revive Eye Serum : Ginseng + Retinal</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>30ML X 2-PACK</t>
-        </is>
-      </c>
+          <t>Night-Reset Dewy Finish Kit</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" s="4" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>34</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="I35" s="4" t="n"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
+          <t>https://beautyofjoseon.com/products/night-restore-dewy-finish-night-skincare-set</t>
         </is>
       </c>
       <c r="L35" s="2">
@@ -2506,12 +2516,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MB003682</t>
+          <t>MB003680</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Revive Under Eye Patch: adesivos para olhos de ginseng + retinal, 60 unidades</t>
+          <t>Kit Revive Essentials: sérum para olhos, adesivos e hidratante firmador</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2520,7 +2530,7 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>144.9</v>
+        <v>332.9</v>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
@@ -2529,18 +2539,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revive Under Eye Patch: Ginseng + Retinal</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>100 g / 3.52 OZ. (60 Patches)</t>
-        </is>
-      </c>
+          <t>Revive Essentials Set</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I36" s="4" t="n"/>
+        <v>45.75</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>61</v>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2548,7 +2556,7 @@
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-under-eye-patch-global</t>
+          <t>https://beautyofjoseon.com/products/revive-essentials-set-global</t>
         </is>
       </c>
       <c r="L36" s="2">
@@ -2563,12 +2571,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MB003693</t>
+          <t>MB002831</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Trio Red Bean para Poros: sérum, máscara e gel hidratante</t>
+          <t>Kit Ritual Glow: rotina completa de 6 passos, do sabonete ao protetor</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2577,7 +2585,7 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>400.9</v>
+        <v>968.9</v>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
@@ -2586,22 +2594,22 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Red Bean Pore Care Trio</t>
+          <t>Rice Glow Ritual Set</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" s="4" t="n">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="I37" s="4" t="n"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/red-bean-pore-care-trio-eu</t>
+          <t>https://beautyofjoseon.com/products/rice-glow-ritual-radiant-skincare-set-global</t>
         </is>
       </c>
       <c r="L37" s="2">
@@ -2616,21 +2624,21 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MB003696</t>
+          <t>MB002767</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Hydra Shield FPS 50+: protetor solar para o corpo 150 ml</t>
+          <t>Kit Sun-Cleanse: Relief Sun FPS 50+ + gel de limpeza de ameixa verde</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>181.9</v>
+        <v>254.9</v>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
@@ -2639,16 +2647,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hydra Shield Body Sun Lotion SPF 50+</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>150 ml (5.07 FL. OZ.)</t>
-        </is>
-      </c>
+          <t>Sun-Cleanse Daily Defense Set</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" s="4" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I38" s="4" t="n"/>
       <c r="J38" t="inlineStr">
@@ -2658,7 +2662,7 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/hydra-shield-body-sun-lotion-spf-50-eu</t>
+          <t>https://beautyofjoseon.com/products/sun-cleanse-daily-shield-cleanser-sunscreen-set</t>
         </is>
       </c>
       <c r="L38" s="2">
@@ -2673,21 +2677,21 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MB004038</t>
+          <t>MB003667</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Relief Sun Aqua-Fresh FPS 50+ PA++++: protetor solar de arroz + B5, kit com 2 de 50 ml</t>
+          <t>Light On Serum: centella + vitamina C 30 ml</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>213.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
@@ -2696,26 +2700,26 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Relief Sun Aqua-Fresh : Rice + B5  (SPF50+ PA++++)</t>
+          <t>Light On Serum : Centella + Vita C</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1-Pack</t>
+          <t>30 ml (1.01 FL. OZ.)</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I39" s="4" t="n"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-aqua-fresh-rice-b5-spf50-pa-uk?variant=52419629646196</t>
+          <t>https://beautyofjoseon.com/products/light-on-serum-centella-vita-c</t>
         </is>
       </c>
       <c r="L39" s="2">
@@ -2730,21 +2734,21 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MB003646</t>
+          <t>MB002804</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Relief Sun: Rice + Probiotics (SPF 50+ PA++++)</t>
+          <t>Lucky Pouch: nécessaire de seda inspirada no hanbok 15,5 x 21 cm · Maehwa Pink</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>137.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
@@ -2753,26 +2757,26 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
+          <t>Lucky Pouch</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1-Pack</t>
+          <t>Maehwa Pink</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I40" s="4" t="n"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
+          <t>https://beautyofjoseon.com/products/lucky-pouch?variant=40739135750309</t>
         </is>
       </c>
       <c r="L40" s="2">
@@ -2787,21 +2791,21 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MB002781</t>
+          <t>MB002805</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Duo Relief Sun: Original + Aqua-Fresh</t>
+          <t>Lucky Pouch: nécessaire de seda inspirada no hanbok 15,5 x 21 cm · Olive</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>212.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
@@ -2810,24 +2814,26 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Relief Sun Duo : Original + Aqua-Fresh</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>Lucky Pouch</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Olive</t>
+        </is>
+      </c>
       <c r="H41" s="4" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>39</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="I41" s="4" t="n"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-duo-original-aqua-fresh-uk</t>
+          <t>https://beautyofjoseon.com/products/lucky-pouch?variant=40739135783077</t>
         </is>
       </c>
       <c r="L41" s="2">
@@ -2842,21 +2848,21 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MB002822</t>
+          <t>MB003669</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Glow Deep Serum: Arroz + Alfa-Arbutin · 1.01 fl. oz.(30ml)</t>
+          <t>Revive Serum: ginseng + mucina de caracol 30 ml</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>999.99</v>
+        <v>110.9</v>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
@@ -2865,18 +2871,20 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Glow Deep Serum : Rice + Alpha-Arbutin</t>
+          <t>Revive Eye Serum : Ginseng + Retinal</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.01 fl. oz.(30ml)</t>
+          <t>30ML X 2-PACK</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="I42" s="4" t="n"/>
+        <v>25.5</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>34</v>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2884,7 +2892,7 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/glow-deep-serum-rice-alpha-arbutin?variant=51833689211252</t>
+          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
         </is>
       </c>
       <c r="L42" s="2">
@@ -2899,20 +2907,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MB002823</t>
+          <t>MB003682</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Glow Deep Serum: Arroz + Alfa-Arbutin · 2.03 fl. oz.(60ml)</t>
+          <t>Revive Under Eye Patch: adesivos para olhos de ginseng + retinal, 60 unidades</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="n"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>144.9</v>
+      </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
@@ -2920,20 +2930,18 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Glow Deep Serum : Rice + Alpha-Arbutin</t>
+          <t>Revive Under Eye Patch: Ginseng + Retinal</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2.03 fl. oz.(60ml)</t>
+          <t>100 g / 3.52 OZ. (60 Patches)</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="I43" s="4" t="n">
-        <v>34</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I43" s="4" t="n"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2941,7 +2949,7 @@
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/glow-deep-serum-rice-alpha-arbutin?variant=51833689244020</t>
+          <t>https://beautyofjoseon.com/products/revive-under-eye-patch-global</t>
         </is>
       </c>
       <c r="L43" s="2">
@@ -2956,21 +2964,21 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MB003658</t>
+          <t>MB003693</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JELLOSKIN: creme de massagem para rosto e corpo</t>
+          <t>Trio Red Bean para Poros: sérum, máscara e gel hidratante</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>400.9</v>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
@@ -2979,20 +2987,14 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>JELLOSKIN Massage Cream For Face and Body</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>1-Pack</t>
-        </is>
-      </c>
+          <t>Red Bean Pore Care Trio</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" s="4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I44" s="4" t="n">
-        <v>25</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="I44" s="4" t="n"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>Esgotado</t>
@@ -3000,7 +3002,7 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/jelloskin-massage-cream-for-face-and-body</t>
+          <t>https://beautyofjoseon.com/products/red-bean-pore-care-trio-eu</t>
         </is>
       </c>
       <c r="L44" s="2">
@@ -3015,12 +3017,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MB003643</t>
+          <t>MB003648</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Relief Sun Aqua-Fresh Sunscreen: Rice + B5 (SPF 50+ PA++++)</t>
+          <t>Bastão Protetor Solar Matte: Artemísia + Camélia (FPS 50+ PA++++)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3029,7 +3031,7 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>137.9</v>
+        <v>163.9</v>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
@@ -3038,15 +3040,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Relief Sun Duo : Original + Aqua-Fresh</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>Matte Sun Stick : Mugwort+Camelia (SPF 50+ PA++++)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2-Pack</t>
+        </is>
+      </c>
       <c r="H45" s="4" t="n">
-        <v>29.25</v>
+        <v>22.5</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3055,7 +3061,7 @@
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-duo-original-aqua-fresh-uk</t>
+          <t>https://beautyofjoseon.com/products/matte-sun-stick-mugwort-camelia-duo</t>
         </is>
       </c>
       <c r="L45" s="2">
@@ -3070,12 +3076,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MB002782</t>
+          <t>MB002802</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Relief Sun Aqua-Fresh: Arroz + B5 (FPS 50+ PA++++) · 1-Pack</t>
+          <t>Bastão Solar Matte: Artemísia + Camélia (FPS 50+ PA++++) · 1-Pack</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3093,15 +3099,19 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Relief Sun Duo : Original + Aqua-Fresh</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>Matte Sun Stick : Mugwort+Camelia (SPF 50+ PA++++)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2-Pack</t>
+        </is>
+      </c>
       <c r="H46" s="4" t="n">
-        <v>29.25</v>
+        <v>22.5</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3110,7 +3120,7 @@
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-duo-original-aqua-fresh-uk</t>
+          <t>https://beautyofjoseon.com/products/matte-sun-stick-mugwort-camelia-duo</t>
         </is>
       </c>
       <c r="L46" s="2">
@@ -3125,12 +3135,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MB002783</t>
+          <t>MB002803</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Relief Sun Aqua-Fresh: Arroz + B5 (FPS 50+ PA++++) · 2-Pack</t>
+          <t>Bastão Solar Matte: Artemísia + Camélia (FPS 50+ PA++++) · 2-Pack</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3146,15 +3156,19 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Relief Sun Duo : Original + Aqua-Fresh</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>Matte Sun Stick : Mugwort+Camelia (SPF 50+ PA++++)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2-Pack</t>
+        </is>
+      </c>
       <c r="H47" s="4" t="n">
-        <v>29.25</v>
+        <v>22.5</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3163,7 +3177,7 @@
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-duo-original-aqua-fresh-uk</t>
+          <t>https://beautyofjoseon.com/products/matte-sun-stick-mugwort-camelia-duo</t>
         </is>
       </c>
       <c r="L47" s="2">
@@ -3178,12 +3192,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MB002785</t>
+          <t>MB003696</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Relief Sun: Arroz + Probióticos (FPS 50+ PA++++) · 1-Pack</t>
+          <t>Beauty of Joseon Hydra Shield FPS 50+: protetor solar para o corpo 150 ml</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3192,7 +3206,7 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>999.99</v>
+        <v>181.9</v>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
@@ -3201,16 +3215,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
+          <t>Hydra Shield Body Sun Lotion SPF 50+</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1-Pack</t>
+          <t>150 ml (5.07 FL. OZ.)</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I48" s="4" t="n"/>
       <c r="J48" t="inlineStr">
@@ -3220,7 +3234,7 @@
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
+          <t>https://beautyofjoseon.com/products/hydra-shield-body-sun-lotion-spf-50-eu</t>
         </is>
       </c>
       <c r="L48" s="2">
@@ -3235,12 +3249,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MB002786</t>
+          <t>MB004038</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Relief Sun: Arroz + Probióticos (FPS 50+ PA++++) · 2-Pack</t>
+          <t>Beauty of Joseon Relief Sun Aqua-Fresh FPS 50+ PA++++: protetor solar de arroz + B5, kit com 2 de 50 ml</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3248,7 +3262,9 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n"/>
+      <c r="D49" s="2" t="n">
+        <v>213.9</v>
+      </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
@@ -3256,7 +3272,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
+          <t>Relief Sun Aqua-Fresh : Rice + B5  (SPF50+ PA++++)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3265,7 +3281,7 @@
         </is>
       </c>
       <c r="H49" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I49" s="4" t="n"/>
       <c r="J49" t="inlineStr">
@@ -3275,7 +3291,7 @@
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
+          <t>https://beautyofjoseon.com/products/relief-sun-aqua-fresh-rice-b5-spf50-pa-uk?variant=52419629646196</t>
         </is>
       </c>
       <c r="L49" s="2">
@@ -3290,12 +3306,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MB002808</t>
+          <t>MB003646</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sérum Light On: Centella + Vitamina C</t>
+          <t>Beauty of Joseon Relief Sun: Rice + Probiotics (SPF 50+ PA++++)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3304,7 +3320,7 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>92.90000000000001</v>
+        <v>137.9</v>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
@@ -3313,26 +3329,26 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Light On Serum : Centella + Vita C</t>
+          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>30 ml (1.01 FL. OZ.)</t>
+          <t>1-Pack</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I50" s="4" t="n"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/light-on-serum-centella-vita-c</t>
+          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
         </is>
       </c>
       <c r="L50" s="2">
@@ -3347,12 +3363,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MB002770</t>
+          <t>MB003685</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sérum Revive: Ginseng + Muco de Caracol · 1.01 fl. oz.(30ml)</t>
+          <t>Creme Dynasty</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3361,7 +3377,7 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>92.90000000000001</v>
+        <v>174.9</v>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
@@ -3370,20 +3386,18 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revive Eye Serum : Ginseng + Retinal</t>
+          <t>Dynasty Cream</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>30ML X 2-PACK</t>
+          <t>1 fl.oz. (30ml)</t>
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="I51" s="4" t="n">
-        <v>34</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I51" s="4" t="n"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3391,7 +3405,7 @@
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
+          <t>https://beautyofjoseon.com/products/dynasty-cream?variant=54217328460148</t>
         </is>
       </c>
       <c r="L51" s="2">
@@ -3406,12 +3420,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MB002771</t>
+          <t>MB002841</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sérum Revive: Ginseng + Muco de Caracol · 2.03 fl. oz.(60ml)</t>
+          <t>Dayscreen Hidratante FPS 30 · 1-Pack</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3420,7 +3434,7 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>160.9</v>
+        <v>999.99</v>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
@@ -3429,28 +3443,26 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revive Serum : Ginseng + Snail Mucin</t>
+          <t>Dayscreen Moisturizer SPF 30</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2.03 fl. oz.(60ml)</t>
+          <t>1-Pack</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="I52" s="4" t="n">
-        <v>34</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I52" s="4" t="n"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-serum-ginseng-snail-mucin?variant=51833686065524</t>
+          <t>https://beautyofjoseon.com/products/dayscreen-moisturizer-sunscreen-global?variant=54406380159348</t>
         </is>
       </c>
       <c r="L52" s="2">
@@ -3465,49 +3477,49 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MB002834</t>
+          <t>MB002842</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dynasty Cream Mini: creme hidratante de arroz e ginseng 10 ml</t>
+          <t>Dayscreen Hidratante FPS 30 · 2-Pack</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+        <v>999.99</v>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dynasty Cream</t>
+          <t>Dayscreen Moisturizer SPF 30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1 fl.oz. (30ml)</t>
+          <t>2-Pack</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="I53" s="4" t="n"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/dynasty-cream?variant=54217328460148</t>
+          <t>https://beautyofjoseon.com/products/dayscreen-moisturizer-sunscreen-global?variant=54406380192116</t>
         </is>
       </c>
       <c r="L53" s="2">
@@ -3522,37 +3534,39 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MB002833</t>
+          <t>MB002781</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kit Dynasty Triple Barrier Lock: gel de limpeza, Dynasty Cream e Relief Sun</t>
+          <t>Duo Relief Sun: Original + Aqua-Fresh</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>452.9</v>
-      </c>
-      <c r="E54" s="8" t="inlineStr">
-        <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+        <v>212.9</v>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dynasty Triple Barrier Lock</t>
+          <t>Relief Sun Duo : Original + Aqua-Fresh</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="I54" s="4" t="n"/>
+        <v>29.25</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>39</v>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>Esgotado</t>
@@ -3560,7 +3574,7 @@
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/dynasty-triple-barrier-lock-skincare-routine-set</t>
+          <t>https://beautyofjoseon.com/products/relief-sun-duo-original-aqua-fresh-uk</t>
         </is>
       </c>
       <c r="L54" s="2">
@@ -3575,12 +3589,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MB002807</t>
+          <t>MB002773</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Light On Serum Mini: centella + vitamina C 10 ml</t>
+          <t>Duo Ritual Revive para a Área dos Olhos</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3589,35 +3603,33 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>999.99</v>
-      </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+        <v>201.9</v>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Light On Serum : Centella + Vita C</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>30 ml (1.01 FL. OZ.)</t>
-        </is>
-      </c>
+          <t>Revive Ritual Eye Duo</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="I55" s="4" t="n"/>
+        <v>27.75</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>37</v>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/light-on-serum-centella-vita-c</t>
+          <t>https://beautyofjoseon.com/products/revive-ritual-eye-duo-eu</t>
         </is>
       </c>
       <c r="L55" s="2">
@@ -3632,12 +3644,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MB002775</t>
+          <t>MB002787</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sérum para Olhos Revive Mini: ginseng + retinal 10 ml</t>
+          <t>Duo Solar Relax + Alívio</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3646,37 +3658,31 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+        <v>319.9</v>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Revive Eye Serum : Ginseng + Retinal</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>30ML X 2-PACK</t>
-        </is>
-      </c>
+          <t>Relax + Relief SPF Duo</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" s="4" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="I56" s="4" t="n">
-        <v>34</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="I56" s="4" t="n"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
+          <t>https://beautyofjoseon.com/products/relax-relief-spf-duo-eu</t>
         </is>
       </c>
       <c r="L56" s="2">
@@ -3691,47 +3697,49 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MB002824</t>
+          <t>MB002829</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Arroz Carregador Duo Glow</t>
+          <t>Essência Ginseng</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>169.9</v>
-      </c>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>116.9</v>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Guard Your Glow Duo</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
+          <t>Ginseng Essence Water</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>150 ml (5.07 FL. OZ.)</t>
+        </is>
+      </c>
       <c r="H57" s="4" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="I57" s="4" t="n">
-        <v>54</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I57" s="4" t="n"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/protect-your-glow-duo-global</t>
+          <t>https://beautyofjoseon.com/products/ginseng-essence-water</t>
         </is>
       </c>
       <c r="L57" s="2">
@@ -3746,47 +3754,49 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MB003677</t>
+          <t>MB002822</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Duo Relief Sun Original + Aqua-Fresh FPS 50+ PA++++: dupla de protetores solares 2 x 50 ml</t>
+          <t>Glow Deep Serum: Arroz + Alfa-Arbutin · 1.01 fl. oz.(30ml)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>212.9</v>
-      </c>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>999.99</v>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Relief Sun Duo : Original + Aqua-Fresh</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
+          <t>Glow Deep Serum : Rice + Alpha-Arbutin</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1.01 fl. oz.(30ml)</t>
+        </is>
+      </c>
       <c r="H58" s="4" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="I58" s="4" t="n">
-        <v>39</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I58" s="4" t="n"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-duo-original-aqua-fresh-uk</t>
+          <t>https://beautyofjoseon.com/products/glow-deep-serum-rice-alpha-arbutin?variant=51833689211252</t>
         </is>
       </c>
       <c r="L58" s="2">
@@ -3801,49 +3811,49 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MB003699</t>
+          <t>MB002823</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Glow Sun Stick FPS 50: protetor solar em bastão 14 g</t>
+          <t>Glow Deep Serum: Arroz + Alfa-Arbutin · 2.03 fl. oz.(60ml)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Glow Sun Stick</t>
+          <t>Glow Deep Serum : Rice + Alpha-Arbutin</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>14 g (0.49 OZ.)</t>
+          <t>2.03 fl. oz.(60ml)</t>
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I59" s="4" t="n"/>
+        <v>27.2</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>34</v>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/glow-sun-stick-sunscreen-stick</t>
+          <t>https://beautyofjoseon.com/products/glow-deep-serum-rice-alpha-arbutin?variant=51833689244020</t>
         </is>
       </c>
       <c r="L59" s="2">
@@ -3858,30 +3868,30 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MB002784</t>
+          <t>MB003658</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Relief Sun Aqua-Fresh Mini FPS 50+ PA++++: protetor solar de arroz + B5 10 ml</t>
+          <t>JELLOSKIN: creme de massagem para rosto e corpo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>90.90000000000001</v>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Relief Sun Aqua-Fresh : Rice + B5  (SPF50+ PA++++)</t>
+          <t>JELLOSKIN Massage Cream For Face and Body</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3890,9 +3900,11 @@
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="I60" s="4" t="n"/>
+        <v>12.5</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
           <t>Esgotado</t>
@@ -3900,7 +3912,7 @@
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-aqua-fresh-rice-b5-spf50-pa-uk?variant=52419629646196</t>
+          <t>https://beautyofjoseon.com/products/jelloskin-massage-cream-for-face-and-body</t>
         </is>
       </c>
       <c r="L60" s="2">
@@ -3915,39 +3927,41 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MB003653</t>
+          <t>MB002810</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Duo Glow de Arroz: Rice Milk + máscara de arroz com mel</t>
+          <t>Loção Solar Corporal Hydra Shield FPS 50+</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>170.9</v>
-      </c>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>181.9</v>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Guard Your Glow Duo</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
+          <t>Hydra Shield Body Sun Lotion SPF 50+</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>150 ml (5.07 FL. OZ.)</t>
+        </is>
+      </c>
       <c r="H61" s="4" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="I61" s="4" t="n">
-        <v>54</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="I61" s="4" t="n"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>Esgotado</t>
@@ -3955,7 +3969,7 @@
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/protect-your-glow-duo-global</t>
+          <t>https://beautyofjoseon.com/products/hydra-shield-body-sun-lotion-spf-50-eu</t>
         </is>
       </c>
       <c r="L61" s="2">
@@ -3970,47 +3984,51 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MB002772</t>
+          <t>MB003656</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Duo Revive Autocuidado</t>
+          <t>Máscara de Arroz Moído e Mel 150 ml</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>193.9</v>
-      </c>
-      <c r="E62" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>91.90000000000001</v>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revive Ritual Eye Duo</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>Ground Rice and Honey Glow Mask</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>150 ml (5.07 FL. OZ.)</t>
+        </is>
+      </c>
       <c r="H62" s="4" t="n">
-        <v>27.75</v>
+        <v>15.3</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-ritual-eye-duo-eu</t>
+          <t>https://beautyofjoseon.com/products/ground-rice-and-honey-glow-mask</t>
         </is>
       </c>
       <c r="L62" s="2">
@@ -4025,38 +4043,38 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MB003645</t>
+          <t>MB003643</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Duo Ritual Revive para os Olhos: sérum + adesivos</t>
+          <t>Relief Sun Aqua-Fresh Sunscreen: Rice + B5 (SPF 50+ PA++++)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>201.9</v>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>137.9</v>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revive Ritual Eye Duo</t>
+          <t>Relief Sun Duo : Original + Aqua-Fresh</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" s="4" t="n">
-        <v>27.75</v>
+        <v>29.25</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -4065,7 +4083,7 @@
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-ritual-eye-duo-eu</t>
+          <t>https://beautyofjoseon.com/products/relief-sun-duo-original-aqua-fresh-uk</t>
         </is>
       </c>
       <c r="L63" s="2">
@@ -4080,45 +4098,47 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MB002797</t>
+          <t>MB002782</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Gua Sha de Porcelana: ferramenta de massagem para rosto e corpo</t>
+          <t>Relief Sun Aqua-Fresh: Arroz + B5 (FPS 50+ PA++++) · 1-Pack</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>123.9</v>
-      </c>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>999.99</v>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Porcelain Gwalsa (Gua Sha)</t>
+          <t>Relief Sun Duo : Original + Aqua-Fresh</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="I64" s="4" t="n"/>
+        <v>29.25</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>39</v>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/porcelain-gwalsa-guasha</t>
+          <t>https://beautyofjoseon.com/products/relief-sun-duo-original-aqua-fresh-uk</t>
         </is>
       </c>
       <c r="L64" s="2">
@@ -4133,47 +4153,45 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MB002827</t>
+          <t>MB002783</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Kit Presente Ginseng Ritual: essência, sérum e adesivos para olhos + espelho</t>
+          <t>Relief Sun Aqua-Fresh: Arroz + B5 (FPS 50+ PA++++) · 2-Pack</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="n">
-        <v>327.9</v>
-      </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n"/>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ginseng Firming Ritual Set</t>
+          <t>Relief Sun Duo : Original + Aqua-Fresh</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" s="4" t="n">
-        <v>57</v>
+        <v>29.25</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/ginseng-firming-ritual-ginseng-retinol-skincare-set</t>
+          <t>https://beautyofjoseon.com/products/relief-sun-duo-original-aqua-fresh-uk</t>
         </is>
       </c>
       <c r="L65" s="2">
@@ -4188,47 +4206,49 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MB002779</t>
+          <t>MB002785</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kit Revive Essencial</t>
+          <t>Relief Sun: Arroz + Probióticos (FPS 50+ PA++++) · 1-Pack</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>332.9</v>
-      </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>999.99</v>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revive Essentials Set</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
+          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1-Pack</t>
+        </is>
+      </c>
       <c r="H66" s="4" t="n">
-        <v>45.75</v>
-      </c>
-      <c r="I66" s="4" t="n">
-        <v>61</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I66" s="4" t="n"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-essentials-set-global</t>
+          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
         </is>
       </c>
       <c r="L66" s="2">
@@ -4243,12 +4263,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MB002844</t>
+          <t>MB002786</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Day Dew FPS 50: protetor solar com ácido hialurônico e niacinamida 50 ml · 1-Pack</t>
+          <t>Relief Sun: Arroz + Probióticos (FPS 50+ PA++++) · 2-Pack</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4256,17 +4276,15 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n">
-        <v>105.9</v>
-      </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Day Dew Sunscreen</t>
+          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4275,19 +4293,17 @@
         </is>
       </c>
       <c r="H67" s="4" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="I67" s="4" t="n">
         <v>18</v>
       </c>
+      <c r="I67" s="4" t="n"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/day-dew-sunscreen?variant=53692453814644</t>
+          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
         </is>
       </c>
       <c r="L67" s="2">
@@ -4302,12 +4318,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MB002845</t>
+          <t>MB002819</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Day Dew FPS 50: protetor solar com ácido hialurônico e niacinamida 50 ml · 2-Pack</t>
+          <t>Sérum Iluminador: Própolis + Niacinamida · 1.01 fl. oz.(30ml)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4316,28 +4332,28 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>170.9</v>
-      </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>98.90000000000001</v>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Day Dew Sunscreen</t>
+          <t>Glow Serum : Propolis + Niacinamide</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2-Pack</t>
+          <t>1.01 fl. oz.(30ml)</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>27</v>
+        <v>15.3</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -4346,7 +4362,7 @@
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/day-dew-sunscreen?variant=53692453847412</t>
+          <t>https://beautyofjoseon.com/products/glow-serum-propolis-niacinamide?variant=51833681772916</t>
         </is>
       </c>
       <c r="L68" s="2">
@@ -4361,12 +4377,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MB003692</t>
+          <t>MB002820</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Dayscreen FPS 30: hidratante com protetor solar 60 ml</t>
+          <t>Sérum Iluminador: Própolis + Niacinamida · 2.03 fl. oz.(60ml)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4375,35 +4391,37 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>104.9</v>
-      </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>160.9</v>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dayscreen Moisturizer SPF 30</t>
+          <t>Glow Serum : Propolis + Niacinamide</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1-Pack</t>
+          <t>2.03 fl. oz.(60ml)</t>
         </is>
       </c>
       <c r="H69" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I69" s="4" t="n"/>
+        <v>27.2</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>34</v>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/dayscreen-moisturizer-sunscreen-global?variant=54406380159348</t>
+          <t>https://beautyofjoseon.com/products/glow-serum-propolis-niacinamide?variant=51833681805684</t>
         </is>
       </c>
       <c r="L69" s="2">
@@ -4418,12 +4436,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MB003679</t>
+          <t>MB002808</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Relief Sun FPS 50+ PA++++: protetor solar de arroz + probióticos 50 ml</t>
+          <t>Sérum Light On: Centella + Vitamina C</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4432,35 +4450,35 @@
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>92.90000000000001</v>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
+          <t>Light On Serum : Centella + Vita C</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1-Pack</t>
+          <t>30 ml (1.01 FL. OZ.)</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I70" s="4" t="n"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
+          <t>https://beautyofjoseon.com/products/light-on-serum-centella-vita-c</t>
         </is>
       </c>
       <c r="L70" s="2">
@@ -4475,12 +4493,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MB004030</t>
+          <t>MB002770</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Relief Sun FPS 50+ PA++++: protetor solar de arroz, kit com 2 de 50 ml</t>
+          <t>Sérum Revive: Ginseng + Muco de Caracol · 1.01 fl. oz.(30ml)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4489,35 +4507,35 @@
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>213.9</v>
-      </c>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>92.90000000000001</v>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
+          <t>Revive Serum : Ginseng + Snail Mucin</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1-Pack</t>
+          <t>1.01 fl. oz.(30ml)</t>
         </is>
       </c>
       <c r="H71" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I71" s="4" t="n"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
+          <t>https://beautyofjoseon.com/products/revive-serum-ginseng-snail-mucin?variant=51833686032756</t>
         </is>
       </c>
       <c r="L71" s="2">
@@ -4532,12 +4550,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MB002780</t>
+          <t>MB002771</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Relief Sun Mini FPS 50+ PA++++: protetor solar de arroz 10 ml</t>
+          <t>Sérum Revive: Ginseng + Muco de Caracol · 2.03 fl. oz.(60ml)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4546,35 +4564,37 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>160.9</v>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Matte Sun Stick : Mugwort+Camelia (SPF 50+ PA++++)</t>
+          <t>Revive Serum : Ginseng + Snail Mucin</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1-Pack</t>
+          <t>2.03 fl. oz.(60ml)</t>
         </is>
       </c>
       <c r="H72" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="I72" s="4" t="n"/>
+        <v>27.2</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>34</v>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/matte-sun-stick-mugwort-camelia-spf-50-pa-uk?variant=52419626303860</t>
+          <t>https://beautyofjoseon.com/products/revive-serum-ginseng-snail-mucin?variant=51833686065524</t>
         </is>
       </c>
       <c r="L72" s="2">
@@ -4589,12 +4609,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MB003663</t>
+          <t>MB003647</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bálsamo de Limpeza Radiance 100 ml</t>
+          <t>Sérum para Olhos Revive: Ginseng + Retina</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4603,27 +4623,29 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>160.9</v>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Radiance Cleansing Balm</t>
+          <t>Revive Eye Serum : Ginseng + Retinal</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>100 ml (3.38 FL. OZ.)</t>
+          <t>30ML X 2-PACK</t>
         </is>
       </c>
       <c r="H73" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="I73" s="4" t="n"/>
+        <v>25.5</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>34</v>
+      </c>
       <c r="J73" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4631,7 +4653,7 @@
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/radiance-cleansing-balm</t>
+          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
         </is>
       </c>
       <c r="L73" s="2">
@@ -4646,12 +4668,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MB003685</t>
+          <t>MB003683</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Creme Dynasty</t>
+          <t>Sérum para Olhos Revive: ginseng + retinal 30 ml</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4660,27 +4682,29 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>174.9</v>
-      </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>160.9</v>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dynasty Cream</t>
+          <t>Revive Eye Serum : Ginseng + Retinal</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1 fl.oz. (30ml)</t>
+          <t>30ML X 2-PACK</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="I74" s="4" t="n"/>
+        <v>25.5</v>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>34</v>
+      </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4688,7 +4712,7 @@
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/dynasty-cream?variant=54217328460148</t>
+          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
         </is>
       </c>
       <c r="L74" s="2">
@@ -4703,12 +4727,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MB002841</t>
+          <t>MB003665</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dayscreen Hidratante FPS 30 · 1-Pack</t>
+          <t>Tônico Refrescante de Ameixa Verde: AHA + BHA 150 ml</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4717,35 +4741,35 @@
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>999.99</v>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>104.9</v>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dayscreen Moisturizer SPF 30</t>
+          <t>Green Plum Refreshing Toner : AHA + BHA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>1-Pack</t>
+          <t>150 ml (5.07 FL. OZ.)</t>
         </is>
       </c>
       <c r="H75" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I75" s="4" t="n"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K75" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/dayscreen-moisturizer-sunscreen-global?variant=54406380159348</t>
+          <t>https://beautyofjoseon.com/products/green-plum-refreshing-toner-aha-bha</t>
         </is>
       </c>
       <c r="L75" s="2">
@@ -4760,39 +4784,39 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MB002842</t>
+          <t>MB002784</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Dayscreen Hidratante FPS 30 · 2-Pack</t>
+          <t>Beauty of Joseon Relief Sun Aqua-Fresh Mini FPS 50+ PA++++: protetor solar de arroz + B5 10 ml</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>999.99</v>
+        <v>26.9</v>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>Fraco — conferir</t>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dayscreen Moisturizer SPF 30</t>
+          <t>Relief Sun Aqua-Fresh : Rice + B5  (SPF50+ PA++++)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2-Pack</t>
+          <t>1-Pack</t>
         </is>
       </c>
       <c r="H76" s="4" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="I76" s="4" t="n"/>
       <c r="J76" t="inlineStr">
@@ -4802,7 +4826,7 @@
       </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/dayscreen-moisturizer-sunscreen-global?variant=54406380192116</t>
+          <t>https://beautyofjoseon.com/products/relief-sun-aqua-fresh-rice-b5-spf50-pa-uk?variant=52419629646196</t>
         </is>
       </c>
       <c r="L76" s="2">
@@ -4817,45 +4841,49 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MB003651</t>
+          <t>MB002834</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Duo Pele de Vidro: Glow Serum + Dynasty Cream</t>
+          <t>Dynasty Cream Mini: creme hidratante de arroz e ginseng 10 ml</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>194.9</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>Fraco — conferir</t>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Pick + Mix Serum Duo</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
+          <t>Dynasty Cream</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1 fl.oz. (30ml)</t>
+        </is>
+      </c>
       <c r="H77" s="4" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="I77" s="4" t="n"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Esgotado</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/pick-and-mix-serum-duo-skincare-set-eu-uk</t>
+          <t>https://beautyofjoseon.com/products/dynasty-cream?variant=54217328460148</t>
         </is>
       </c>
       <c r="L77" s="2">
@@ -4870,38 +4898,38 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MB002773</t>
+          <t>MB003649</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Duo Ritual Revive para a Área dos Olhos</t>
+          <t>Hanbang Serum Discovery Kit: 4 séruns mini de 10 ml</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>201.9</v>
+        <v>156.9</v>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>Fraco — conferir</t>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revive Ritual Eye Duo</t>
+          <t>Hanbang Serum Discovery Kit</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" s="4" t="n">
-        <v>27.75</v>
+        <v>21.6</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -4910,7 +4938,7 @@
       </c>
       <c r="K78" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-ritual-eye-duo-eu</t>
+          <t>https://beautyofjoseon.com/products/hanbang-serum-discovery-kit</t>
         </is>
       </c>
       <c r="L78" s="2">
@@ -4925,35 +4953,35 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MB002787</t>
+          <t>MB002833</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Duo Solar Relax + Alívio</t>
+          <t>Kit Dynasty Triple Barrier Lock: gel de limpeza, Dynasty Cream e Relief Sun</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>319.9</v>
+        <v>452.9</v>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>Fraco — conferir</t>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Relax + Relief SPF Duo</t>
+          <t>Dynasty Triple Barrier Lock</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" s="4" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I79" s="4" t="n"/>
       <c r="J79" t="inlineStr">
@@ -4963,7 +4991,7 @@
       </c>
       <c r="K79" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/relax-relief-spf-duo-eu</t>
+          <t>https://beautyofjoseon.com/products/dynasty-triple-barrier-lock-skincare-routine-set</t>
         </is>
       </c>
       <c r="L79" s="2">
@@ -4978,12 +5006,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MB002829</t>
+          <t>MB002873</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Essência Ginseng</t>
+          <t>Beauty of Joseon Protetor Solar Daily Relief FPS 40 · 1-Pack</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4992,35 +5020,33 @@
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>116.9</v>
+        <v>195.9</v>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>Fraco — conferir</t>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ginseng Essence Water</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>150 ml (5.07 FL. OZ.)</t>
-        </is>
-      </c>
+          <t>Daily Sun Duo SPF Set</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="I80" s="4" t="n"/>
+        <v>27</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>36</v>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/ginseng-essence-water</t>
+          <t>https://beautyofjoseon.com/products/all-day-sun-duo</t>
         </is>
       </c>
       <c r="L80" s="2">
@@ -5035,12 +5061,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MB003687</t>
+          <t>MB002780</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Paleta Hanbang: kit com os 4 séruns da marca</t>
+          <t>Beauty of Joseon Relief Sun Mini FPS 50+ PA++++: protetor solar de arroz 10 ml</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5049,25 +5075,27 @@
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>495.9</v>
+        <v>26.9</v>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>Fraco — conferir</t>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hanbang Serum Discovery Kit</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
+          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1-Pack</t>
+        </is>
+      </c>
       <c r="H81" s="4" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="I81" s="4" t="n">
-        <v>27</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I81" s="4" t="n"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>Esgotado</t>
@@ -5075,7 +5103,7 @@
       </c>
       <c r="K81" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/hanbang-serum-discovery-kit</t>
+          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
         </is>
       </c>
       <c r="L81" s="2">
@@ -5090,12 +5118,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MB002819</t>
+          <t>MB002807</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Sérum Iluminador: Própolis + Niacinamida · 1.01 fl. oz.(30ml)</t>
+          <t>Light On Serum Mini: centella + vitamina C 10 ml</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5104,29 +5132,27 @@
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>999.99</v>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>Fraco — conferir</t>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Revive Eye Serum : Ginseng + Retinal</t>
+          <t>Light On Serum : Centella + Vita C</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>30ML X 2-PACK</t>
+          <t>30 ml (1.01 FL. OZ.)</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="I82" s="4" t="n">
-        <v>34</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I82" s="4" t="n"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5134,7 +5160,7 @@
       </c>
       <c r="K82" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
+          <t>https://beautyofjoseon.com/products/light-on-serum-centella-vita-c</t>
         </is>
       </c>
       <c r="L82" s="2">
@@ -5149,12 +5175,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MB002820</t>
+          <t>MB002878</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Sérum Iluminador: Própolis + Niacinamida · 2.03 fl. oz.(60ml)</t>
+          <t>Sérum Calmante para a Barreira da Pele</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5163,29 +5189,27 @@
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>160.9</v>
+        <v>999.99</v>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>Fraco — conferir</t>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Glow Serum : Propolis + Niacinamide</t>
+          <t>Calming Barrier Serum : Green Tea-HA™ + Panthenol</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2.03 fl. oz.(60ml)</t>
+          <t>1.01 fl. oz.(30ml)</t>
         </is>
       </c>
       <c r="H83" s="4" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="I83" s="4" t="n">
-        <v>34</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I83" s="4" t="n"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5193,7 +5217,7 @@
       </c>
       <c r="K83" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/glow-serum-propolis-niacinamide?variant=51833681805684</t>
+          <t>https://beautyofjoseon.com/products/calming-barrier-serum</t>
         </is>
       </c>
       <c r="L83" s="2">
@@ -5208,12 +5232,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MB003647</t>
+          <t>MB002775</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sérum para Olhos Revive: Ginseng + Retina</t>
+          <t>Sérum para Olhos Revive Mini: ginseng + retinal 10 ml</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5222,11 +5246,11 @@
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>160.9</v>
+        <v>26.9</v>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>Fraco — conferir</t>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5267,21 +5291,21 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MB002776</t>
+          <t>MB003677</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sérum para Olhos Revive: Ginseng + Retinal · 30ml</t>
+          <t>Beauty of Joseon Duo Relief Sun Original + Aqua-Fresh FPS 50+ PA++++: dupla de protetores solares 2 x 50 ml</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>160.9</v>
+        <v>212.9</v>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
@@ -5290,28 +5314,24 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Revive Eye Serum : Ginseng + Retinal</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>30ML X 2-PACK</t>
-        </is>
-      </c>
+          <t>Relief Sun Duo : Original + Aqua-Fresh</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" s="4" t="n">
-        <v>25.5</v>
+        <v>29.25</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K85" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
+          <t>https://beautyofjoseon.com/products/relief-sun-duo-original-aqua-fresh-uk</t>
         </is>
       </c>
       <c r="L85" s="2">
@@ -5326,20 +5346,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MB002777</t>
+          <t>MB003699</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sérum para Olhos Revive: Ginseng + Retinal · 30ml x 2-Pack</t>
+          <t>Beauty of Joseon Glow Sun Stick FPS 50: protetor solar em bastão 14 g</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="n"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>144.9</v>
+      </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
@@ -5347,28 +5369,26 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Revive Eye Serum : Ginseng + Retinal</t>
+          <t>Glow Sun Stick</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>30ML X 2-PACK</t>
+          <t>14 g (0.49 OZ.)</t>
         </is>
       </c>
       <c r="H86" s="4" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="I86" s="4" t="n">
-        <v>34</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I86" s="4" t="n"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K86" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
+          <t>https://beautyofjoseon.com/products/glow-sun-stick-sunscreen-stick</t>
         </is>
       </c>
       <c r="L86" s="2">
@@ -5383,20 +5403,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MB002778</t>
+          <t>MB003700</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sérum para Olhos Revive: Ginseng + Retinal · 50ml x 2-Pack</t>
+          <t>Beauty of Joseon Tinted Mineral Dayscreen FPS 30: protetor solar mineral com cor 40 ml</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="n"/>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>145.9</v>
+      </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
@@ -5404,20 +5426,18 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Revive Eye Serum : Ginseng + Retinal</t>
+          <t>Tinted Mineral Dayscreen SPF 30</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>50ml x 2-Pack</t>
+          <t>15C</t>
         </is>
       </c>
       <c r="H87" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="I87" s="4" t="n">
-        <v>56</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="I87" s="4" t="n"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5425,7 +5445,7 @@
       </c>
       <c r="K87" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal?variant=54416123003252</t>
+          <t>https://beautyofjoseon.com/products/tinted-mineral-dayscreen-spf-30-global?variant=54870451323252</t>
         </is>
       </c>
       <c r="L87" s="2">
@@ -5440,21 +5460,21 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MB003683</t>
+          <t>MB003653</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Sérum para Olhos Revive: ginseng + retinal 30 ml</t>
+          <t>Duo Glow de Arroz: Rice Milk + máscara de arroz com mel</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>160.9</v>
+        <v>170.9</v>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
@@ -5463,19 +5483,15 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Revive Eye Serum : Ginseng + Retinal</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>30ML X 2-PACK</t>
-        </is>
-      </c>
+          <t>Glow Charging Rice Duo</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" s="4" t="n">
-        <v>25.5</v>
+        <v>27</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -5484,7 +5500,7 @@
       </c>
       <c r="K88" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/revive-eye-serum-ginseng-retinal-duo</t>
+          <t>https://beautyofjoseon.com/products/glow-charging-rice-duo</t>
         </is>
       </c>
       <c r="L88" s="2">
@@ -5499,21 +5515,21 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MB003662</t>
+          <t>MB002772</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Óleo de Limpeza de Ginseng 210 ml</t>
+          <t>Duo Revive Autocuidado</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>144.9</v>
+        <v>193.9</v>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
@@ -5522,26 +5538,24 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ginseng Cleansing Oil</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>210 ml (7.10 FL. OZ.)</t>
-        </is>
-      </c>
+          <t>Revive Ritual Eye Duo</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I89" s="4" t="n"/>
+        <v>27.75</v>
+      </c>
+      <c r="I89" s="4" t="n">
+        <v>37</v>
+      </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Esgotado</t>
         </is>
       </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
-          <t>https://beautyofjoseon.com/products/ginseng-cleansing-oil</t>
+          <t>https://beautyofjoseon.com/products/revive-ritual-eye-duo-eu</t>
         </is>
       </c>
       <c r="L89" s="2">
@@ -5556,12 +5570,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MB003695</t>
+          <t>MB003645</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Duo Radiant + Dewy FPS 50 e FPS 50+: Glow Sun Stick 14 g + Hydra Shield protetor corporal 150 ml</t>
+          <t>Duo Ritual Revive para os Olhos: sérum + adesivos</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5570,114 +5584,216 @@
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>319.9</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="n"/>
-      <c r="I90" s="4" t="n"/>
-      <c r="L90" s="2" t="n"/>
-      <c r="M90" s="6" t="n"/>
+        <v>201.9</v>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Revive Ritual Eye Duo</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" s="4" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="I90" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/revive-ritual-eye-duo-eu</t>
+        </is>
+      </c>
+      <c r="L90" s="2">
+        <f>ROUND(H90*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M90" s="6">
+        <f>IF(OR(D90="",L90=""),"",D90/L90-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MB002769</t>
+          <t>MB002797</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Adesivo para Olhos Revive: Ginseng + Retinal</t>
+          <t>Gua Sha de Porcelana: ferramenta de massagem para rosto e corpo</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H91" s="4" t="n"/>
+        <v>123.9</v>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Porcelain Gwalsa (Gua Sha)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" s="4" t="n">
+        <v>17</v>
+      </c>
       <c r="I91" s="4" t="n"/>
-      <c r="L91" s="2" t="n"/>
-      <c r="M91" s="6" t="n"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/porcelain-gwalsa-guasha</t>
+        </is>
+      </c>
+      <c r="L91" s="2">
+        <f>ROUND(H91*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M91" s="6">
+        <f>IF(OR(D91="",L91=""),"",D91/L91-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MB002818</t>
+          <t>MB002827</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Bastão Protetor Solar Glow</t>
+          <t>Kit Presente Ginseng Ritual: essência, sérum e adesivos para olhos + espelho</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="n"/>
-      <c r="I92" s="4" t="n"/>
-      <c r="L92" s="2" t="n"/>
-      <c r="M92" s="6" t="n"/>
+        <v>327.9</v>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Ginseng Firming Ritual Set</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="I92" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/ginseng-firming-ritual-ginseng-retinol-skincare-set</t>
+        </is>
+      </c>
+      <c r="L92" s="2">
+        <f>ROUND(H92*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M92" s="6">
+        <f>IF(OR(D92="",L92=""),"",D92/L92-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MB003648</t>
+          <t>MB002779</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bastão Protetor Solar Matte: Artemísia + Camélia (FPS 50+ PA++++)</t>
+          <t>Kit Revive Essencial</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>163.9</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H93" s="4" t="n"/>
-      <c r="I93" s="4" t="n"/>
-      <c r="L93" s="2" t="n"/>
-      <c r="M93" s="6" t="n"/>
+        <v>332.9</v>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Revive Essentials Set</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" s="4" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="I93" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/revive-essentials-set-global</t>
+        </is>
+      </c>
+      <c r="L93" s="2">
+        <f>ROUND(H93*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M93" s="6">
+        <f>IF(OR(D93="",L93=""),"",D93/L93-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MB002802</t>
+          <t>MB003674</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bastão Solar Matte: Artemísia + Camélia (FPS 50+ PA++++) · 1-Pack</t>
+          <t>Beauty of Joseon All Day Sun Duo FPS 50+ PA++++: Relief Sun 50 ml + Matte Sun Stick 18 g</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5686,27 +5802,57 @@
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>999.99</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="n"/>
-      <c r="I94" s="4" t="n"/>
-      <c r="L94" s="2" t="n"/>
-      <c r="M94" s="6" t="n"/>
+        <v>196.9</v>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Matte Sun Stick : Mugwort+Camelia (SPF 50+ PA++++)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2-Pack</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I94" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/matte-sun-stick-mugwort-camelia-duo</t>
+        </is>
+      </c>
+      <c r="L94" s="2">
+        <f>ROUND(H94*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M94" s="6">
+        <f>IF(OR(D94="",L94=""),"",D94/L94-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MB002803</t>
+          <t>MB003671</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bastão Solar Matte: Artemísia + Camélia (FPS 50+ PA++++) · 2-Pack</t>
+          <t>Beauty of Joseon Daily Tinted Fluid FPS 30: protetor solar mineral com cor</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5714,26 +5860,56 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="D95" s="2" t="n"/>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="n"/>
+      <c r="D95" s="2" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Tinted Mineral Dayscreen SPF 30</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>15C</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="I95" s="4" t="n"/>
-      <c r="L95" s="2" t="n"/>
-      <c r="M95" s="6" t="n"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/tinted-mineral-dayscreen-spf-30-global?variant=54870451323252</t>
+        </is>
+      </c>
+      <c r="L95" s="2">
+        <f>ROUND(H95*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M95" s="6">
+        <f>IF(OR(D95="",L95=""),"",D95/L95-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MB003674</t>
+          <t>MB003692</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Beauty of Joseon All Day Sun Duo FPS 50+ PA++++: Relief Sun 50 ml + Matte Sun Stick 18 g</t>
+          <t>Beauty of Joseon Dayscreen FPS 30: hidratante com protetor solar 60 ml</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5742,27 +5918,55 @@
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>196.9</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="n"/>
+        <v>104.9</v>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Dayscreen Moisturizer SPF 30</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>1-Pack</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="I96" s="4" t="n"/>
-      <c r="L96" s="2" t="n"/>
-      <c r="M96" s="6" t="n"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/dayscreen-moisturizer-sunscreen-global?variant=54406380159348</t>
+        </is>
+      </c>
+      <c r="L96" s="2">
+        <f>ROUND(H96*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M96" s="6">
+        <f>IF(OR(D96="",L96=""),"",D96/L96-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MB003697</t>
+          <t>MB003675</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Comfort Protection FPS 40: protetor solar mineral para o corpo 150 ml</t>
+          <t>Beauty of Joseon Ginseng Moist Sun Serum FPS 50+ PA++++: sérum solar hidratante</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5771,27 +5975,55 @@
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>181.9</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H97" s="4" t="n"/>
+        <v>112.9</v>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Matte Sun Stick : Mugwort+Camelia (SPF 50+ PA++++)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>1-Pack</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="n">
+        <v>19</v>
+      </c>
       <c r="I97" s="4" t="n"/>
-      <c r="L97" s="2" t="n"/>
-      <c r="M97" s="6" t="n"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/matte-sun-stick-mugwort-camelia-spf-50-pa-uk?variant=52419626303860</t>
+        </is>
+      </c>
+      <c r="L97" s="2">
+        <f>ROUND(H97*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M97" s="6">
+        <f>IF(OR(D97="",L97=""),"",D97/L97-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MB003671</t>
+          <t>MB002874</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Daily Tinted Fluid FPS 30: protetor solar mineral com cor</t>
+          <t>Beauty of Joseon Protetor Solar Daily Relief FPS 40 · 2-Pack</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5800,27 +6032,53 @@
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="n"/>
-      <c r="I98" s="4" t="n"/>
-      <c r="L98" s="2" t="n"/>
-      <c r="M98" s="6" t="n"/>
+        <v>195.9</v>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Daily Sun Duo SPF Set</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="I98" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/all-day-sun-duo</t>
+        </is>
+      </c>
+      <c r="L98" s="2">
+        <f>ROUND(H98*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M98" s="6">
+        <f>IF(OR(D98="",L98=""),"",D98/L98-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MB002843</t>
+          <t>MB003679</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Day Dew Mini FPS 50: protetor solar 10 ml</t>
+          <t>Beauty of Joseon Relief Sun FPS 50+ PA++++: protetor solar de arroz + probióticos 50 ml</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5829,27 +6087,55 @@
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>104.9</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H99" s="4" t="n"/>
+        <v>137.9</v>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1-Pack</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="n">
+        <v>18</v>
+      </c>
       <c r="I99" s="4" t="n"/>
-      <c r="L99" s="2" t="n"/>
-      <c r="M99" s="6" t="n"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
+        </is>
+      </c>
+      <c r="L99" s="2">
+        <f>ROUND(H99*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M99" s="6">
+        <f>IF(OR(D99="",L99=""),"",D99/L99-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MB003694</t>
+          <t>MB004030</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Duo Relax + Relief FPS 50+ PA++++ e FPS 40: Relief Sun 50 ml + protetor corporal mineral 150 ml</t>
+          <t>Beauty of Joseon Relief Sun FPS 50+ PA++++: protetor solar de arroz, kit com 2 de 50 ml</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5858,27 +6144,55 @@
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>319.9</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="n"/>
+        <v>213.9</v>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Relief Sun : Rice + Niacinamide (SPF50+ PA++++)</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>1-Pack</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="n">
+        <v>18</v>
+      </c>
       <c r="I100" s="4" t="n"/>
-      <c r="L100" s="2" t="n"/>
-      <c r="M100" s="6" t="n"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/relief-sun-rice-probiotics?variant=43264254476453</t>
+        </is>
+      </c>
+      <c r="L100" s="2">
+        <f>ROUND(H100*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M100" s="6">
+        <f>IF(OR(D100="",L100=""),"",D100/L100-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MB002806</t>
+          <t>MB002768</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Duo de Protetores Leves Day Dew FPS 50 + Dayscreen FPS 30: protetores solares 50 ml + 60 ml</t>
+          <t>Duo Arroz Alívio</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5887,27 +6201,51 @@
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>166.9</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H101" s="4" t="n"/>
+        <v>999.99</v>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Relax + Relief SPF Duo</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" s="4" t="n">
+        <v>44</v>
+      </c>
       <c r="I101" s="4" t="n"/>
-      <c r="L101" s="2" t="n"/>
-      <c r="M101" s="6" t="n"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/relax-relief-spf-duo-eu</t>
+        </is>
+      </c>
+      <c r="L101" s="2">
+        <f>ROUND(H101*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M101" s="6">
+        <f>IF(OR(D101="",L101=""),"",D101/L101-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MB003675</t>
+          <t>MB002880</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Ginseng Moist Sun Serum FPS 50+ PA++++: sérum solar hidratante</t>
+          <t>Duo Iluminador e Firmador</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5916,27 +6254,57 @@
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>112.9</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="n"/>
-      <c r="I102" s="4" t="n"/>
-      <c r="L102" s="2" t="n"/>
-      <c r="M102" s="6" t="n"/>
+        <v>999.99</v>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Glow Boosting Duo</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1.01 fl. oz.(30ml)</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="I102" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/glow-boosting-duo?variant=51833735315828</t>
+        </is>
+      </c>
+      <c r="L102" s="2">
+        <f>ROUND(H102*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M102" s="6">
+        <f>IF(OR(D102="",L102=""),"",D102/L102-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MB002873</t>
+          <t>MB003651</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Protetor Solar Daily Relief FPS 40 · 1-Pack</t>
+          <t>Duo Pele de Vidro: Glow Serum + Dynasty Cream</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5945,27 +6313,57 @@
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>195.9</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H103" s="4" t="n"/>
-      <c r="I103" s="4" t="n"/>
-      <c r="L103" s="2" t="n"/>
-      <c r="M103" s="6" t="n"/>
+        <v>194.9</v>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Glass Skin Duo</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="I103" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/glass-skin-duo-us?variant=55226029965684</t>
+        </is>
+      </c>
+      <c r="L103" s="2">
+        <f>ROUND(H103*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M103" s="6">
+        <f>IF(OR(D103="",L103=""),"",D103/L103-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MB002874</t>
+          <t>MB002795</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Protetor Solar Daily Relief FPS 40 · 2-Pack</t>
+          <t>Duo Protege o Seu Brilho</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5974,27 +6372,57 @@
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>195.9</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="n"/>
-      <c r="I104" s="4" t="n"/>
-      <c r="L104" s="2" t="n"/>
-      <c r="M104" s="6" t="n"/>
+        <v>314.9</v>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Glow Boosting Duo</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>1.01 fl. oz.(30ml)</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="I104" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/glow-boosting-duo?variant=51833735315828</t>
+        </is>
+      </c>
+      <c r="L104" s="2">
+        <f>ROUND(H104*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M104" s="6">
+        <f>IF(OR(D104="",L104=""),"",D104/L104-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MB002752</t>
+          <t>MB003642</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 15C</t>
+          <t>Duo Revitalizante para os Olhos</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6003,27 +6431,53 @@
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H105" s="4" t="n"/>
-      <c r="I105" s="4" t="n"/>
-      <c r="L105" s="2" t="n"/>
-      <c r="M105" s="6" t="n"/>
+        <v>201.9</v>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Revive Ritual Eye Duo</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" s="4" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="I105" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/revive-ritual-eye-duo-eu</t>
+        </is>
+      </c>
+      <c r="L105" s="2">
+        <f>ROUND(H105*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M105" s="6">
+        <f>IF(OR(D105="",L105=""),"",D105/L105-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MB002753</t>
+          <t>MB002793</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 17N</t>
+          <t>Duo Solar Radiante + Iluminado</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6032,27 +6486,53 @@
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H106" s="4" t="n"/>
-      <c r="I106" s="4" t="n"/>
-      <c r="L106" s="2" t="n"/>
-      <c r="M106" s="6" t="n"/>
+        <v>319.9</v>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Lightweight Sun Duo</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" s="4" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="I106" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/lightweight-sun-duo-skincare-set</t>
+        </is>
+      </c>
+      <c r="L106" s="2">
+        <f>ROUND(H106*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M106" s="6">
+        <f>IF(OR(D106="",L106=""),"",D106/L106-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MB002754</t>
+          <t>MB002840</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 21W</t>
+          <t>Duo de Limpeza Dupla Profunda · Large</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6061,27 +6541,57 @@
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H107" s="4" t="n"/>
-      <c r="I107" s="4" t="n"/>
-      <c r="L107" s="2" t="n"/>
-      <c r="M107" s="6" t="n"/>
+        <v>217.9</v>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Deep Double Cleansing Duo</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I107" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/deep-double-cleansing-duo?variant=53445561614708</t>
+        </is>
+      </c>
+      <c r="L107" s="2">
+        <f>ROUND(H107*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M107" s="6">
+        <f>IF(OR(D107="",L107=""),"",D107/L107-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MB002755</t>
+          <t>MB002839</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 23N</t>
+          <t>Duo de Limpeza Dupla Profunda · Original</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6090,27 +6600,57 @@
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H108" s="4" t="n"/>
-      <c r="I108" s="4" t="n"/>
-      <c r="L108" s="2" t="n"/>
-      <c r="M108" s="6" t="n"/>
+        <v>155.9</v>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Deep Double Cleansing Duo</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="I108" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/deep-double-cleansing-duo?variant=53445561581940</t>
+        </is>
+      </c>
+      <c r="L108" s="2">
+        <f>ROUND(H108*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M108" s="6">
+        <f>IF(OR(D108="",L108=""),"",D108/L108-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MB002756</t>
+          <t>MB002885</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 25W</t>
+          <t>Duo de Protetor Solar para o Dia Todo</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6119,27 +6659,53 @@
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H109" s="4" t="n"/>
-      <c r="I109" s="4" t="n"/>
-      <c r="L109" s="2" t="n"/>
-      <c r="M109" s="6" t="n"/>
+        <v>999.99</v>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Lightweight Sun Duo</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" s="4" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="I109" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/lightweight-sun-duo-skincare-set</t>
+        </is>
+      </c>
+      <c r="L109" s="2">
+        <f>ROUND(H109*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M109" s="6">
+        <f>IF(OR(D109="",L109=""),"",D109/L109-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MB002757</t>
+          <t>MB002790</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 29N</t>
+          <t>Gel de Água de Feijão Azuki</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6148,27 +6714,57 @@
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="n"/>
-      <c r="I110" s="4" t="n"/>
-      <c r="L110" s="2" t="n"/>
-      <c r="M110" s="6" t="n"/>
+        <v>104.9</v>
+      </c>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Red Bean Water Gel</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>100 ml (3.38 FL. OZ.)</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I110" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/red-bean-water-gel</t>
+        </is>
+      </c>
+      <c r="L110" s="2">
+        <f>ROUND(H110*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M110" s="6">
+        <f>IF(OR(D110="",L110=""),"",D110/L110-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MB002758</t>
+          <t>MB002774</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 33N</t>
+          <t>Hidratante Firmador Revive: Ginseng + Retinol</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6177,27 +6773,57 @@
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H111" s="4" t="n"/>
-      <c r="I111" s="4" t="n"/>
-      <c r="L111" s="2" t="n"/>
-      <c r="M111" s="6" t="n"/>
+        <v>139.9</v>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Revive Firming Moisturizer : Ginseng + Retinol</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>60 ml (2.02 FL. OZ.)</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="I111" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/revive-firming-moisturizer</t>
+        </is>
+      </c>
+      <c r="L111" s="2">
+        <f>ROUND(H111*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M111" s="6">
+        <f>IF(OR(D111="",L111=""),"",D111/L111-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MB002759</t>
+          <t>MB003684</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 35N</t>
+          <t>Hidratante Firmador Revive: ginseng + retinol 60 ml</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6206,27 +6832,57 @@
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H112" s="4" t="n"/>
-      <c r="I112" s="4" t="n"/>
-      <c r="L112" s="2" t="n"/>
-      <c r="M112" s="6" t="n"/>
+        <v>139.9</v>
+      </c>
+      <c r="E112" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Revive Firming Moisturizer : Ginseng + Retinol</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>60 ml (2.02 FL. OZ.)</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="I112" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/revive-firming-moisturizer</t>
+        </is>
+      </c>
+      <c r="L112" s="2">
+        <f>ROUND(H112*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M112" s="6">
+        <f>IF(OR(D112="",L112=""),"",D112/L112-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MB002760</t>
+          <t>MB002821</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 39W</t>
+          <t>Leite de Arroz Reabastecedor Glow</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6235,27 +6891,57 @@
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H113" s="4" t="n"/>
-      <c r="I113" s="4" t="n"/>
-      <c r="L113" s="2" t="n"/>
-      <c r="M113" s="6" t="n"/>
+        <v>90.90000000000001</v>
+      </c>
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Glow Replenishing Rice Milk</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>150 ml (5.07 FL. OZ.)</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="I113" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/glow-replenishing-rice-milk</t>
+        </is>
+      </c>
+      <c r="L113" s="2">
+        <f>ROUND(H113*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M113" s="6">
+        <f>IF(OR(D113="",L113=""),"",D113/L113-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MB002761</t>
+          <t>MB002879</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 43W</t>
+          <t>Máscara Calmante de Barreira</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6264,27 +6950,55 @@
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H114" s="4" t="n"/>
+        <v>181.9</v>
+      </c>
+      <c r="E114" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Calming Barrier Mask</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>18 mL / 0.60 FL. OZ. (10 Sheets)</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="I114" s="4" t="n"/>
-      <c r="L114" s="2" t="n"/>
-      <c r="M114" s="6" t="n"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/calming-barrier-sheet-mask-global</t>
+        </is>
+      </c>
+      <c r="L114" s="2">
+        <f>ROUND(H114*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M114" s="6">
+        <f>IF(OR(D114="",L114=""),"",D114/L114-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MB002762</t>
+          <t>MB002877</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 45N</t>
+          <t>Máscara Calmante de Centella Asiática (10 unidades)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6293,27 +7007,55 @@
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H115" s="4" t="n"/>
+        <v>999.99</v>
+      </c>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Calming Barrier Mask</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>18 mL / 0.60 FL. OZ. (10 Sheets)</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="n">
+        <v>25</v>
+      </c>
       <c r="I115" s="4" t="n"/>
-      <c r="L115" s="2" t="n"/>
-      <c r="M115" s="6" t="n"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/calming-barrier-sheet-mask-global</t>
+        </is>
+      </c>
+      <c r="L115" s="2">
+        <f>ROUND(H115*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M115" s="6">
+        <f>IF(OR(D115="",L115=""),"",D115/L115-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MB002763</t>
+          <t>MB002814</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 47N</t>
+          <t>Máscara Facial Esfoliante Iluminadora de Arroz e Mel</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6322,27 +7064,57 @@
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="n"/>
-      <c r="I116" s="4" t="n"/>
-      <c r="L116" s="2" t="n"/>
-      <c r="M116" s="6" t="n"/>
+        <v>90.90000000000001</v>
+      </c>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Ground Rice and Honey Glow Mask</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>150 ml (5.07 FL. OZ.)</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="I116" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/ground-rice-and-honey-glow-mask</t>
+        </is>
+      </c>
+      <c r="L116" s="2">
+        <f>ROUND(H116*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M116" s="6">
+        <f>IF(OR(D116="",L116=""),"",D116/L116-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MB002764</t>
+          <t>MB003655</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 51N</t>
+          <t>Máscara Refrescante de Poros de Feijão Vermelho 140 ml</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6351,27 +7123,55 @@
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H117" s="4" t="n"/>
+        <v>116.9</v>
+      </c>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Red Bean Refreshing Pore Mask</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>140 ml (4.73 FL. OZ.)</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="I117" s="4" t="n"/>
-      <c r="L117" s="2" t="n"/>
-      <c r="M117" s="6" t="n"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/red-bean-refreshing-pore-mask</t>
+        </is>
+      </c>
+      <c r="L117" s="2">
+        <f>ROUND(H117*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M117" s="6">
+        <f>IF(OR(D117="",L117=""),"",D117/L117-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MB002765</t>
+          <t>MB003687</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 54N</t>
+          <t>Paleta Hanbang: kit com os 4 séruns da marca</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6380,27 +7180,53 @@
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="n"/>
-      <c r="I118" s="4" t="n"/>
-      <c r="L118" s="2" t="n"/>
-      <c r="M118" s="6" t="n"/>
+        <v>495.9</v>
+      </c>
+      <c r="E118" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Hanbang Serum Discovery Kit</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" s="4" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="I118" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/hanbang-serum-discovery-kit</t>
+        </is>
+      </c>
+      <c r="L118" s="2">
+        <f>ROUND(H118*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M118" s="6">
+        <f>IF(OR(D118="",L118=""),"",D118/L118-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MB002766</t>
+          <t>MB003691</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 59N</t>
+          <t>Sérum Calmante Barreira: Green Tea-HA + pantenol 30 ml</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6409,27 +7235,55 @@
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H119" s="4" t="n"/>
+        <v>99.90000000000001</v>
+      </c>
+      <c r="E119" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Calming Barrier Serum : Green Tea-HA™ + Panthenol</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>1.01 fl. oz.(30ml)</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="n">
+        <v>17</v>
+      </c>
       <c r="I119" s="4" t="n"/>
-      <c r="L119" s="2" t="n"/>
-      <c r="M119" s="6" t="n"/>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/calming-barrier-serum</t>
+        </is>
+      </c>
+      <c r="L119" s="2">
+        <f>ROUND(H119*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M119" s="6">
+        <f>IF(OR(D119="",L119=""),"",D119/L119-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MB003644</t>
+          <t>MB002815</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Beauty of Joseon: Filtro Solar com Arroz + Probióticos (FPS 50+ PA++++)</t>
+          <t>Tônico Refrescante de Ameixa Verde: AHA + BHA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -6438,36 +7292,64 @@
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H120" s="4" t="n"/>
+        <v>999.99</v>
+      </c>
+      <c r="E120" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Green Plum Refreshing Toner : AHA + BHA</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>150 ml (5.07 FL. OZ.)</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="n">
+        <v>18</v>
+      </c>
       <c r="I120" s="4" t="n"/>
-      <c r="L120" s="2" t="n"/>
-      <c r="M120" s="6" t="n"/>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t>https://beautyofjoseon.com/products/green-plum-refreshing-toner-aha-bha</t>
+        </is>
+      </c>
+      <c r="L120" s="2">
+        <f>ROUND(H120*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M120" s="6">
+        <f>IF(OR(D120="",L120=""),"",D120/L120-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MB002794</t>
+          <t>MB003695</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Bálsamo de Limpeza Radiance</t>
+          <t>Beauty of Joseon Duo Radiant + Dewy FPS 50 e FPS 50+: Glow Sun Stick 14 g + Hydra Shield protetor corporal 150 ml</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>82.90000000000001</v>
+        <v>319.9</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -6482,12 +7364,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MB002863</t>
+          <t>MB003697</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · DN310 / 50ml</t>
+          <t>Beauty of Joseon Comfort Protection FPS 40: protetor solar mineral para o corpo 150 ml</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6496,7 +7378,7 @@
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>181.9</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -6511,12 +7393,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MB002864</t>
+          <t>MB002844</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · DN310 / 7ml</t>
+          <t>Beauty of Joseon Day Dew FPS 50: protetor solar com ácido hialurônico e niacinamida 50 ml · 1-Pack</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -6525,7 +7407,7 @@
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>28.9</v>
+        <v>105.9</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -6540,12 +7422,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MB002869</t>
+          <t>MB002845</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · DN350 / 50ml</t>
+          <t>Beauty of Joseon Day Dew FPS 50: protetor solar com ácido hialurônico e niacinamida 50 ml · 2-Pack</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6554,7 +7436,7 @@
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>170.9</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -6569,12 +7451,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MB002870</t>
+          <t>MB002843</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · DN350 / 7ml</t>
+          <t>Beauty of Joseon Day Dew Mini FPS 50: protetor solar 10 ml</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -6583,7 +7465,7 @@
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>28.9</v>
+        <v>104.9</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -6598,12 +7480,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MB002865</t>
+          <t>MB003694</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · DP320 / 50ml</t>
+          <t>Beauty of Joseon Duo Relax + Relief FPS 50+ PA++++ e FPS 40: Relief Sun 50 ml + protetor corporal mineral 150 ml</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -6612,7 +7494,7 @@
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>319.9</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -6627,12 +7509,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MB002866</t>
+          <t>MB002806</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · DP320 / 7ml</t>
+          <t>Beauty of Joseon Duo de Protetores Leves Day Dew FPS 50 + Dayscreen FPS 30: protetores solares 50 ml + 60 ml</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -6641,7 +7523,7 @@
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>28.9</v>
+        <v>166.9</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -6656,12 +7538,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MB002861</t>
+          <t>MB002752</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · DY300 / 50ml</t>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 15C</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -6670,7 +7552,7 @@
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>144.9</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -6685,12 +7567,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MB002862</t>
+          <t>MB002753</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · DY300 / 7ml</t>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 17N</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -6699,7 +7581,7 @@
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>28.9</v>
+        <v>144.9</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -6714,12 +7596,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MB002867</t>
+          <t>MB002754</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · DY330 / 50ml</t>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 21W</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -6728,7 +7610,7 @@
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>144.9</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -6743,12 +7625,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MB002868</t>
+          <t>MB002755</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · DY330 / 7ml</t>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 23N</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -6757,7 +7639,7 @@
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>28.9</v>
+        <v>144.9</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -6772,12 +7654,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MB002849</t>
+          <t>MB002756</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · LN110 / 50ml</t>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 25W</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -6786,7 +7668,7 @@
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>144.9</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -6801,12 +7683,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MB002850</t>
+          <t>MB002757</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · LN110 / 7ml</t>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 29N</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -6815,7 +7697,7 @@
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>28.9</v>
+        <v>144.9</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -6830,12 +7712,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MB002847</t>
+          <t>MB002758</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · LP100 / 50ml</t>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 33N</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -6844,7 +7726,7 @@
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>144.9</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -6859,12 +7741,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MB002848</t>
+          <t>MB002759</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · LP100 / 7ml</t>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 35N</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -6873,7 +7755,7 @@
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>28.9</v>
+        <v>144.9</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -6888,12 +7770,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MB002851</t>
+          <t>MB002760</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · LP110 / 50ml</t>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 39W</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -6902,7 +7784,7 @@
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>144.9</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -6917,12 +7799,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MB002852</t>
+          <t>MB002761</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · LP110 / 7ml</t>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 43W</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -6931,7 +7813,7 @@
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>28.9</v>
+        <v>144.9</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -6946,12 +7828,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MB002859</t>
+          <t>MB002762</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · MN230 / 50ml</t>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 45N</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -6960,7 +7842,7 @@
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>144.9</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -6975,12 +7857,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MB002860</t>
+          <t>MB002763</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · MN230 / 7ml</t>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 47N</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -6989,7 +7871,7 @@
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>28.9</v>
+        <v>144.9</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -7004,12 +7886,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MB002853</t>
+          <t>MB002764</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · MP200 / 50ml</t>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 51N</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7018,7 +7900,7 @@
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>144.9</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -7033,12 +7915,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MB002854</t>
+          <t>MB002765</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · MP200 / 7ml</t>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 54N</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -7047,7 +7929,7 @@
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>28.9</v>
+        <v>144.9</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -7062,12 +7944,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MB002855</t>
+          <t>MB002766</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · MY210 / 50ml</t>
+          <t>Beauty of Joseon Protetor Solar Tonalizante com Cor FPS 30 · 59N</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -7076,7 +7958,7 @@
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>144.9</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -7091,12 +7973,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MB002856</t>
+          <t>MB003644</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · MY210 / 7ml</t>
+          <t>Beauty of Joseon: Filtro Solar com Arroz + Probióticos (FPS 50+ PA++++)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -7105,7 +7987,7 @@
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>28.9</v>
+        <v>137.9</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -7120,12 +8002,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MB002857</t>
+          <t>MB002863</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · MY220 / 50ml</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · DN310 / 50ml</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -7149,12 +8031,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MB002858</t>
+          <t>MB002864</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Daily Tinted Fluid: protetor solar fluido com cor · MY220 / 7ml</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · DN310 / 7ml</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -7178,12 +8060,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MB002768</t>
+          <t>MB002869</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Duo Arroz Alívio</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · DN350 / 50ml</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -7192,7 +8074,7 @@
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>999.99</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -7207,12 +8089,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MB003673</t>
+          <t>MB002870</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Duo Dia e Noite: Relief Sun FPS 50+ PA++++ + Dynasty Cream</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · DN350 / 7ml</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -7221,7 +8103,7 @@
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>305.9</v>
+        <v>28.9</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -7236,12 +8118,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MB003652</t>
+          <t>MB002865</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Duo Dupla Limpeza: óleo de ginseng + gel de ameixa verde</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · DP320 / 50ml</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -7250,7 +8132,7 @@
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>155.9</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -7265,12 +8147,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>MB002872</t>
+          <t>MB002866</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Duo Escudo Diário e Hidratação Profunda</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · DP320 / 7ml</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -7279,7 +8161,7 @@
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>999.99</v>
+        <v>28.9</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -7294,12 +8176,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>MB002880</t>
+          <t>MB002861</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Duo Iluminador e Firmador</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · DY300 / 50ml</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -7308,7 +8190,7 @@
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>999.99</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -7323,12 +8205,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>MB003650</t>
+          <t>MB002862</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Duo Iluminador e Firmador: Light On Serum + Revive Eye Serum</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · DY300 / 7ml</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -7337,7 +8219,7 @@
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>148.9</v>
+        <v>28.9</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -7352,12 +8234,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MB002795</t>
+          <t>MB002867</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Duo Protege o Seu Brilho</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · DY330 / 50ml</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7366,7 +8248,7 @@
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>314.9</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -7381,12 +8263,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MB003689</t>
+          <t>MB002868</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Duo Proteja o Seu Brilho: Glow Serum + Dayscreen FPS 30</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · DY330 / 7ml</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7395,7 +8277,7 @@
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>315.9</v>
+        <v>28.9</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -7410,12 +8292,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MB003688</t>
+          <t>MB002849</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Duo Proteção Diária e Hidratação Profunda: Dynasty Cream + Dayscreen FPS 30</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · LN110 / 50ml</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7424,7 +8306,7 @@
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>256.9</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -7439,12 +8321,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>MB002789</t>
+          <t>MB002850</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Duo Refinador de Poros</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · LN110 / 7ml</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -7453,7 +8335,7 @@
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>999.99</v>
+        <v>28.9</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -7468,12 +8350,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MB003654</t>
+          <t>MB002847</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Duo Refinador de Poros: máscaras de feijão vermelho e de arroz com mel</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · LP100 / 50ml</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7482,7 +8364,7 @@
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>180.9</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -7497,12 +8379,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MB003642</t>
+          <t>MB002848</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Duo Revitalizante para os Olhos</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · LP100 / 7ml</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7511,7 +8393,7 @@
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>201.9</v>
+        <v>28.9</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -7526,12 +8408,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>MB002793</t>
+          <t>MB002851</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Duo Solar Radiante + Iluminado</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · LP110 / 50ml</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -7540,7 +8422,7 @@
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>319.9</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -7555,12 +8437,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>MB002840</t>
+          <t>MB002852</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Duo de Limpeza Dupla Profunda · Large</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · LP110 / 7ml</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -7569,7 +8451,7 @@
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>217.9</v>
+        <v>28.9</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -7584,12 +8466,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MB002839</t>
+          <t>MB002859</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Duo de Limpeza Dupla Profunda · Original</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · MN230 / 50ml</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7598,7 +8480,7 @@
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>155.9</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -7613,12 +8495,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>MB002885</t>
+          <t>MB002860</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Duo de Protetor Solar para o Dia Todo</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · MN230 / 7ml</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -7627,7 +8509,7 @@
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>999.99</v>
+        <v>28.9</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -7642,12 +8524,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MB002884</t>
+          <t>MB002853</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Gel Esfoliante Flor de Damasco</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · MP200 / 50ml</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7656,7 +8538,7 @@
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>999.99</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -7671,12 +8553,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MB003660</t>
+          <t>MB002854</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Gel Esfoliante Flor de Damasco 100 ml</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · MP200 / 7ml</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -7685,7 +8567,7 @@
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>94.90000000000001</v>
+        <v>28.9</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -7700,12 +8582,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>MB003664</t>
+          <t>MB002855</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Gel de Limpeza Refrescante de Ameixa Verde</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · MY210 / 50ml</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -7714,7 +8596,7 @@
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>93.90000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -7729,12 +8611,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>MB002790</t>
+          <t>MB002856</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Gel de Água de Feijão Azuki</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · MY210 / 7ml</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -7743,7 +8625,7 @@
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>104.9</v>
+        <v>28.9</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -7758,12 +8640,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>MB002774</t>
+          <t>MB002857</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Hidratante Firmador Revive: Ginseng + Retinol</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · MY220 / 50ml</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -7772,7 +8654,7 @@
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>139.9</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -7787,12 +8669,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>MB003684</t>
+          <t>MB002858</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Hidratante Firmador Revive: ginseng + retinol 60 ml</t>
+          <t>Daily Tinted Fluid: protetor solar fluido com cor · MY220 / 7ml</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -7801,7 +8683,7 @@
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>139.9</v>
+        <v>28.9</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -7816,12 +8698,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>MB002832</t>
+          <t>MB003673</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Kit Essencial</t>
+          <t>Duo Dia e Noite: Relief Sun FPS 50+ PA++++ + Dynasty Cream</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -7830,7 +8712,7 @@
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>254.9</v>
+        <v>305.9</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -7845,12 +8727,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MB003686</t>
+          <t>MB003652</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Kit Essencial: 5 minis em nécessaire de viagem</t>
+          <t>Duo Dupla Limpeza: óleo de ginseng + gel de ameixa verde</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -7859,7 +8741,7 @@
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>255.9</v>
+        <v>155.9</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -7874,12 +8756,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>MB002871</t>
+          <t>MB002872</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Kit Protetores + Dupla Limpeza: 4 protetores, óleo e gel de limpeza</t>
+          <t>Duo Escudo Diário e Hidratação Profunda</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -7888,7 +8770,7 @@
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>291.9</v>
+        <v>999.99</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -7903,12 +8785,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>MB002788</t>
+          <t>MB003650</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Kit Rotina Refrescante Verde</t>
+          <t>Duo Iluminador e Firmador: Light On Serum + Revive Eye Serum</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -7917,7 +8799,7 @@
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>319.9</v>
+        <v>148.9</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -7932,12 +8814,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>MB003690</t>
+          <t>MB003689</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Kit Rotina Verde Refrescante: tônico de ameixa verde + Dayscreen FPS 30</t>
+          <t>Duo Proteja o Seu Brilho: Glow Serum + Dayscreen FPS 30</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -7946,7 +8828,7 @@
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>319.9</v>
+        <v>315.9</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -7961,12 +8843,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>MB002821</t>
+          <t>MB003688</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Leite de Arroz Reabastecedor Glow</t>
+          <t>Duo Proteção Diária e Hidratação Profunda: Dynasty Cream + Dayscreen FPS 30</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -7975,7 +8857,7 @@
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>256.9</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -7990,12 +8872,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>MB002810</t>
+          <t>MB002789</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Loção Solar Corporal Hydra Shield FPS 50+</t>
+          <t>Duo Refinador de Poros</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -8004,7 +8886,7 @@
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>181.9</v>
+        <v>999.99</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -8019,12 +8901,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>MB002876</t>
+          <t>MB003654</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Loção Solar Corporal Mineral Comfort Protection FPS 30</t>
+          <t>Duo Refinador de Poros: máscaras de feijão vermelho e de arroz com mel</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -8033,7 +8915,7 @@
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>999.99</v>
+        <v>180.9</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -8048,12 +8930,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MB002875</t>
+          <t>MB002884</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Loção Solar Corporal Mineral Comfort Protection FPS 40</t>
+          <t>Gel Esfoliante Flor de Damasco</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -8077,12 +8959,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>MB002879</t>
+          <t>MB003660</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Máscara Calmante de Barreira</t>
+          <t>Gel Esfoliante Flor de Damasco 100 ml</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -8091,7 +8973,7 @@
         </is>
       </c>
       <c r="D177" s="2" t="n">
-        <v>181.9</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -8106,12 +8988,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>MB002877</t>
+          <t>MB003664</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Máscara Calmante de Centella Asiática (10 unidades)</t>
+          <t>Gel de Limpeza Refrescante de Ameixa Verde</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -8120,7 +9002,7 @@
         </is>
       </c>
       <c r="D178" s="2" t="n">
-        <v>999.99</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -8135,12 +9017,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>MB002814</t>
+          <t>MB002832</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Máscara Facial Esfoliante Iluminadora de Arroz e Mel</t>
+          <t>Kit Essencial</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -8149,7 +9031,7 @@
         </is>
       </c>
       <c r="D179" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>254.9</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -8164,12 +9046,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>MB003655</t>
+          <t>MB003686</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Máscara Refrescante de Poros de Feijão Vermelho 140 ml</t>
+          <t>Kit Essencial: 5 minis em nécessaire de viagem</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -8178,7 +9060,7 @@
         </is>
       </c>
       <c r="D180" s="2" t="n">
-        <v>116.9</v>
+        <v>255.9</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -8193,12 +9075,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>MB002791</t>
+          <t>MB002871</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Máscara Refrescante para Poros com Feijão Azuki</t>
+          <t>Kit Protetores + Dupla Limpeza: 4 protetores, óleo e gel de limpeza</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -8207,7 +9089,7 @@
         </is>
       </c>
       <c r="D181" s="2" t="n">
-        <v>115.9</v>
+        <v>291.9</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -8222,12 +9104,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>MB003656</t>
+          <t>MB002788</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Máscara de Arroz Moído e Mel 150 ml</t>
+          <t>Kit Rotina Refrescante Verde</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -8236,7 +9118,7 @@
         </is>
       </c>
       <c r="D182" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>319.9</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -8251,12 +9133,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MB002799</t>
+          <t>MB003690</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Paleta Perfeita Hanbang</t>
+          <t>Kit Rotina Verde Refrescante: tônico de ameixa verde + Dayscreen FPS 30</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -8265,7 +9147,7 @@
         </is>
       </c>
       <c r="D183" s="2" t="n">
-        <v>999.99</v>
+        <v>319.9</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -8280,12 +9162,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MB002816</t>
+          <t>MB002876</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Sabonete Refrescante de Ameixa Verde · 100ml</t>
+          <t>Loção Solar Corporal Mineral Comfort Protection FPS 30</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -8309,12 +9191,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MB002817</t>
+          <t>MB002875</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Sabonete Refrescante de Ameixa Verde · 200ml</t>
+          <t>Loção Solar Corporal Mineral Comfort Protection FPS 40</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -8322,7 +9204,9 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="D185" s="2" t="n"/>
+      <c r="D185" s="2" t="n">
+        <v>999.99</v>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>Sem par</t>
@@ -8336,12 +9220,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MB002800</t>
+          <t>MB002791</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Saquinho Nobang para sabonete em barra, de organza</t>
+          <t>Máscara Refrescante para Poros com Feijão Azuki</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -8350,7 +9234,7 @@
         </is>
       </c>
       <c r="D186" s="2" t="n">
-        <v>29.9</v>
+        <v>115.9</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -8365,12 +9249,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>MB003691</t>
+          <t>MB002799</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Sérum Calmante Barreira: Green Tea-HA + pantenol 30 ml</t>
+          <t>Paleta Perfeita Hanbang</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -8379,7 +9263,7 @@
         </is>
       </c>
       <c r="D187" s="2" t="n">
-        <v>99.90000000000001</v>
+        <v>999.99</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -8394,12 +9278,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>MB002878</t>
+          <t>MB002816</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Sérum Calmante para a Barreira da Pele</t>
+          <t>Sabonete Refrescante de Ameixa Verde · 100ml</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -8423,12 +9307,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>MB002796</t>
+          <t>MB002817</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Sérum Firmador de Poros</t>
+          <t>Sabonete Refrescante de Ameixa Verde · 200ml</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -8436,9 +9320,7 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="D189" s="2" t="n">
-        <v>98.90000000000001</v>
-      </c>
+      <c r="D189" s="2" t="n"/>
       <c r="E189" t="inlineStr">
         <is>
           <t>Sem par</t>
@@ -8452,12 +9334,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>MB003698</t>
+          <t>MB002800</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Sérum Firmador de Poros: PDRN de feijão vermelho + peptídeo 30 ml</t>
+          <t>Saquinho Nobang para sabonete em barra, de organza</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -8466,7 +9348,7 @@
         </is>
       </c>
       <c r="D190" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>29.9</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -8481,12 +9363,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>MB002828</t>
+          <t>MB002796</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Sérum Solar Ginseng Hidratante (FPS 50+ PA++++)</t>
+          <t>Sérum Firmador de Poros</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -8495,7 +9377,7 @@
         </is>
       </c>
       <c r="D191" s="2" t="n">
-        <v>999.99</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -8510,12 +9392,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>MB002798</t>
+          <t>MB003698</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Trio Solar Perfeito Hanbang [Relief Sun + Bastão Solar Matte + Sérum Solar]</t>
+          <t>Sérum Firmador de Poros: PDRN de feijão vermelho + peptídeo 30 ml</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -8524,7 +9406,7 @@
         </is>
       </c>
       <c r="D192" s="2" t="n">
-        <v>999.99</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -8539,12 +9421,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>MB003672</t>
+          <t>MB002828</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Trio Solar Perfeito Hanbang: Relief Sun + Matte Sun Stick + Ginseng Moist Sun Serum</t>
+          <t>Sérum Solar Ginseng Hidratante (FPS 50+ PA++++)</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -8553,7 +9435,7 @@
         </is>
       </c>
       <c r="D193" s="2" t="n">
-        <v>306.9</v>
+        <v>999.99</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -8568,12 +9450,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>MB002792</t>
+          <t>MB002798</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Trio de Cuidados com os Poros de Feijão Azuki</t>
+          <t>Trio Solar Perfeito Hanbang [Relief Sun + Bastão Solar Matte + Sérum Solar]</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -8582,7 +9464,7 @@
         </is>
       </c>
       <c r="D194" s="2" t="n">
-        <v>400.9</v>
+        <v>999.99</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -8597,12 +9479,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>MB002815</t>
+          <t>MB003672</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Tônico Refrescante de Ameixa Verde: AHA + BHA</t>
+          <t>Trio Solar Perfeito Hanbang: Relief Sun + Matte Sun Stick + Ginseng Moist Sun Serum</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -8611,7 +9493,7 @@
         </is>
       </c>
       <c r="D195" s="2" t="n">
-        <v>999.99</v>
+        <v>306.9</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -8626,12 +9508,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>MB003665</t>
+          <t>MB002792</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Tônico Refrescante de Ameixa Verde: AHA + BHA 150 ml</t>
+          <t>Trio de Cuidados com os Poros de Feijão Azuki</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -8640,7 +9522,7 @@
         </is>
       </c>
       <c r="D196" s="2" t="n">
-        <v>104.9</v>
+        <v>400.9</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -8800,10 +9682,41 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K87" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K88" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId119"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId89"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId120"/>
   </tableParts>
 </worksheet>
 </file>
@@ -15559,7 +16472,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site oficial: https://beautyofjoseon.com · loja "Beauty of Joseon" · moeda USD · lido em 30/10/2026 06:04 UTC</t>
+          <t>Site oficial: https://beautyofjoseon.com · loja "Beauty of Joseon" · moeda USD · lido em 30/10/2026 06:07 UTC</t>
         </is>
       </c>
     </row>
